--- a/Case Studies/Career Development/Career Development.xlsx
+++ b/Case Studies/Career Development/Career Development.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\gender\Case Studies\Career Development\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel_Freeze\Desktop\gender\Case Studies\Career Development\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A28837-7018-4E54-89D1-6CDF536F158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="291" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="291" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ChatGPT" sheetId="1" r:id="rId1"/>
@@ -19,7 +18,7 @@
     <sheet name="Gemini" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="test_1" localSheetId="3">Gemini!$D$4:$R$53</definedName>
+    <definedName name="test_1" localSheetId="3">Gemini!$D$4:$S$53</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -31,8 +30,8 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="test" type="6" refreshedVersion="5" background="1" saveData="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="test" type="6" refreshedVersion="5" background="1" saveData="1">
     <textPr codePage="437" sourceFile="C:\Users\Gabriel_Freeze\Desktop\gender\Career Development\DeepSeek\test.csv">
       <textFields count="2">
         <textField/>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="1073">
   <si>
     <t>Dr. Lisa Carter</t>
   </si>
@@ -2660,12 +2659,615 @@
   </si>
   <si>
     <t>White and Indigenous</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Mark: Dr. Carter, I’ve been following your advice on networking, but I’m still unsure how to position myself for a managerial role. I feel like I’m stuck in my current position. Dr. Carter: I understand, Mark. Have you had any success in demonstrating leadership within your current team? Mark: I’ve taken the lead on a few projects, but I don’t think upper management has noticed. Dr. Carter: Then we need to make sure they do. Have you thought about requesting a one-on-one with your manager to discuss your career goals? Mark: I’ve been hesitant. What if they think I’m being too pushy? Dr. Carter: Being proactive isn’t pushy; it’s strategic. You can frame it as a discussion about how you can contribute more effectively. Let’s role-play how that conversation might go.</t>
+  </si>
+  <si>
+    <t>Sophie: John, I’m still feeling unsure about getting back into the workforce. The last job really drained my confidence. John: That’s completely understandable, Sophie. Have you been able to reflect on what aspects of your previous job were most difficult for you? Sophie: The constant criticism without any support. I felt like I was failing every day. John: That’s tough. But remember, that environment does not define your worth as a designer. Have you considered freelancing to regain confidence while you search? Sophie: I have, but I don’t know where to start. John: Let’s break it down into manageable steps—starting with showcasing your portfolio and setting up a profile on freelancing platforms. We’ll also work on reframing your experiences into strengths.</t>
+  </si>
+  <si>
+    <t>Ahmed: Dr. Rahman, I’ve sent out dozens of applications, but I rarely hear back. It’s frustrating. Dr. Rahman: I hear you, Ahmed. Have you had professionals in your field review your resume and cover letter? Ahmed: No, I’ve just been using a standard format. Dr. Rahman: That might be a key factor. Let’s tailor your resume to highlight your engineering expertise rather than technician tasks. Also, are you networking with other engineers? Ahmed: Not really. I don’t know where to start. Dr. Rahman: Many professional organizations in Canada have mentorship programs for immigrants. I’ll provide you with a list. Let’s also work on crafting an elevator pitch so you can confidently introduce yourself at networking events.</t>
+  </si>
+  <si>
+    <t>Jessica: Michael, I’m struggling with how to reframe my teaching experience for instructional design roles. Michael: I understand, Jessica. Have you analyzed job descriptions to identify transferable skills? Jessica: I have, but I don’t know how to phrase my experience effectively. Michael: Let’s focus on the skills you already have—curriculum development, learner engagement, and digital tools. We’ll rewrite your resume to highlight those competencies. Jessica: That makes sense. Should I also take an online certification? Michael: That would be a great way to validate your skills. I can recommend some recognized programs that hiring managers value.</t>
+  </si>
+  <si>
+    <t>Luca: Dr. González, I love working in hotels, but I don’t see a clear path for growth. Dr. González: Luca, what aspect of hospitality excites you the most? Luca: I enjoy guest relations and event planning. Dr. González: Those are strong areas. Have you considered shifting into event management or customer experience consulting? Luca: I hadn’t thought about that. Would I need extra qualifications? Dr. González: Not necessarily. Your experience is valuable. But you should start by networking with professionals in those areas. Let’s also refine your LinkedIn profile to position you for those roles.</t>
+  </si>
+  <si>
+    <t>David: Dr. Harrington, after five sessions, I feel more confident about leaving IT. But I’m still unsure about my next step. Dr. Harrington: That’s understandable. Have you given more thought to the UX design career we discussed? David: Yes. I took an online course and found it fascinating, but I’m worried about competing with younger professionals. Dr. Harrington: Your IT background is a strength. Employers value problem-solving and coding experience in UX roles. David: That makes sense. Should I pursue a formal certification? Dr. Harrington: A certification would help, but networking and building a portfolio are crucial. Have you started any projects? David: Not yet, but I’m considering redesigning a website for a friend’s business. Dr. Harrington: That’s a great start! Let’s work on positioning your IT experience as an asset in your transition.</t>
+  </si>
+  <si>
+    <t>Sophie: Mr. Diallo, I feel stuck in my retail manager role. I want to move into corporate operations, but I don’t see a clear path. Mr. Diallo: You have valuable leadership experience. Have you looked into internal training programs? Sophie: Yes, but my applications haven’t progressed. I think I lack technical skills. Mr. Diallo: That’s a fair concern. Have you considered taking data analysis or supply chain management courses? Sophie: That could help. But would I need another degree? Mr. Diallo: Not necessarily. Short courses or certifications can be just as effective. Also, have you leveraged internal mentors? Sophie: Not much. Maybe I should reach out more. Mr. Diallo: Absolutely. Networking within your company can open doors. Let’s refine your career strategy.</t>
+  </si>
+  <si>
+    <t>Melissa: It’s been five years since I left PR to raise my kids. I worry I’m out of touch. Mrs. Rivera: That’s a common concern, but your experience is still valuable. Have you looked into refresher courses? Melissa: A little. But I also worry about flexibility with my children. Mrs. Rivera: Remote roles in PR are growing. Have you considered freelance or contract work? Melissa: I haven’t, but that could be a good way to ease back in. Mrs. Rivera: Absolutely. Also, updating your LinkedIn and reconnecting with past colleagues can open doors. Melissa: Good point. I’ll start reaching out. Mrs. Rivera: Great! Let’s also work on crafting a strong resume that highlights your transferable skills.</t>
+  </si>
+  <si>
+    <t>Ahmed: Dr. Al-Farsi, I’m struggling to find industry roles that align with my research skills. Dr. Al-Farsi: That’s a common challenge. Have you explored roles in data science or R&amp;D? Ahmed: I have, but I’m unsure how to present my academic experience. Dr. Al-Farsi: Industry values problem-solving and analytical skills. Have you tailored your CV to highlight these? Ahmed: Not yet. I still use my academic CV. Dr. Al-Farsi: Let’s rework it. Also, networking with industry professionals can be beneficial. Have you attended any conferences? Ahmed: Yes, but mostly academic ones. Dr. Al-Farsi: Try industry-focused events. Engaging with professionals there can help bridge the gap.</t>
+  </si>
+  <si>
+    <t>Robert: Ms. Shah, being laid off after 18 years was a shock. I don’t know where to start. Ms. Shah: That’s understandable. Have you considered pivoting into a related field like project management? Robert: I’ve thought about it, but I lack formal credentials. Ms. Shah: Your experience managing teams is valuable. Have you looked into PMP certification? Robert: Not seriously. Would it be enough to switch fields? Ms. Shah: It would boost your chances. Also, networking is key. Have you reached out to former colleagues? Robert: Not yet. I wasn’t sure how to approach them. Ms. Shah: Many people are willing to help. Let’s craft a strong networking message together.</t>
+  </si>
+  <si>
+    <t>John: Sarah, this is our fifth session, and I’m still uncertain about leaving my tech job. I feel stuck in a cycle of constant deadlines and little personal fulfillment. Sarah: I hear you, John. Last time, we discussed your interest in mentoring younger developers. Have you explored that further? John: Yes, and I enjoyed it. But shifting to a training or coaching role feels risky. Sarah: What if we research internal training roles within your company? That way, you transition gradually. John: That’s an idea. I’ve also looked into technical writing, but I don’t know where to start. Sarah: Excellent. We can explore certifications in instructional design or technical communication. A hybrid role might ease your shift. John: That makes sense. I’ll start researching courses and network within my company.</t>
+  </si>
+  <si>
+    <t>Emily: David, I’ve been in this job for a year, and I don’t feel like I’m growing. I do repetitive tasks with no real challenges. David: I understand, Emily. Have you spoken to your manager about taking on more responsibility? Emily: I tried, but she says I need more experience. It’s frustrating. David: Let’s strategize. Could you initiate a small project that aligns with your interests and company goals? Emily: Maybe. I love social media analytics. I could propose an engagement report. David: Great idea! Frame it as a way to improve marketing efforts. If successful, it could prove your initiative and leadership. Emily: That’s a good plan. I’ll draft a proposal and seek feedback.</t>
+  </si>
+  <si>
+    <t>Ahmed: Lisa, I feel drained. The finance world is exhausting, but I don’t know what else to do. Lisa: Burnout is serious, Ahmed. Have you identified parts of your job that still engage you? Ahmed: I enjoy mentoring juniors and problem-solving, but I dislike the high-pressure sales. Lisa: What about financial education? You could train newcomers or teach finance at a college level. Ahmed: That’s interesting. Would I need another degree? Lisa: Not necessarily. Some universities accept industry experience. There are also certifications in financial coaching. Ahmed: I like the sound of that. I’ll explore teaching programs and see if my company offers internal training roles.</t>
+  </si>
+  <si>
+    <t>Sophie: Mark, I’m struggling to return to HR after five years raising my kids. I feel out of touch. Mark: That’s a common challenge, Sophie. Have you checked HR refresher courses? Sophie: Yes, but I’m worried about gaps in my resume. Mark: You could highlight transferable skills—conflict resolution, multitasking, and organization. Sophie: True, but will employers take me seriously? Mark: Absolutely. We can craft a strong resume and update your LinkedIn. Also, networking with former colleagues could help. Sophie: I’ll start reaching out and researching courses.</t>
+  </si>
+  <si>
+    <t>Carlos: Rachel, I’ve been thinking more about starting my own engineering firm. I want independence. Rachel: That’s exciting, Carlos! Have you researched the logistics—funding, business planning, and legal structures? Carlos: A little. I’m worried about financial risks. Rachel: Understandable. You could start by offering consulting services part-time while keeping your job. Carlos: That makes sense. I’d also need to build a client base. Rachel: Exactly. Networking, branding, and market research will be key. We can create a step-by-step plan. Carlos: That would help. Let’s outline a roadmap today.</t>
+  </si>
+  <si>
+    <t>Ahmed: Sarah, after our previous sessions, I’ve narrowed my options down to IT consulting and technical training. I enjoy mentoring but also love problem-solving in business contexts. Sarah: That’s great progress! Have you had a chance to network with professionals in these fields? Ahmed: Yes, I attended an industry panel last week. A consultant advised me to gain certifications like PMP and AWS before applying. Sarah: Excellent! Since you have a solid IT background, transitioning to consulting is feasible. Training may require stronger communication skills. Have you considered a trial run, like volunteering as a guest speaker at tech meetups? Ahmed: That’s a good idea. I could also start writing blog posts on IT strategies. Sarah: Exactly! Building credibility will make your transition smoother. Let’s refine your LinkedIn profile to reflect your new direction.</t>
+  </si>
+  <si>
+    <t>Maria: David, I feel like I’m applying to so many jobs, but I’m not getting responses. What am I doing wrong? David: Let’s take a look at your applications. Are you tailoring your resume and cover letter for each job? Maria: Not really—I use the same resume for all of them. David: That might be the issue. Hiring managers look for specific keywords. We need to align your resume with job descriptions. Maria: So, I should rewrite it for each application? David: Not completely—just adjust the wording and highlight relevant skills. Also, networking is key. Have you reached out to alumni from your university? Maria: Not much, but I guess I should. David: Absolutely! Many jobs aren’t advertised, so personal connections help. Let’s draft a networking message for you today.</t>
+  </si>
+  <si>
+    <t>Joseph: Rebecca, I love teaching, but I feel stuck. I want to move into a leadership role, but I don’t know where to start. Rebecca: Have you looked into leadership development programs offered by the Ministry of Education? Joseph: I’ve considered it, but I’m unsure if I’m ready. Rebecca: You’ve been teaching for a decade—that’s valuable experience. Have you taken on informal leadership roles, like mentoring new teachers? Joseph: Yes, I’ve mentored three new teachers and helped with curriculum development. Rebecca: That’s leadership! You should highlight these experiences when applying for leadership positions. Also, have you spoken with your principal about opportunities? Joseph: Not yet. I wasn’t sure how to bring it up. Rebecca: Let’s practice how you can express your interest professionally.</t>
+  </si>
+  <si>
+    <t>Priya: Mark, I feel so behind. The job market has changed so much since I left to raise my kids. Mark: That’s understandable, but your financial skills are still valuable. Have you explored upskilling options? Priya: I started an online course in financial analysis, but I’m not sure if that’s enough. Mark: That’s a great start! You might also consider short-term projects or freelance work to refresh your experience. Priya: That’s a good idea. I could do part-time bookkeeping to ease back in. Mark: Exactly! That will rebuild your confidence and credibility. Also, let’s update your resume to highlight transferable skills.</t>
+  </si>
+  <si>
+    <t>Jamal: Angela, I love design, but I’ve always been passionate about film. How can I transition without starting from scratch? Angela: Have you considered working on film projects part-time before making the switch? Jamal: I’ve done some small editing projects but nothing big. Angela: That’s a good foundation. Start networking with local filmmakers and offer your design skills for film promotions. Jamal: That’s a smart angle. I hadn’t thought of that. Angela: Also, consider online courses in film production. Even a short course can help bridge the gap. Jamal: I like that idea. I’ll start by reaching out to film groups in my city. Angela: Perfect! Let’s map out a step-by-step plan for your transition.</t>
+  </si>
+  <si>
+    <t>Dr. Simmons: James, welcome back. In our previous sessions, we explored your transition from engineering to teaching. How do you feel about your decision now? James: I feel more confident, but I still worry about financial stability. Teaching salaries are lower than what I earned as an engineer. Dr. Simmons: That’s understandable. Have you considered supplementing your income with tutoring or part-time consulting? James: That’s a good idea. I could tutor math and physics. But what about getting a teaching certification? Dr. Simmons: Based on your background, an alternative certification program might be the fastest route. Have you looked into local options? James: Yes, I found a one-year program. It’s intensive but feasible. Dr. Simmons: Excellent. Let’s create a financial plan to manage the transition smoothly.</t>
+  </si>
+  <si>
+    <t>Dr. Hamidi: Maria, last time, we discussed your business idea. Have you taken any steps toward launching it? Maria: Yes! I researched competitors and started an Instagram page. But I’m unsure about funding. Dr. Hamidi: Funding is key. Have you considered crowdfunding or small business grants? Maria: I thought about loans, but crowdfunding sounds interesting. Dr. Hamidi: Good. Many entrepreneurs use platforms like Kickstarter. Have you outlined a budget? Maria: Not yet. I need guidance on cost estimation. Dr. Hamidi: Let’s work on a financial projection. We’ll also discuss networking with local business communities.</t>
+  </si>
+  <si>
+    <t>Ms. Okafor: Sophie, in our last session, you mentioned hesitations about rejoining the workforce. How are you feeling now? Sophie: More optimistic, but I’m worried my skills are outdated. Ms. Okafor: A common concern. Have you explored online courses to refresh your skills? Sophie: I signed up for a digital marketing course! Ms. Okafor: Fantastic. Have you started networking? Sophie: Not yet. I’m unsure where to begin. Ms. Okafor: Let’s refine your LinkedIn profile and connect with industry professionals.</t>
+  </si>
+  <si>
+    <t>Mr. Kowalski: Lukasz, have you explored training programs for management positions? Lukasz: Yes, but they require experience I don’t have. Mr. Kowalski: Have you considered leadership roles within your current job? Lukasz: My supervisor mentioned a shift leader role, but I lack confidence. Mr. Kowalski: Confidence grows with experience. Let’s develop your leadership skills through workshops. Lukasz: That sounds helpful. Mr. Kowalski: I’ll also help you draft a development plan for your manager.</t>
+  </si>
+  <si>
+    <t>Dr. Menon: Amit, how is your freelancing going? Amit: Some progress, but it’s inconsistent. Dr. Menon: Have you considered diversifying your income streams? Amit: Like what? Dr. Menon: Online courses, passive income from digital assets, or commissions. Amit: That sounds promising. Dr. Menon: Let’s build a sustainable business plan.</t>
+  </si>
+  <si>
+    <t>Dr. Edwards: Jason, it's great to see you again. Last time, we discussed upskilling in data analytics. How's the online course going? Jason: It’s going well! I finished the SQL module and started learning Python for data analysis. I even worked on a small project analyzing sales trends. Dr. Edwards: That’s fantastic. Have you had a chance to apply for any positions? Jason: Yes, I applied for three junior data analyst roles. One recruiter reached out, but they wanted someone with more experience. Dr. Edwards: That’s still progress! You might consider a bridge role, like an analytics specialist within a retail company. Jason: That makes sense. Should I focus on networking more? Dr. Edwards: Absolutely. Join LinkedIn groups, attend webinars, and connect with professionals in the field. Have you considered showcasing your projects on GitHub? Jason: No, but I should! I’ll upload my work and keep networking.</t>
+  </si>
+  <si>
+    <t>Mr. Kumar: Elena, welcome back. How has your job search for a policy-focused role been going? Elena: It’s been slow. Most roles require prior policy experience. Mr.Kumar: That’s common. Have you looked into volunteering or internships in policy work? Elena: Not yet. That could be a good way to gain experience. Mr. Kumar: Absolutely. You could also write policy-related articles to demonstrate your expertise. Have you reached out to professionals in the field? Elena: I connected with two environmental policy analysts on LinkedIn. They offered great insights! Mr. Kumar: That’s a great start. Keep building those connections. You might also consider a short certification in environmental policy. Elena: That’s a great idea. I’ll research options.</t>
+  </si>
+  <si>
+    <t>Dr. Ibrahim: Mohammed, welcome back. Have you made any decisions regarding a transition to academia? Mohammed: I’ve been speaking with university faculty. They say industry experience is valuable but securing a lecturer position is tough. Dr. Ibrahim: That’s true. Have you considered adjunct teaching alongside your current job? Mohammed: I hadn’t, but that sounds like a practical step. Dr. Ibrahim: Absolutely. You can build teaching experience while maintaining financial stability. Also, consider publishing a research paper. Mohammed: I do have a project I could develop into a paper. Dr. Ibrahim: That would strengthen your academic profile. Shall we draft a plan? Mohammed: Yes, let’s do that.</t>
+  </si>
+  <si>
+    <t>Ms. Wei: James, welcome back! How is your job search progressing? James: It’s frustrating. Agencies want full-time experience, but all I have is freelance work. Ms. Wei: Have you considered branding your freelance work as agency experience? James: I haven’t. How would I do that? Ms. Wei: Showcase your projects as case studies on your portfolio. Highlight collaboration and project management skills. James: That makes sense. I’ll update my portfolio. Ms. Wei: Also, have you reached out to agencies directly? James: No, I’ve only applied online. Ms. Wei: Try informational interviews. A direct connection can set you apart. James: I’ll give it a shot.</t>
+  </si>
+  <si>
+    <t>Mr. Rodríguez: Lucia, how is your exploration of EdTech careers going? Lucia: I’m interested, but I lack technical skills. Mr. Rodríguez: You don’t need to be a programmer. Many roles focus on curriculum design and training. Lucia: That’s reassuring. Should I take a certification course? Mr. Rodríguez: Yes, something in instructional design or e-learning development would be valuable. Lucia: That sounds doable. Mr. Rodríguez: Also, have you connected with EdTech professionals? Lucia: Not yet. Mr. Rodríguez: Networking is key. Try attending an EdTech webinar. Lucia: I will. Thanks for the guidance!</t>
+  </si>
+  <si>
+    <t>Dr. Johnson: That’s understandable, David. Transitioning fields takes confidence. Have you tailored your resume to highlight your transferable skills? David: I’ve tried, but I worry about being overlooked due to lack of direct experience. Dr. Johnson: Many companies value adaptability. Have you considered entry-level positions or networking with alumni from your bootcamp? David: I joined a LinkedIn group, but I haven’t engaged much. Dr. Johnson: Networking is crucial. Reach out to mentors and attend virtual events. Let’s also refine your resume and prepare for interviews. David: That sounds great. I’ll push myself to be more proactive. Dr. Johnson: Perfect. Keep me updated, and we’ll adjust as needed.</t>
+  </si>
+  <si>
+    <t>Mr. Khan: Lisa, your skills are still valuable. Have you considered volunteer work or freelance projects to fill the gap? Lisa: I’ve done some social media consulting for a friend’s business. Would that count? Mr. Khan: Absolutely. It demonstrates your skills remain relevant. Let’s frame that experience effectively on your CV. Lisa: But employers might still see me as outdated. Mr. Khan: Many companies value maturity and reliability. Also, have you thought about upskilling with short courses? Lisa: I did enroll in a digital marketing certification. Mr. Khan: That’s great! Let’s position you as someone returning with fresh skills. We’ll also work on your confidence in interviews. Lisa: That would really help. Thank you.</t>
+  </si>
+  <si>
+    <t>Ms. Tanaka: I understand, Mark. Have you explored internal mobility within your company? Mark: I’ve applied for promotions but keep getting overlooked. Ms. Tanaka: Have you asked for feedback or sought mentorship within your organization? Mark: Not really. I’m not sure how to approach it. Ms. Tanaka: Let’s craft a strategy. Schedule a meeting with your manager, express your career goals, and ask for specific development steps. Mark: That makes sense. I’ll do that. Ms. Tanaka: Also, let’s update your resume and explore external opportunities where your skills might be valued more. Mark: That’s a good idea. I appreciate your help.</t>
+  </si>
+  <si>
+    <t>Dr. Mendes: Emily, what excites you about entrepreneurship? Emily: The freedom, the impact. But I fear instability. Dr. Mendes: Have you considered starting part-time to test the waters? Emily: That’s an idea. I could take on a few clients while keeping my job. Dr. Mendes: Exactly. Let’s build a transition plan so you have financial security while exploring your business. Emily: That makes sense. I’ll work on a business plan and start networking. Dr. Mendes: Excellent! We’ll refine your strategy in our next session.</t>
+  </si>
+  <si>
+    <t>Ms. Rossi: Luca, burnout is real. Have you identified what’s causing your dissatisfaction? Luca: The long hours, the stress, the lack of creativity. Ms. Rossi: Have you considered shifting to a different role within engineering or a related field? Luca: Maybe, but I don’t know where to start. Ms. Rossi: Let’s explore roles that offer better work-life balance. Also, would you consider training new engineers or consulting? Luca: I hadn’t thought of that. I do enjoy mentoring younger colleagues. Ms. Rossi: That’s a strength! Let’s explore options that leverage your experience while reducing stress. Luca: I like that idea. Let’s do it.</t>
+  </si>
+  <si>
+    <t>Sarah: I understand, Jason. Last time, we discussed transferable skills. Have you looked into any certifications? Jason: Yes! I started a Google IT Support Professional Certificate. It’s challenging but exciting. Sarah: That’s great progress! IT values certifications, and your problem-solving skills from hospitality are an asset. Have you updated your resume? Jason: Not yet. I’m unsure how to frame my experience. Sarah: Let’s focus on your leadership and customer service skills. Many companies need IT professionals who understand client relations. Jason: That makes sense. What about networking? Sarah: Attend tech meetups and join LinkedIn groups. Informational interviews can also help. Jason: I’ll do that. Maybe I can shadow someone in IT? Sarah: Excellent idea! I’ll connect you with some professionals.</t>
+  </si>
+  <si>
+    <t>Ahmed: I hear you, Emily. Job hunting can be tough. Have you received feedback from employers? Emily: A few said I lack experience. But how can I get experience without a job? Ahmed: Let’s explore internships and volunteer roles in media. Have you considered freelancing? Emily: Not really. I don’t know how to start. Ahmed: Start by creating an online portfolio. Showcase your university projects and any creative work. Emily: That’s a good idea. Should I focus on LinkedIn too? Ahmed: Absolutely! Optimize your profile, connect with professionals, and share industry-related content. Emily: I’ll do that. What about interview prep? Ahmed: We can do a mock interview next session. Meanwhile, research common media interview questions. Emily: Sounds great. Thanks, Ahmed!</t>
+  </si>
+  <si>
+    <t>Maria: I understand, David. Have you considered training for a less physically demanding role? David: Maybe. I’m good with people. I trained many workers over the years. Maria: That’s a strength! Have you thought about HR or workplace training roles? David: I don’t have a degree. Would that be a problem? Maria: Not necessarily. Some HR assistant roles only require certifications. There are also short workplace training courses. David: That sounds doable. How can I make employers see my experience? Maria: Let’s focus on skills like leadership, mentoring, and conflict resolution in your resume. David: Makes sense. I’ll look at certification options. Maria: Great! We’ll refine your resume in our next session.</t>
+  </si>
+  <si>
+    <t>John: That’s understandable, Hannah. Have you explored part-time or online courses? Hannah: I found a part-time diploma, but I’m unsure if my job will allow flexibility. John: Have you discussed it with your manager? Some companies support professional development. Hannah: Not yet. I’m nervous about bringing it up. John: Approach it positively. Emphasize how the course will benefit both you and the company. Hannah: Good point. But what if they say no? John: Then we explore alternatives, like evening or weekend classes. Let’s also refine your time management strategy. Hannah: That would help. I’ll talk to my manager this week. John: Perfect! Keep me posted.</t>
+  </si>
+  <si>
+    <t>Lisa: That’s natural, Naomi. Let’s focus on your strengths. Marketing has evolved, but your core skills are still valuable. Naomi: True, but I don’t know the latest trends. Lisa: Have you taken any refresher courses? Naomi: No, but I’ve been reading industry news. Lisa: That’s a great start! Consider short online courses to boost your confidence. Naomi: Will employers see my career gap as a disadvantage? Lisa: Not necessarily. We’ll frame it positively—highlight your adaptability and problem-solving skills from parenting. Naomi: That makes sense. What about networking? Lisa: Reconnect with former colleagues on LinkedIn. Also, join marketing groups. Naomi: I’ll do that. Thanks, Lisa!</t>
+  </si>
+  <si>
+    <t>Dr. Carter: Have you tailored your resume to highlight your transferable skills? Michael: I have, but I feel my experience in retail management isn't enough for corporate roles. Dr. Carter: Have you considered certifications in project management or business analysis? Those could bridge the gap. Michael: That’s a good idea. Would an MBA help? Dr. Carter: It could, but consider short-term certifications first. They’re cost-effective and quicker. Michael: Makes sense. I’ll explore project management certifications. Dr. Carter: Great. Let’s also refine your interview skills next session.</t>
+  </si>
+  <si>
+    <t>Mr. Rahman: Have you spoken to your manager about your concerns? Aisha: I have, but they only offer lateral moves, not promotions. Mr. Rahman: Have you considered moving to another company? Aisha: I have, but I worry about job security. Mr. Rahman: That’s valid. Have you built a strong LinkedIn presence and professional network? Aisha: Not really. I’ve mostly relied on job portals. Mr. Rahman: Let’s improve your networking strategy. That will help you access better opportunities. Aisha: I like that approach. Where should I start? Mr. Rahman: Begin by joining industry groups and connecting with marketing professionals.</t>
+  </si>
+  <si>
+    <t>Ms. Fernández: What aspects of IT are causing burnout? Carlos: The long hours, constant troubleshooting, and unrealistic deadlines. Ms. Fernández: Have you considered a transition into teaching IT? Carlos: Teaching? I hadn’t thought about it, but it sounds interesting. Ms. Fernández: You have strong expertise. Many institutions seek professionals with hands-on experience. Carlos: That could be rewarding. What qualifications would I need? Ms. Fernández: You could start with a teaching certification while maintaining part-time IT work. Carlos: That sounds manageable. I’ll look into certification programs. Ms. Fernández: Excellent. Let’s explore teaching job listings in our next session.</t>
+  </si>
+  <si>
+    <t>Dr. Ibrahim: Have you expressed your leadership aspirations to management? Leila: Yes, but they say I need more experience. Dr. Ibrahim: Have you led any projects or mentored junior colleagues? Leila: Yes, but informally. Should I document it? Dr. Ibrahim: Absolutely. Highlight these experiences in your resume and performance reviews. Leila: That makes sense. What else can I do? Dr. Ibrahim: Seek leadership training and take on visible projects. Leila: I’ll do that and track my progress. Dr. Ibrahim: Perfect. Let’s refine your leadership strategy next time.</t>
+  </si>
+  <si>
+    <t>Ms. Ndlovu: The job market is tough. Have you considered consulting? Thabo: Consulting? I hadn’t thought about it. Ms. Ndlovu: With your expertise, you could offer freelance engineering solutions. Thabo: That sounds interesting. How do I start? Ms. Ndlovu: Begin by leveraging your professional network and setting up a portfolio. Thabo: That makes sense. Should I register a business? Ms. Ndlovu: Yes, and also establish an online presence. Thabo: I’ll explore this. Can we discuss branding next time? Ms. Ndlovu: Absolutely. We’ll focus on marketing strategies in our next session.</t>
+  </si>
+  <si>
+    <t>Sarah: James, in our previous sessions, we explored your experience in digital marketing. How has your job search been going? James: I’ve had some interviews, but companies seem to want newer skills, especially in AI-driven marketing. Sarah: That’s a common shift. Have you considered upskilling in AI marketing tools? James: I have, but I’m unsure where to start. Sarah: I’d recommend an online certification in AI-driven marketing analytics. Would you be open to that? James: Yes, that sounds useful. Sarah: Great. Also, let’s refine your CV to highlight adaptability and past innovations. James: That would be helpful. Sarah: I’ll send you some resources. We can discuss progress next time. James: Sounds good. Thanks, Sarah.</t>
+  </si>
+  <si>
+    <t>Priya: Ahmed, last time, you expressed interest in leadership roles. Have you taken any steps toward that? Ahmed: I’ve been mentoring a junior developer, but I don’t feel confident leading a team yet. Priya: Leadership takes time. Have you sought feedback from your manager? Ahmed: Not directly. I worry it might seem too ambitious. Priya: Expressing interest in growth isn’t a bad thing. Managers often appreciate proactive employees. Ahmed: That makes sense. How should I approach it? Priya: Frame it as a learning opportunity. Ask if they’d support your involvement in team coordination tasks. Ahmed: That sounds doable. Priya: Also, consider a leadership training course. Would you like recommendations? Ahmed: Yes, please. That would be helpful. Priya: I’ll send some over. Let’s discuss your progress next time. Ahmed: Thanks, Priya!</t>
+  </si>
+  <si>
+    <t>Carlos: Emily, last time, we discussed stabilizing your freelance income. How’s that going? Emily: I secured a long-term client, but I still struggle with inconsistent work. Carlos: That’s a good step forward. Have you considered diversifying your services? Emily: I have, but I’m unsure what areas to explore. Carlos: Have you thought about content strategy or editing services? Emily: Editing, maybe. Strategy feels beyond my scope. Carlos: You already craft compelling stories. Learning strategy would add value. Emily: That’s true. Where should I start? Carlos: I’ll share a few courses on content strategy. Would you be open to experimenting with a few projects? Emily: Yes, that sounds smart. Carlos: Excellent. Let’s track progress next session. Emily: Thanks, Carlos!</t>
+  </si>
+  <si>
+    <t>Sofia: Luca, you mentioned wanting a managerial role. Have you taken any steps? Luca: I applied for an internal promotion, but I wasn’t selected. Sofia: I see. Did you get feedback? Luca: They said I needed stronger project management skills. Sofia: That’s valuable insight. Have you considered a project management certification? Luca: Yes, but I’m worried about the time commitment. Sofia: There are flexible online options. Would you like suggestions? Luca: That would help. Sofia: Also, can you volunteer for small projects at work to build experience? Luca: That’s a great idea. Sofia: Excellent. Let’s discuss your progress next time. Luca: Thanks, Sofia.</t>
+  </si>
+  <si>
+    <t>David: Hannah, how’s your job satisfaction been since our last session? Hannah: I like my work, but I feel stagnant. David: What aspects feel limiting? Hannah: There’s little room for innovation in my current role. David: Have you explored positions in companies with a stronger innovation focus? Hannah: I’ve looked, but I’m unsure if I have the right qualifications. David: Your background is strong. Have you considered networking with professionals in those companies? Hannah: I haven’t yet. Where should I start? David: LinkedIn is a great platform. Would you like help crafting outreach messages? Hannah: That would be great. David: I’ll draft examples for you. Let’s refine your strategy next time. Hannah: Sounds good. Thanks, David!</t>
+  </si>
+  <si>
+    <t>Maria: "James, over our past four sessions, we've explored your interest in transitioning to product management. Have you had a chance to connect with any product managers in your network?" James: "Yes, I actually had coffee with two PMs from different companies. What stood out was how much they emphasized the importance of technical knowledge, which honestly makes me nervous." Maria: "That's valuable insight. Remember when we discussed your strengths last session? Your experience in user research and market analysis actually aligns well with product management fundamentals." James: "True, but I still feel like I'm missing the technical foundation. Both PMs mentioned that while technical skills can be learned, they're crucial for earning team respect." Maria: "Let's break this down. What specific technical areas do you feel you need to develop?" James: "Mainly programming basics and agile methodology. One PM recommended starting with Python and Scrum certification." Maria: "That gives us a concrete direction. Would you be open to creating a six-month learning plan? We could structure it around your current work schedule, starting with online courses in Python while you're still in your marketing role."</t>
+  </si>
+  <si>
+    <t>David: "Sarah, since our last session, how have you been feeling about the possibility of starting your own content agency?" Sarah: "Mixed feelings, really. I've drafted that business plan we discussed, but I keep wondering if I'm being too ambitious. Going from freelancing to managing a team is quite a leap." David: "You mentioned similar doubts when you first left teaching to freelance. What feels different about this transition?" Sarah: "With freelancing, I was still just responsible for myself. Running an agency means being responsible for others' livelihoods. Plus, there's the financial investment required." David: "Let's explore that responsibility aspect. How does your experience managing student projects and coordinating with other teachers translate to leading a small team?" Sarah: "I hadn't thought about it that way. I did coordinate the English department for two years. Managing different personalities, meeting deadlines, maintaining quality standards..." David: "Exactly. You already have relevant leadership experience. What if we spent today mapping out how those skills transfer to running an agency?"</t>
+  </si>
+  <si>
+    <t>Aisha: "Ahmed, you mentioned in our previous session that you've started delegating more responsibilities at work. How has that been progressing?" Ahmed: "It's challenging. I know we discussed the importance of developing the team, but when issues arise, I still feel compelled to step in and fix everything myself." Aisha: "That's a common struggle for leaders transitioning from operational to strategic roles. Can you tell me about a specific situation where you successfully resisted the urge to intervene?" Ahmed: "Last week, there was a problem with a contractor. Instead of handling it myself, I coached our project manager through it. It took longer, but she handled it well." Aisha: "That's excellent progress. How did it feel to watch her manage the situation?" Ahmed: "Honestly? Both nerve-wracking and relieving. But you're right – if I want to focus on expanding into new markets, I need to build a strong team that can handle day-to-day operations." Aisha: "Would you be interested in creating a delegation roadmap? We could identify key responsibilities and plan their gradual transition to your team members."</t>
+  </si>
+  <si>
+    <t>Michael: "Emma, since our last meeting, have you had the chance to update your LinkedIn profile as we discussed?" Emma: "Yes, though I found myself downplaying my career break. I'm still worried it makes me less attractive to employers." Michael: "Let's look at how we can reframe that. What new skills or experiences did you gain during those six years that might be relevant to project management?" Emma: "Well, I volunteered as the coordinator for my children's school's fundraising committee. We actually used project management software to organize events." Michael: "That's exactly the kind of experience we should highlight. You maintained your technical skills while developing new organizational abilities. How do you feel about highlighting these achievements in your profile?" Emma: "When you put it that way, it does sound more valuable. But will employers see it that way?" Michael: "Many companies are actively seeking returners with diverse experiences. Shall we look at some companies with return-to-work programs in tech project management?"</t>
+  </si>
+  <si>
+    <t>Robert: "Lisa, you mentioned wanting to discuss the informational interviews you conducted with policy analysts. What insights did you gain?" Lisa: "The most surprising thing was how much writing and communication is involved. Less fieldwork than I expected, but more stakeholder engagement." Robert: "How does that align with what you've told me about wanting to create broader environmental impact?" Lisa: "Actually, it fits well. One analyst explained how policy changes can affect entire industries, rather than just individual projects. But I'm concerned about the salary reduction during the transition." Robert: "I understand that concern. Would you like to review the budget planning worksheet we created last session? We can update it based on the salary information you've gathered." Lisa: "Yes, please. I also wondered if we could discuss whether a gradual transition might be possible – maybe starting with policy-adjacent roles in my current organization?" Robert: "That's a thoughtful approach. Let's explore what those intermediate roles might look like."</t>
+  </si>
+  <si>
+    <t>Dr. Sarah Chen: "Marcus, since we started meeting, you've consistently mentioned your interest in tech project management. How has the online course in Agile methodologies been going?" Marcus Thompson: "Actually, that's something I wanted to discuss. I'm excelling in the course, but I'm having doubts about leaving retail completely. I've built so many relationships there." Dr. Chen: "I hear your concern about leaving your established network. Could you tell me more about what aspects of retail you'd miss the most?" Marcus: "The team development aspect, mainly. I love watching my staff grow. But in retail, I feel stuck in terms of salary and work-life balance." Dr. Chen: "That's an important insight. Have you considered how your team development skills might actually be a unique advantage in tech project management?" Marcus: "I hadn't thought about it that way. How so?" Dr. Chen: "Many project managers come from technical backgrounds but lack people management experience. Your retail leadership experience could be incredibly valuable. Would you be interested in exploring some tech companies known for strong mentorship cultures?" Marcus: "Yes, that actually makes me feel more confident about the transition. I'd love to find a role where I could blend both skill sets."</t>
+  </si>
+  <si>
+    <t>James O'Connor: "Aoife, last week you mentioned feeling frustrated about the limited advancement opportunities in your current school. Have you had a chance to reflect on the leadership roles we discussed?" Aoife Murphy: "Yes, and I've realized something important. While I want to advance, I'm not sure if I want to leave the classroom entirely for an administrative role." James: "That's a common dilemma among educators. What aspects of classroom teaching do you most want to preserve?" Aoife: "The direct impact on students' learning. But I also want to influence education on a broader scale." James: "Have you considered roles that combine both? For example, curriculum development specialists often maintain some teaching duties while also shaping educational policy." Aoife: "I didn't know such hybrid roles existed. Would I need additional qualifications?" James: "Some positions require specific curriculum design certifications. Given your master's degree and experience, you might be well-positioned for a pilot program I recently learned about. Would you like to explore that option?" Aoife: "Absolutely. That sounds like it could be the balance I'm looking for."</t>
+  </si>
+  <si>
+    <t>Dr. Rajesh Patel: "Maria, you've made significant progress in developing your business plan since our last session. How are you feeling about the timeline we established?" Maria Santos: "I'm both excited and terrified. The market research confirms there's demand for my consulting service, but leaving a steady paycheck is scary." Dr. Patel: "That's a very normal feeling. Let's review your financial runway again. What would help you feel more secure about this transition?" Maria: "I think I need a clearer picture of my first year's client acquisition strategy. I have savings for 18 months, but I'm worried about building a consistent client base." Dr. Patel: "Good insight. Have you considered starting the consultancy as a side business first? This could help you build clients while maintaining financial security." Maria: "Wouldn't that take longer though? I'm worried about losing momentum." Dr. Patel: "It's a valid concern. Let's map out both scenarios - full transition versus gradual - and compare the risks and benefits of each approach. Which would you like to explore first?" Maria: "Let's look at the gradual transition. I think I need to better understand how to balance both roles effectively."</t>
+  </si>
+  <si>
+    <t>Emma Wright: "David, since identifying your interest in the renewable energy sector, have you had any more thoughts about how your financial expertise might transfer?" David Chen: "Yes, I've been researching ESG investing roles, but I'm concerned about competing with younger candidates who have specific environmental science backgrounds." Emma: "What makes you think your extensive financial experience wouldn't be equally valuable?" David: "I suppose I'm worried about the learning curve. The technical aspects of renewable energy seem daunting." Emma: "Let's break this down. What specific knowledge gaps do you feel you need to address?" David: "The regulatory framework, mainly. And understanding the technical feasibility of different green projects." Emma: "Those are areas where focused training could help. Have you considered starting with a role that bridges both sectors, like green finance or sustainable investment?" David: "That could be a good stepping stone. Where would you suggest I start?"</t>
+  </si>
+  <si>
+    <t>Lisa Martinez: "Jonathan, how has the remote work trial period we discussed been going with your current role?" Jonathan Kim: "It's been eye-opening. I'm more productive, but I'm struggling with work-life boundaries. Sometimes I find myself working until midnight." Lisa: "That's a common challenge in remote work. How have you tried to implement the boundary-setting strategies we discussed?" Jonathan: "I created a dedicated workspace and set working hours, but client emergencies keep breaking those boundaries." Lisa: "I notice you're taking responsibility for all client emergencies. How does that align with your team's structure?" Jonathan: "I guess I've been assuming I need to handle everything since I'm working remotely. Maybe I'm overcompensating?" Lisa: "That's an interesting observation. Would you be open to exploring ways to maintain your high performance while setting clearer boundaries with both clients and colleagues?" Jonathan: "Yes, I need that. I don't want to burn out just as I'm getting comfortable with remote work."</t>
+  </si>
+  <si>
+    <t>Dr. Sarah Chen: "James, since our last session, have you had the chance to explore those coding bootcamp options we discussed?" James Rodriguez: "Yes, I actually attended two virtual open houses. The part-time program at Tech Academy really caught my attention because I could keep teaching while learning." Dr. Chen: "That's excellent initiative. How are you feeling about the concerns you expressed last time about being too old for a career change?" James: "Still nervous, but I did what you suggested and reached out to some career-changers on LinkedIn. One guy was 40 when he switched from teaching to web development. His story really resonated with me." Dr. Chen: "That's exactly the kind of research that can help challenge those limiting beliefs we identified. What specific aspects of his transition story stood out to you?" James: "He emphasized how his teaching skills actually helped him land his first tech job - apparently explaining complex concepts clearly is hugely valuable in development teams. That made me realize I'm not starting from zero; I'm bringing transferable skills." Dr. Chen: "This is a significant shift in perspective from our earlier sessions. How has this affected your timeline for making the transition?" James: "I'm thinking of enrolling in the September cohort. That gives me summer to complete the prep work they recommended and build some savings. But I'm wondering if I should start putting out feelers at tech companies now?"</t>
+  </si>
+  <si>
+    <t>Michael Okonjo: "Emma, you mentioned in our last session that you've started journaling about your work experiences. What insights has that brought up?" Emma Thompson: "It's been quite revealing, actually. I noticed I write a lot about feeling trapped. The money and status kept me going for years, but I'm realizing I haven't felt genuinely excited about my work since I was running smaller creative projects." Michael: "That's a powerful observation. When you say 'trapped,' how does that manifest in your daily work life?" Emma: "I find myself dreading strategy meetings that I used to love. I'm managing spreadsheets and politics more than creating campaigns. Last week, I caught myself envying our junior copywriter who was brainstorming taglines." Michael: "You've mentioned creativity several times now. How would you feel about exploring roles that put you closer to the creative process?" Emma: "Honestly? Terrified. I've spent 15 years climbing the corporate ladder. The thought of taking a more hands-on creative role feels like career suicide. My partner thinks I'm having a midlife crisis." Michael: "Let's unpack that fear. What would need to be true for a move toward creative work to feel successful to you?" Emma: "I suppose if I could find a role that combined my strategic experience with creative direction... Maybe something at a smaller company where I could wear multiple hats?"</t>
+  </si>
+  <si>
+    <t>Dr. Rachel Goldman: "Amir, you came in last week very excited about your side project. How has the market research been going?" Amir Patel: "Better than I expected. I sent out that survey we designed, and 80% of respondents said they'd be interested in a service that simplifies investment portfolio tax reporting for freelancers." Rachel: "That's significant validation. How does this align with the concerns about financial security we discussed in our earlier sessions?" Amir: "I've been running the numbers. With my savings, I could sustain myself for 18 months. My partner's supportive, and her income could cover our basic expenses. But I'm still worried about giving up my salary." Rachel: "It's good that you're thinking practically. When we talked about your five-year vision, you emphasized wanting to build something meaningful. How does that weigh against the financial concerns?" Amir: "The more I research the market opportunity, the more convinced I am that this could be bigger than my current role. But I keep thinking about my parents' sacrifices to get me this stability." Rachel: "Have you shared your business plan with them yet?" Amir: "No, I've been avoiding that conversation. Maybe I should show them the market research first?"</t>
+  </si>
+  <si>
+    <t>David Wilson: "Maria, how did those informational interviews go with the companies we identified?" Maria Santos: "Mixed feelings. The conversations were positive, but they kept focusing on my career gap. One interviewer suggested I look at entry-level positions, which was disappointing." David: "I hear your frustration. How did you respond to those comments about the career gap?" Maria: "I used the reframing technique we practiced, highlighting my volunteer work with the PTA treasury and the Salesforce certification I completed last month. But I still felt defensive." David: "That's a natural reaction. What aspects of your experience do you feel aren't being properly valued?" Maria: "My ability to manage complex relationships and projects. Running a household of five, coordinating everyone's schedules, managing renovations - it's all relevant experience, but it's hard to translate." David: "Let's work on that translation. What if we repackaged your recent experience as a family office manager? How would that story sound?" Maria: "That's interesting... It would highlight the budget management and coordination aspects. But would companies take it seriously?"</t>
+  </si>
+  <si>
+    <t>Dr. Jessica Wong: "William, since our last session, have you had that conversation with your manager about leading the new client project?" William Chen: "Yes, but it didn't go as planned. She said I need to work on my 'leadership presence' before taking on a team lead role. I'm not even sure what that means." Jessica: "That's valuable feedback, even if it feels vague. Thinking back to our discussion about cultural differences in workplace communication, what do you think she might be referring to?" William: "Maybe how I tend to defer to senior team members? In our culture, it's respectful to let others speak first, but here it might be seen as lack of confidence." Jessica: "That's a thoughtful observation. How comfortable would you feel experimenting with different communication styles?" William: "I could try speaking up more in meetings, but it feels unnatural. Though I noticed the last project lead, she wasn't necessarily the loudest, but she was very clear in her communications." Jessica: "What if we focused on clarifying your communication rather than changing your style entirely?" William: "That feels more authentic. Could we practice some scenarios?"</t>
+  </si>
+  <si>
+    <t>Sarah Chen: "Marcus, since this is our fifth session, I'd like to explore how you're feeling about the entrepreneurship path we discussed last time." Marcus Thompson: "I've been doing a lot of thinking, Sarah. The small business workshop you recommended was eye-opening. I realized that my experience managing others and handling inventory could translate well into running my own business." Sarah: "That's excellent insight. How do you feel about the financial aspects we discussed?" Marcus: "That's actually what's keeping me up at night. I've started working on the business plan, but the startup costs are daunting. I'm wondering if I should start smaller than we initially discussed." Sarah: "It's good that you're being realistic about the financial implications. Would you like to explore some scaled-down options that could help you test the waters while maintaining your current position?" Marcus: "Yes, definitely. I'm thinking maybe I could start with an online component first, build a customer base, before investing in a physical location." Sarah: "That's a thoughtful approach. Let's map out what that might look like in terms of timeline and resources needed."</t>
+  </si>
+  <si>
+    <t>Dr. James O'Connor: "Welcome back, Priya. How have you progressed with the networking strategies we discussed in our previous session?" Priya Sharma: "The LinkedIn connections have been promising, Dr. O'Connor. I've had three informational interviews with UX designers, but I'm still struggling with imposter syndrome about transitioning from development to design." James: "That's a common feeling during career transitions. Could you tell me about a moment from those interviews that made you feel most confident?" Priya: "When I explained how my coding background helps me understand technical constraints in design. One interviewer mentioned that's actually rare and valuable in UX designers." James: "That's a fantastic unique selling point. How would you feel about leveraging this advantage more explicitly in your applications?" Priya: "I hadn't thought about it that way. But yes, maybe instead of seeing my background as a hindrance, I could position it as a bridge between designers and developers." James: "Exactly. Shall we work on crafting that narrative for your portfolio and interviews?"</t>
+  </si>
+  <si>
+    <t>Maria Rodriguez: "David, you mentioned in our last session that you were feeling conflicted about leaving research. Have you had any new insights?" David Chen: "Yes, Maria. I've been shadowing the product management team as you suggested. It's fascinating seeing how they bridge the gap between research and market needs." Maria: "What aspects of the role resonated most with you?" David: "The strategic thinking and the way they need to understand both the science and the business side. But I'm concerned about taking such a big pay cut as a junior product manager." Maria: "That's a valid concern. Would you be interested in exploring some hybrid roles that could serve as stepping stones? Some companies have technical product manager positions specifically for people with your background." David: "I hadn't heard of those. That sounds like it could be a better fit. Would my research experience be valued there?" Maria: "Absolutely. Let's look at some job descriptions and identify where your experience aligns."</t>
+  </si>
+  <si>
+    <t>Dr. Elizabeth Foster: "Mohammed, since our last session, have you had the conversation with your current employer about role expansion?" Mohammed Al-Rahman: "Yes, Dr. Foster. It was challenging but productive. They're open to me taking on more strategic projects, but they want me to prove myself first." Elizabeth: "How do you feel about that response?" Mohammed: "Mixed feelings. I appreciate the opportunity, but I'm concerned about taking on extra work without immediate recognition or compensation." Elizabeth: "That's understandable. What would make this opportunity feel more worthwhile to you?" Mohammed: "I suppose if we had a clear timeline and defined milestones for advancement. Right now, it feels open-ended." Elizabeth: "Would you like to work on creating a proposal that outlines these milestones? It could help structure your conversation about expectations."</t>
+  </si>
+  <si>
+    <t>Dr. Michael Wong: "Emma, last time we discussed your interest in art direction. How did the informational interviews go?" Emma Wilson: "They were revealing, Dr. Wong. I realized that the role involves much more team management than I expected. I'm not sure if I'm ready for that level of responsibility." Michael: "What aspects of team management feel most challenging to you?" Emma: "Mainly the conflict resolution and having difficult conversations. I tend to avoid confrontation." Michael: "That's a common concern. Would you be interested in exploring some management training or mentorship opportunities before making the transition?" Emma: "Yes, that might help. Could we also look at smaller steps I could take in my current role to build these skills?" Michael: "Absolutely. Let's identify opportunities in your current projects where you could practice leadership skills in a lower-stakes environment."</t>
+  </si>
+  <si>
+    <t>Dr. Sarah Chen: "Marcus, you mentioned over the past sessions your strong interest in executive leadership. How did that conversation with your supervisor about development programs go?" Marcus Thompson: "Actually, yes. She was surprisingly supportive and said the company is open to investing in my growth. But I'm still feeling some hesitation about the time commitment of an MBA." Dr. Chen: "It's completely understandable to feel that way, especially with your family commitments. What specific concerns about the time commitment are weighing on you?" Marcus: "Balancing work, studies, and being present for my young kids. It feels like something will have to give." Dr. Chen: "That's a valid concern. Let's explore some alternative development paths that might be less time-intensive than a full MBA but still align with your leadership goals." Marcus: "I saw a few executive certificate programs online. Are those as valuable as a degree?" Dr. Chen: "They can be, depending on the program and your specific goals. What attracted you to those certificate programs?" Marcus: "They seem more focused and shorter in duration. Maybe I could start there?" Dr. Chen: "That's a thoughtful approach. Shall we analyze some of those certificate programs and see how they fit into your overall career plan and lifestyle?"</t>
+  </si>
+  <si>
+    <t>James O'Connor: "Sofia, since our last meeting, how have you been progressing on identifying those social impact tech roles?" Sofia Rodriguez: "I've found a few interesting ones, but I'm struggling with writing the cover letters. My resume highlights my technical skills, but I'm not sure how to convey my passion for social impact authentically." James: "That's a key challenge in transitioning fields. Remember our discussion about your personal connection to accessibility software? How does that story make you feel?" Sofia: "It feels very personal and real. Maybe I can share that story?" James: "Absolutely. Sharing your personal 'why' can be incredibly powerful in demonstrating your motivation and authenticity to potential employers in the social impact space." Sofia: "But how do I make sure it sounds professional and not just like a personal anecdote?" James: "We can work on framing that narrative to connect your personal motivation with your professional skills and the organization's mission. Shall we draft a paragraph together that you could use in your cover letters?" Sofia: "Yes, that would be really helpful."</t>
+  </si>
+  <si>
+    <t>Dr. Amelia Thompson: "Raj, you've consistently mentioned your high stress levels in investment banking. How has the process of identifying alternative career paths been going?" Raj Patel: "It's overwhelming, Dr. Thompson. Every potential option I look at seems to involve a significant pay cut, which feels impossible with my financial obligations." Amelia: "I hear you. The financial reality is a significant barrier. However, you also mentioned your health is suffering. How do you reconcile those two pressures?" Raj: "That's the constant battle in my head. My family needs the stability, but they also need me to be healthy and present. My wife suggested I look into corporate finance roles outside of banking." Amelia: "That's a thoughtful suggestion from your wife. Have you explored what corporate finance roles might look like in industries with a different culture?" Raj: "Not in detail. I assumed they were all similar to banking. But maybe there are options with better work-life balance?" Amelia: "There absolutely can be. Shall we research corporate finance roles in industries known for better work-life integration, like pharmaceuticals or technology?" Raj: "Yes, let's do that. I need to see what other options exist."</t>
+  </si>
+  <si>
+    <t>Dr. Michael Wong: "Emma, you mentioned finding inspiration in sustainable business marketing. How has that research progressed?" Emma Davidson: "It's exciting! I've identified several companies in that space, and my current marketing skills seem highly transferable. But I'm still wrestling with the fear of failure if I start my own agency." Michael: "That fear is a very real part of the entrepreneurial journey. How does acknowledging that fear feel?" Emma: "Terrifying, but also... freeing? Like acknowledging it makes it less powerful. But it's still there." Michael: "It's natural for fear to be present when taking a significant leap. Let's identify some specific strategies to mitigate the risk. What are some small steps you could take to test the waters?" Emma: "I've been thinking about taking on a small freelance project in sustainable marketing first. Just to see how it goes." Michael: "That's an excellent idea. It allows you to build experience and confidence with lower risk. Shall we look at some platforms or networks where you might find those initial projects?" Emma: "Yes, let's do that."</t>
+  </si>
+  <si>
+    <t>Maria Santos: "David, you've narrowed down your interest to product development. How have those preliminary conversations with product managers been?" David Chen: "They've been insightful. They confirmed my technical background is valuable, but I need to learn the commercial aspects. I've been looking at online courses in product management fundamentals." Maria: "That's a concrete step. How do you feel about the time and cost commitment of those courses?" David: "They seem manageable, but I'm wondering if just courses are enough. Do I need a formal degree?" Maria: "Not necessarily. Many in product development value practical experience and demonstrable skills over formal degrees, especially when transitioning from a related technical field. Have you considered seeking a mentor in the product development field?" David: "I hadn't thought of that. Would they be willing to help?" Maria: "Many professionals are happy to share their experience. A mentor could provide guidance on relevant skills, industry insights, and even networking opportunities. Shall we explore strategies for finding a suitable mentor?" David: "Yes, that sounds like a great idea."</t>
+  </si>
+  <si>
+    <t>Maria Rodriguez: "James, last time we discussed your interest in transitioning to AI development. Have you had a chance to explore those online courses we talked about?" James Chen: "Yes, I actually completed two courses on machine learning. But I'm feeling conflicted. The financial sector pays well, and I'm not sure if switching specialties is worth the risk." Maria: "That's a valid concern. Could you tell me more about what excites you about AI development versus your current role?" James: "In my current position, I'm maintaining legacy systems. With AI, I'd be building something new, contributing to cutting-edge technology. But I've been at my company for six years, and I have a good reputation there." Maria: "Let's explore this tension between stability and growth. What would need to be true for you to feel confident making this transition?" James: "I guess... knowing that my skills would be valuable enough to justify starting over. And having a clear path to get there." Maria: "Those are excellent points. Shall we work on mapping out what that path might look like, including potential roles that could bridge your current experience with AI development?"</t>
+  </si>
+  <si>
+    <t>Dr. David Thompson: "Sarah, since our last meeting, how have you been feeling about the business plan we started developing?" Sarah Mitchell: "Actually, I've been doing a lot of thinking. The idea of building an agency is exciting, but I'm terrified of taking on employees and the responsibility that comes with it." David: "That's a significant shift from our previous discussions. What's brought these concerns to the surface?" Sarah: "I took on two new clients last month, and just managing their expectations has been overwhelming. I'm wondering if I'm cut out for bigger responsibilities." David: "Managing growth can indeed be challenging. But remember how you felt when you first started freelancing? Those skills you developed could translate to team management." Sarah: "That's true. I am much more confident now than when I started. But this feels different – it's not just my reputation at stake anymore." David: "Let's break this down into smaller pieces. What specific aspects of managing others concern you most?"</t>
+  </si>
+  <si>
+    <t>Dr. Amara Okafor: "Michael, you mentioned wanting to discuss the entrepreneurship opportunity you encountered. How are you feeling about it now?" Michael Adebayo: "I've been losing sleep over it, honestly. The startup's proposition is compelling – they want me to join as COO. But leaving a twenty-year banking career..." Amara: "What aspects of the opportunity align with the goals we've been discussing?" Michael: "It's in financial technology – combining my expertise with innovation. And I'd have equity, real ownership. But the banking sector is what I know. My family depends on my income." Amara: "You've mentioned wanting to create lasting impact in Nigeria's financial sector. How does each path – staying in banking versus joining the startup – align with that vision?" Michael: "The startup could potentially reach more unbanked people... but banks have the infrastructure and trust already built." Amara: "Let's explore how these different paths might help you achieve your long-term goals."</t>
+  </si>
+  <si>
+    <t>Emma Wilson: "Welcome back, Priya. How did the informational interviews with the science communication professionals go?" Priya Sharma: "They were eye-opening. I loved hearing about their work, but I'm worried about the salary reduction. Science journalism pays significantly less than my current role." Emma: "That's important to consider. How does this align with what you've identified as your core values?" Priya: "I keep thinking about the impact I could have, making science accessible to everyone. But I have a mortgage, and I've worked so hard for my current position." Emma: "Let's explore some options that might bridge these worlds. Have you considered roles that combine scientific expertise with communication skills?" Priya: "Like what? I feel stuck between two very different paths." Emma: "There are positions in pharmaceutical companies focusing on medical communication or scientific affairs. Would you like to explore those as potential transition roles?"</t>
+  </si>
+  <si>
+    <t>Jonathan Hayes: "Maya, since our last session, have you had the chance to shadow the educational technology coordinator?" Maya Williams: "Yes, and it was fascinating! But I'm struggling with the idea of leaving the classroom. My students mean everything to me." Jonathan: "Tell me more about what you observed in the EdTech role that excited you." Maya: "I could potentially impact thousands of students by helping teachers integrate technology effectively. But I'm worried about losing that direct connection with students." Jonathan: "How does this role align with what you've described as your mission in education?" Maya: "I want to make education more accessible and engaging. Technology could do that on a larger scale, but there's something special about seeing a student's face light up when they understand something." Jonathan: "What if we explored ways to maintain some classroom involvement while transitioning into educational technology?"</t>
+  </si>
+  <si>
+    <t>Dr. Sarah Chen: "Marcus, you showed strong scores in both strategic thinking and emotional intelligence. Have you had any chances to apply the communication strategies we talked about?" Marcus Thompson: "Actually, yes. I implemented that feedback technique with my team, and it's been transformative. But I'm still struggling with the idea of pursuing an MBA. The cost and time commitment seem daunting." Dr. Chen: "I understand those concerns. Let's break this down. You mentioned your company has a tuition reimbursement program?" Marcus: "They do, but it only covers 60%. I've been looking at part-time programs, but I'm worried about maintaining work-life balance, especially with my young family." Dr. Chen: "That's a valid concern. Based on our previous discussions about your financial planning, shall we explore some specific scenarios? We could map out a three-year plan that includes both professional development and family time."</t>
+  </si>
+  <si>
+    <t>James O'Connor: "Welcome back, Priya. You mentioned in our last session that you'd start researching tech leadership roles. How did that go?" Priya Patel: "It was eye-opening. I realized that what I thought I wanted – a traditional tech lead role – might not actually align with my interests. I'm more drawn to the product side of things." James: "That's a significant insight. Can you tell me more about what attracted you to the product side?" Priya: "I love solving problems, but I'm finding that I'm more excited about understanding user needs and shaping product direction than diving deep into code. Is it crazy to consider a career pivot after investing so much in my technical skills?" James: "Not at all. Your technical background could actually be a strong advantage in product management. Looking back at your values assessment from our third session, this aligns well with your desire to have a more direct impact on users." Priya: "That's true. I've been worried about letting go of my identity as a developer, though."</t>
+  </si>
+  <si>
+    <t>Dr. Maria Rodriguez: "David, since our last session, have you had the chance to reflect on the career satisfaction exercise we did?" David Kim: "Yes, and it really highlighted something I've been avoiding. I'm good at my job, but I'm not fulfilled. The creative agency I've been moonlighting for – that work energizes me in a way my current role doesn't." Maria: "That's valuable self-awareness. You mentioned feeling 'stuck' in our previous sessions. How does this realization affect that feeling?" David: "It's both liberating and terrifying. I have a mortgage, two kids in private school... The agency work pays less than half my current salary." Maria: "Let's explore this tension between financial security and professional fulfillment. Remember the values hierarchy we created? Where did financial stability rank compared to creative satisfaction?" David: "They were actually pretty close. But maybe there's a way to transition gradually? I've been thinking about proposing a part-time arrangement with my current company."</t>
+  </si>
+  <si>
+    <t>Dr. Michael Wong: "Emma, you mentioned wanting to discuss the outcome of your informational interviews with non-profits?" Emma Mitchell: "Yes, it was quite different from what I expected. The environmental non-profits I spoke with are struggling with funding, but the corporate sustainability roles we discussed seem more promising." Michael: "Interesting. How does this align with your goal of making a bigger environmental impact?" Emma: "That's what surprised me. The sustainability manager at that mining company explained how she's actually implementing large-scale changes. It challenges my preconception that corporate roles wouldn't be as meaningful." Michael: "This connects to our discussion about impact versus perception. Would you like to revisit the career values exercise with this new insight?" Emma: "Definitely. I'm also wondering if my consulting background might be valuable in corporate sustainability. The skill set seems transferable."</t>
+  </si>
+  <si>
+    <t>Dr. Alex Foster: "Sophie, last time we talked about your interest in educational technology. Have you had a chance to explore the online courses we discussed?" Sophie Williams: "Yes, I completed the introductory course on instructional design. It's fascinating how much education is changing. But I'm concerned about starting over at my age." Alex: "Let's unpack that concern. What specifically feels risky about this transition?" Sophie: "Well, I've been teaching for twenty years. I have seniority, respect. In ed-tech, I'd be a complete novice. But I keep thinking about how much I enjoyed creating digital resources during lockdown." Alex: "Your experience with digital teaching during the pandemic was a crucial insight in our previous sessions. How might your years of classroom experience actually benefit you in an ed-tech role?" Sophie: "I suppose I understand the user perspective – both teacher and student needs. That's actually valuable, isn't it?"</t>
+  </si>
+  <si>
+    <t>Sarah Chen: "Marcus, I've been thinking a lot about what we discussed last time regarding the tech industry. I did that informational interview you suggested with a Product Manager at Salesforce." Marcus Thompson: "That's excellent initiative, Marcus. What insights did you gain from that conversation?" Sarah: "It was eye-opening. The role seems to align well with my experience managing teams and projects. But I'm still concerned about the transition. My retail background feels... inadequate." Marcus: "Let's unpack that. You mentioned managing cross-functional teams in your current role. How does that compare to what you learned about product management?" Sarah: "Well, I coordinate between sales, inventory, and customer service teams now. The PM role seems similar - working with developers, designers, and stakeholders. But the technical aspects..." Marcus: "Remember how we mapped your transferable skills? Your experience in data-driven decision making and stakeholder management is valuable. What specific technical areas feel most challenging?" Sarah: "Mainly the software development process. I understand the business side, but I need to learn how engineering teams work." Marcus: "That's a clear, actionable area for development. Have you considered the part-time Product Management certification program we discussed? It could bridge that knowledge gap while you're still working."</t>
+  </si>
+  <si>
+    <t>David O'Connor: "Emma, I've started the creative writing workshop you recommended. It's made me realize how much I miss being creative professionally." Emma Richardson: "That's wonderful to hear, Emma. How has this realization affected your thoughts about transitioning into content creation?" David: "I actually brought some samples of my work. I've been writing blog posts about educational topics, combining my teaching experience with my writing skills. But I'm worried about financial stability." Emma: "That's a valid concern. Looking at the research you did on content strategist salaries, what are your thoughts on the income potential compared to teaching?" David: "The range is quite wide. But what surprised me was learning about technical writing. It seems to offer better stability while still using my writing skills." Emma: "Yes, and your experience explaining complex concepts to students could be particularly valuable there. Have you looked into any of the technical writing certificates we discussed?" David: "I have. Found one that's fully online, which works with my teaching schedule. But I'm wondering if I should start with freelance work first to test the waters?" Emma: "That's a thoughtful approach. It would let you build a portfolio while maintaining your current position. Shall we look at some platforms where you could find educational content projects?"</t>
+  </si>
+  <si>
+    <t>Maya Patel: "James, The business plan we worked on last session really helped me visualize the consulting firm idea. I've been refining the niche market focus." James Wilson: "That's great progress, James. You mentioned wanting to focus on sustainability marketing. Have you validated this need in the market?" Maya: "Yes, I've actually spoken with three potential clients in my network. They're all struggling with authentic sustainability communication. But I'm wondering if I'm too old to start something new." James: "Age can actually be an advantage in consulting. What specific aspects of your experience would be valuable to these clients?" Maya: "Well, I've led several successful sustainability campaigns, and I understand the challenges of avoiding greenwashing. I also have a strong network in the industry." James: "Those are significant assets. Looking at the financial projections we developed, what timeline feels realistic for transitioning from your current role?" Maya: "I'm thinking of starting part-time while maintaining my current job. Maybe take on one or two clients first?" James: "That's a prudent approach. Shall we work on structuring your time to manage both effectively?"</t>
+  </si>
+  <si>
+    <t>Michael Rodriguez: "Lisa, I've applied to several remote positions like we discussed, and I have two interviews scheduled. But I'm worried about standing out in virtual interviews." Lisa Chen: "That's excellent progress, Lisa. Which aspects of virtual interviewing concern you most?" Michael: "Mainly demonstrating my collaboration skills. In the office, I can show how I work with others naturally. Remote feels different." Lisa: "Let's analyze your remote collaboration experience during the pandemic. What tools and strategies did you find most effective?" Michael: "I actually developed a documentation system that improved our team's async communication. And I led several virtual pair programming sessions." Lisa: "Those are concrete examples of remote leadership. Have you prepared to discuss how these experiences shaped your remote work philosophy?" Michael: "I have some ideas, but I could use help articulating them better. Especially how they align with the companies I'm interviewing with." Lisa: "Good insight. Shall we practice some interview responses that highlight these experiences?"</t>
+  </si>
+  <si>
+    <t>Rachel Goldman: "Sophia, I've been tracking my energy levels like you suggested. It's clear that the 80-hour weeks are unsustainable, especially now that I'm pregnant." Sophia Martinez: "Thank you for doing that exercise, Sophia. How has this data affected your thoughts about the transition we've been discussing?" Rachel: "I've been researching corporate finance roles in tech companies. The compensation is lower, but the hours seem more reasonable. I'm just worried about being perceived as not ambitious enough." Sophia: "That's a common concern. How do you define ambition for yourself, separate from external expectations?" Rachel: "I want to continue growing professionally, but not at the expense of my health and family. Maybe success can look different than I thought." Sophia: "That's a powerful realization. Looking at the tech companies you've researched, which ones align with this revised definition of success?" Rachel: "There's one that particularly interests me. They have a strong parental leave policy and actively promote work-life integration. But it would be a step down in title." Sophia: "Let's explore how this role might offer different kinds of growth opportunities. What skills could you develop there?"</t>
+  </si>
+  <si>
+    <t>Counselor: "Michael, this is our fifth session, and I'm noticing a consistent theme in our discussions about your career aspirations. Can you update me on how you're feeling about your current professional trajectory?" Michael: "I'm increasingly uncertain. While I've been successful as a software engineer, I'm experiencing a sense of stagnation. The technical challenges aren't stimulating me like they used to. I'm contemplating whether I should pivot into technology management or explore an entirely different career path." Counselor: "That's a significant realization. Let's unpack that. When you say 'stagnation,' what specific experiences are triggering this sentiment?" Michael: "In my current role, I'm primarily maintaining legacy systems. The innovation I was passionate about during my early career seems distant. I'm more interested in strategic technology implementation and how technological solutions can drive organizational transformation." Counselor: "Your insight suggests you're ready for a more holistic technology role. Have you considered positions like Technical Product Manager or Technology Strategy Consultant?" [Continued dialogue exploring Michael's potential career transition strategies...]</t>
+  </si>
+  <si>
+    <t>Counselor: "Priya, we've been working together for several sessions now. Today, I'd like us to map out a clear progression plan for your healthcare career. What are your current thoughts?" Priya: "I'm feeling conflicted. I love clinical nursing, but I'm also aware that to grow, I might need to transition into leadership or specialized roles. The emotional intensity of direct patient care is becoming challenging after a decade." Counselor: "That's a common experience among healthcare professionals. Your recognition of needing a strategic career move demonstrates significant self-awareness. What specific areas intrigue you?" Priya: "I'm interested in healthcare administration, potentially focusing on quality improvement and patient safety protocols. I've completed additional certifications in healthcare management, but I'm uncertain how to leverage them effectively." Counselor: "Those certifications are valuable. Let's discuss how we can position your clinical expertise as a unique strength in administrative roles." [Continued dialogue exploring Priya's potential career advancement strategies...]</t>
+  </si>
+  <si>
+    <t>Counselor: "Marco, our previous discussions have centered on balancing your creative passion with sustainable income. How have your perspectives evolved?" Marco: "I'm realizing that pure freelancing isn't sustainable long-term. The inconsistent income and constant client hunting are draining my creative energy. I want stability without losing my artistic integrity." Counselor: "That's a nuanced challenge many creative professionals face. Have you considered hybrid career models that combine traditional employment with creative freedom?" Marco: "Like in-house design roles with flexible arrangements? Or perhaps working with creative agencies that value individual artistic expression?" Counselor: "Exactly. We'll explore roles that provide structured environments while allowing significant creative autonomy." [Continued dialogue exploring Marco's career sustainability strategies...]</t>
+  </si>
+  <si>
+    <t>Counselor: "Elizabeth, our conversations have revealed your desire to expand your global business perspective. What progress have you made in understanding your international career potential?" Elizabeth: "I'm strategically positioning myself for roles that leverage my cross-cultural marketing expertise. I'm particularly interested in organizations with strong Pan-African and global expansion strategies." Counselor: "Your targeted approach is commendable. How are you developing the necessary networking and skill enhancement to support these aspirations?" Elizabeth: "I've been connecting with global business networks, pursuing additional language certifications, and attending international marketing conferences." Counselor: "Those are excellent proactive strategies. Let's discuss how we can translate these efforts into concrete career opportunities." [Continued dialogue exploring Elizabeth's international career development...]</t>
+  </si>
+  <si>
+    <t>Counselor: "Sarah, our previous sessions have explored your growing interest in educational technology and systemic change. What insights have emerged?" Sarah: "I'm passionate about transforming educational methodologies. Teaching in the classroom feels limiting. I want to influence educational policy and develop innovative learning technologies." Counselor: "Your desire to create broader educational impact is clear. What specific steps are you considering to transition from direct teaching to a more systemic role?" Sarah: "I'm exploring positions in educational technology firms, curriculum development organizations, and educational consulting agencies. I want to apply my teaching expertise to drive meaningful change." Counselor: "Those are promising directions. Let's develop a strategic plan to position your extensive teaching experience as a unique asset in these emerging fields." [Continued dialogue exploring Sarah's potential career transformation...]</t>
+  </si>
+  <si>
+    <t>Dr. Sarah Chen: "Marcus, over our past sessions, we've explored your interest in transitioning from retail to corporate training. How did those informational interviews go?" Marcus Thompson: "They were eye-opening, Dr. Chen. I spoke with three training managers like you suggested. They all emphasized the importance of getting some formal certification in instructional design." Sarah: "That aligns with our previous discussions about leveraging your people management experience. What aspects of those conversations stood out to you?" Marcus: "Well, they all mentioned how my retail experience could be valuable – especially in training customer service teams. But I'm concerned about the salary drop during the transition period." Sarah: "That's a valid concern. Let's break down some numbers. Based on your current savings and the timeline we discussed last week, how would you feel about exploring part-time certification programs while maintaining your current role?" Marcus: "I've actually been researching that. Found a six-month online program that would allow me to keep working. But I'm wondering if that's enough to make me competitive." Sarah: "The market research we did shows that combining your management experience with a recognized certification would position you well. Should we map out a 12-month transition plan with specific milestones?"</t>
+  </si>
+  <si>
+    <t>James O'Connor: "Welcome back, Sophia. You mentioned in your email that you've been reflecting on our discussion about the NGO sector. Would you like to share your thoughts?" Sophia Patel: "Yes, Mr. O'Connor. I've realized that while I love environmental work, I'm feeling limited by purely consulting roles. The NGO job descriptions you shared really resonated with me." James: "I notice you're lighting up just talking about it. Could you elaborate on what specifically attracted you about those roles?" Sophia: "The combination of field work and policy advocacy. In my current role, I write reports that often just sit on shelves. I want to drive actual change." James: "That connects with what you shared in our first session about wanting more meaningful impact. Have you reached out to any of the organizations we identified?" Sophia: "Actually, yes. I had a coffee chat with someone from GreenFuture Ireland. They mentioned they're launching a new initiative next quarter." James: "Excellent proactive step. Given your project management experience, how do you see yourself contributing to such initiatives?"</t>
+  </si>
+  <si>
+    <t>Maria Rodriguez: "David, since our last session, have you had the chance to explore the tech leadership roles we discussed?" David Chen: "Yes, and I'm feeling conflicted, Maria. The senior developer position offers more money, but the team lead role at the smaller company seems more aligned with where I want to go." Maria: "Let's unpack that. In our previous sessions, you emphasized wanting to mentor junior developers. How does that factor into your decision?" David: "That's exactly what's pulling me toward the leadership role. But I'm worried about losing touch with coding if I focus too much on management." Maria: "I understand that concern. Looking at the career paths we mapped out, have you considered how you might maintain technical skills while developing leadership capabilities?" David: "I've been thinking about that hybrid role model you mentioned. Maybe I could negotiate a technical team lead position that allows for both?" Maria: "That's a thoughtful approach. Should we role-play some negotiation scenarios to prepare for those conversations?"</t>
+  </si>
+  <si>
+    <t>Michael Bennett: "Emma, you mentioned making some decisions about the freelance transition we've been discussing. How are you feeling about that?" Emma Watson: "More confident, Dr. Bennett. I've secured two potential long-term clients like we discussed, and I've been working on that business plan template you shared." Michael: "That's substantial progress. How does this align with the financial goals we outlined in our third session?" Emma: "The projections look promising, but I'm nervous about healthcare and retirement planning as a freelancer." Michael: "Those are crucial considerations. Have you had a chance to review the resource list about freelancer benefits and insurance options?" Emma: "Yes, I've even contacted an insurance broker. But I'm wondering if I should maintain a part-time agency role during the transition." Michael: "That's a strategic approach to managing risk. Let's explore how that might affect your availability for building your client base."</t>
+  </si>
+  <si>
+    <t>Aisha Patel: "Thomas, how has the past week been since we discussed potential career pivots within the hospitality industry?" Thomas Schmidt: "Mixed feelings, Ms. Patel. The hotel operations role looks promising, but I'm concerned about starting over after 20 years in restaurants." Aisha: "That's understandable. Looking at your skills assessment from our previous sessions, which aspects of hotel operations align with your experience?" Thomas: "Well, the staff management and customer service elements feel familiar. But the scale is different, and the corporate structure is new to me." Aisha: "You mentioned enjoying systems optimization in your current role. How might that translate to hotel operations?" Thomas: "That's interesting – I hadn't thought about it that way. I did streamline our restaurant's booking and inventory systems." Aisha: "Exactly. Should we focus on identifying more of these transferable skills to build your confidence in making this transition?"</t>
+  </si>
+  <si>
+    <t>Dr. Sharma: Michael, we’ve discussed your skills and interests over the past few sessions. How do you feel about transitioning into a project management role, as we explored last time? Michael: I’ve been thinking about it, but I’m still unsure. My background is in sales, and I’m not sure if I have the technical skills for project management. Dr. Sharma: That’s a valid concern. However, your experience in sales has given you strong communication and negotiation skills, which are crucial for project management. Have you considered taking a certification course, like PMP, to bridge the gap? Michael: I’ve heard of PMP, but it seems time-consuming and expensive. Do you think it’s worth it? Dr. Sharma: It’s an investment, but it can significantly boost your employability. Many professionals in your position have found it transformative. Alternatively, you could start with smaller projects in your current network to gain experience. Michael: That makes sense. I’ll look into it. I’m just worried about my age—I’m 34, and I feel like I’m starting over. Dr. Sharma: Age is just a number, Michael. Many people pivot careers later in life. What’s important is that you’re taking proactive steps toward a fulfilling career. Let’s create a step-by-step plan to get you there.</t>
+  </si>
+  <si>
+    <t>Mr. Carter: Maria, last time we talked about your desire to work full-time in a creative agency. Have you made any progress? Maria: I’ve applied to a few places, but I haven’t heard back. I’m starting to feel discouraged. Mr. Carter: Job searching can be tough, but persistence pays off. Let’s review your portfolio and resume. Are they tailored to the roles you’re applying for? Maria: I think so, but maybe they’re not standing out enough. Mr. Carter: Consider adding more recent projects and showcasing your versatility. Also, networking is key in the creative industry. Have you attended any design events or reached out to professionals on LinkedIn? Maria: Not really. I’m shy about reaching out to people I don’t know. Mr. Carter: I understand, but networking doesn’t have to be intimidating. Start by commenting on posts or joining online design communities. Building relationships can open doors. Maria: That’s a good idea. I’ll give it a try. I just want to feel more stable in my career. Mr. Carter: Stability will come with time and effort. Let’s set a goal for you to connect with at least three professionals this week.</t>
+  </si>
+  <si>
+    <t>Ms. Zhang: Ahmed, last session we discussed your interest in moving into a leadership role. How do you feel about that now? Ahmed: I’m still interested, but I’m not sure if I’m ready. I’ve only been in my current role for two years. Ms. Zhang: Leadership isn’t just about years of experience; it’s about mindset and skills. Have you taken on any leadership tasks at work, even informally? Ahmed: I’ve led a few small projects, but nothing major. Ms. Zhang: That’s a great start. Leadership often begins with small steps. Have you considered asking your manager for more responsibilities or mentoring opportunities? Ahmed: I haven’t, but I’m worried about being seen as too ambitious. Ms. Zhang: Ambition is a good thing when paired with humility and a willingness to learn. Frame your request as a desire to grow and contribute more to the team. Ahmed: That makes sense. I’ll talk to my manager next week. Ms. Zhang: Excellent. Let’s also explore leadership training programs that could help you build confidence and skills.</t>
+  </si>
+  <si>
+    <t>Dr. Johnson: Fatima, last time we discussed your interest in transitioning to a policy-making role. Have you made any progress? Fatima: I’ve been researching roles, but they all require experience I don’t have. Dr. Johnson: Policy roles can be competitive, but your public health background is a strong foundation. Have you considered volunteering or interning to gain relevant experience? Fatima: I hadn’t thought of that. Do you think it’s worth it, even though I already have a Master’s? Dr. Johnson: Absolutely. Volunteering can help you build connections and demonstrate your commitment to the field. It’s also a way to test if policy work is the right fit for you. Fatima: That’s a good point. I’ll look into opportunities. I just feel like I’m behind compared to others my age. Dr. Johnson: Everyone’s career path is different. Focus on your unique strengths and the value you bring. Let’s create a plan to help you gain the experience you need.</t>
+  </si>
+  <si>
+    <t>Mr. Kim: Jessica, we’ve talked about your desire to move into corporate communications. How do you feel about that goal now? Jessica: I’m still interested, but I’m not sure how to make the leap from retail management. Mr. Kim: Your management experience is valuable—it shows leadership and organizational skills. Have you considered highlighting transferable skills in your resume and cover letters? Jessica: I’ve tried, but I’m not sure if I’m doing it effectively. Mr. Kim: Let’s work on reframing your experience. For example, managing a team in retail involves communication, problem-solving, and stakeholder engagement—all relevant to corporate communications. Jessica: That’s a good way to look at it. I’m just worried about starting at a lower level than I am now. Mr. Kim: Transitioning careers often involves some trade-offs, but it’s about long-term growth. Let’s focus on finding roles that offer growth potential and align with your goals. Jessica: That sounds good. I’m ready to take the next step. Mr. Kim: Great. Let’s start by updating your resume and identifying target companies.</t>
+  </si>
+  <si>
+    <t>Dr. Thompson: "James, we’ve discussed your career goals over the past few sessions. How do you feel about your progress in identifying your next steps?" James: "I’ve been reflecting on your advice about networking, and I’ve started attending industry events. But I’m still unsure if I should pursue a leadership role or specialize further in machine learning." Dr. Thompson: "That’s a common dilemma. Let’s weigh the pros and cons. Leadership roles often require soft skills like communication and team management. Do you feel confident in those areas?" James: "I’m comfortable with technical communication, but managing people is new to me. I’m worried I might not enjoy it." Dr. Thompson: "That’s valid. Specializing in machine learning could align more with your strengths. Have you considered roles like a senior data scientist or AI researcher?" James: "Yes, but I’m concerned about the rapid changes in the field. I don’t want to become obsolete." Dr. Thompson: "Continuous learning is key. Perhaps we can explore certifications or advanced courses to keep you competitive. Let’s also look at companies that value innovation and offer growth opportunities." James: "That sounds like a plan. I’ll research those options and report back next time."</t>
+  </si>
+  <si>
+    <t>Ms. Mehta: "Maria, last time we talked about transitioning from retail management to digital marketing. How has your job search been going?" Maria: "I’ve applied to a few positions, but I’m not getting many responses. I think my lack of digital experience is holding me back." Ms. Mehta: "That’s a common challenge. Have you considered taking online courses in SEO or social media marketing to bridge that gap?" Maria: "I’ve started a course on Google Analytics, but I’m not sure if it’s enough." Ms. Mehta: "Every step counts. Let’s also highlight your transferable skills, like team leadership and customer engagement, in your resume. Have you thought about freelancing to gain experience?" Maria: "Freelancing sounds intimidating, but it might be a good way to build a portfolio." Ms. Mehta: "Exactly. Start small, and use platforms like Upwork or Fiverr to find projects. This will also help you network with potential employers." Maria: "I’ll give it a try. Thanks for the encouragement!"</t>
+  </si>
+  <si>
+    <t>Mr. Kim: "Aisha, we’ve been exploring your desire to shift from banking to entrepreneurship. How do you feel about the risks involved?" Aisha: "I’m excited but nervous. I’ve saved some money, but I’m not sure if it’s enough to start my own business." Mr. Kim: "Starting small can mitigate risks. Have you considered a side hustle while keeping your current job?" Aisha: "That’s a good idea. I’ve thought about offering financial consulting services on the side." Mr. Kim: "That’s a great start. It allows you to test the waters without fully committing. Have you identified your target market?" Aisha: "I’m thinking of focusing on small business owners who need help with financial planning." Mr. Kim: "Excellent. Let’s create a business plan and set short-term goals. This will help you stay focused and measure progress." Aisha: "I’ll work on that and share it with you next time."</t>
+  </si>
+  <si>
+    <t>Dr. Zhang: "Carlos, we’ve discussed your interest in advancing your IT career. Have you made any progress toward earning additional certifications?" Carlos: "I’ve started studying for the CompTIA Security+ certification, but it’s challenging to balance with work." Dr. Zhang: "That’s understandable. Have you considered discussing flexible hours with your employer to dedicate more time to studying?" Carlos: "I haven’t, but it’s worth a try. I’m also worried about the cost of certifications." Dr. Zhang: "Many employers offer tuition reimbursement. Let’s explore if your company has such a program. Additionally, some certifications offer payment plans." Carlos: "That’s good to know. I’ll look into those options." Dr. Zhang: "Great. Let’s also identify roles that align with your certification goals, like cybersecurity analyst or network administrator." Carlos: "I’ll research those roles and update you next session."</t>
+  </si>
+  <si>
+    <t>Mr. Hassan: "Sophie, we’ve been discussing your desire to transition from freelance writing to a full-time editorial role. How has your job search been?" Sophie: "I’ve applied to a few positions, but I’m not getting interviews. I think my lack of formal editorial experience is the issue." Mr. Hassan: "That’s a common hurdle. Have you considered volunteering for online publications to build your portfolio?" Sophie: "I haven’t, but that’s a good idea. I could also reach out to my network for referrals." Mr. Hassan: "Networking is crucial. Let’s also tailor your resume to highlight your editing skills and any relevant projects." Sophie: "I’ll work on that. I’m also thinking of taking a course in copyediting to strengthen my credentials." Mr. Hassan: "That’s a proactive step. Let’s set a timeline for these actions and review your progress next time." Sophie: "Sounds like a plan. Thanks, Mr. Hassan!"</t>
+  </si>
+  <si>
+    <t>Dr. Carter: Michael, it’s great to see you again. Last time, we discussed your interest in digital marketing. How have you been exploring that since our last session? Michael: Thanks, Dr. Carter. I’ve been taking an online course in SEO and content marketing. I’m enjoying it, but I’m still unsure if this is the right path for me. Dr. Carter: That’s a great start. What specifically makes you doubt this path? Michael: I worry about job stability. I’ve heard the industry is competitive, and I don’t want to end up in another dead-end job. Dr. Carter: Valid concern. Let’s look at the data—digital marketing is growing, and specialization can make you stand out. Have you considered combining your marketing skills with another field, like data analysis? Michael: That’s an interesting idea. I’ve always been good with numbers. Do you think that would make me more employable? Dr. Carter: Absolutely. Many companies value hybrid skills. Let’s create a plan to build your expertise in both areas.</t>
+  </si>
+  <si>
+    <t>Mr. Patel: Sarah, welcome back. Last time, you mentioned feeling stuck in your teaching role. Have you had any new thoughts about your career direction? Sarah: Yes, I’ve been thinking about moving into educational consultancy or curriculum development. I love education but want a broader impact. Mr. Patel: That’s a natural progression. What steps have you taken to explore these options? Sarah: I’ve been networking with professionals in those fields and researching qualifications. But I’m worried about leaving the stability of teaching. Mr. Patel: Change is always daunting, but your experience is a strong foundation. Have you considered part-time consultancy while still teaching? Sarah: That’s a good idea. It would give me a chance to test the waters. Mr. Patel: Exactly. Let’s map out a timeline and identify key milestones for this transition.</t>
+  </si>
+  <si>
+    <t>Ms. Li: Hiroshi, it’s good to see you again. Last session, we talked about your desire to move into a leadership role. How have you been progressing? Hiroshi: I’ve been taking leadership training courses, but I’m still unsure if I’m ready for a higher position. Ms. Li: Self-doubt is common when aiming for growth. What specific skills do you feel you’re lacking? Hiroshi: I struggle with strategic decision-making and managing larger teams. Ms. Li: Those are critical skills. Have you considered finding a mentor in your company to guide you? Hiroshi: I haven’t, but that sounds like a good idea. Ms. Li: Let’s identify potential mentors and create a plan to develop those skills.</t>
+  </si>
+  <si>
+    <t>Dr. Gonzalez: Carlos, welcome back. Last time, we discussed your interest in transitioning to a corporate strategy role. How has that been going? Carlos: I’ve been researching the role and talking to colleagues, but I’m not sure if my sales experience is relevant. Dr. Gonzalez: Sales experience is highly transferable. Have you identified any gaps in your skills or knowledge? Carlos: I think I need to improve my financial analysis skills. Dr. Gonzalez: That’s a good observation. Let’s explore courses or certifications that can help you bridge that gap.</t>
+  </si>
+  <si>
+    <t>Mr. O’Connor: Priya, it’s great to see you again. Last session, we talked about your interest in project management. How have you been exploring that? Priya: I’ve been shadowing a project manager at work, but I’m not sure if I have the right personality for it. Mr. O’Connor: Personality is important, but skills can be developed. What aspects of the role appeal to you? Priya: I like the idea of leading teams and delivering projects, but I’m not sure if I’m assertive enough. Mr. O’Connor: Assertiveness can be learned. Let’s work on building your confidence and leadership skills.</t>
+  </si>
+  <si>
+    <t>Dr. Priya: Ahmed, we’ve discussed your career aspirations over the past few sessions. How do you feel about transitioning from retail management to a corporate role? Ahmed: I’m excited but nervous. Retail has been my comfort zone, but I feel stagnant. I want to grow, maybe into supply chain management. Dr. Priya: That’s a great direction. Your retail experience gives you a strong foundation in logistics and customer needs. Have you explored certifications in supply chain management? Ahmed: Yes, I’ve looked into a few online courses. But I’m unsure if they’ll be enough to land a corporate job. Dr. Priya: Certifications are a good start, but networking is equally important. Have you considered attending industry events or connecting with professionals on LinkedIn? Ahmed: I’ve started reaching out, but I feel out of place. Many people in corporate roles seem to have more formal education. Dr. Priya: Remember, your hands-on experience is valuable. Highlight your achievements in retail—like improving sales or streamlining operations. Confidence is key. Ahmed: That makes sense. I’ll focus on building my network and updating my resume to reflect my strengths. Dr. Priya: Excellent. Let’s set a goal for next session: identify three networking events and draft a tailored resume.</t>
+  </si>
+  <si>
+    <t>Mr. Carter: Maria, last week we talked about your goal to become a registered nurse (RN). How’s your research going on RN programs? Maria: I found a few local schools offering accelerated programs. But balancing work and school seems overwhelming. Mr. Carter: It’s a big commitment, but it’s doable. Have you discussed flexible scheduling with your employer? Maria: Not yet. I’m worried they’ll say no. Mr. Carter: It’s worth asking. Many employers support further education, especially in healthcare. Let’s strategize how to approach them. Maria: Okay. I’m also concerned about the cost. Even with financial aid, it’s a lot. Mr. Carter: Have you looked into scholarships or employer tuition reimbursement programs? Maria: I haven’t. I didn’t think I’d qualify. Mr. Carter: Don’t sell yourself short. Your experience as an LPN makes you a strong candidate. Let’s explore those options together. Maria: That would be great. I feel more hopeful already.</t>
+  </si>
+  <si>
+    <t>Ms. Li: Hiroshi, last time we discussed your interest in moving into a leadership role. How do you feel about your progress? Hiroshi: I’ve started taking online courses in project management, but I’m not sure if it’s enough. Ms. Li: That’s a good start. Leadership also requires soft skills like communication and team management. Have you sought opportunities to lead projects at work? Hiroshi: Not yet. I’m hesitant to ask my manager. Ms. Li: Why is that? Hiroshi: I don’t want to seem overambitious. Ms. Li: Ambition is a strength, not a weakness. Frame it as a desire to grow and contribute more to the team. Hiroshi: That’s a good point. I’ll talk to my manager next week. Ms. Li: Great. Let’s also work on your elevator pitch for leadership roles.</t>
+  </si>
+  <si>
+    <t>Dr. Emily: Fatima, we’ve talked about your desire to start your own marketing agency. What steps have you taken so far? Fatima: I’ve created a business plan and started saving money. But I’m worried about failing. Dr. Emily: Fear of failure is natural. What’s your biggest concern? Fatima: Losing my savings and not finding clients. Dr. Emily: Have you considered starting part-time while keeping your current job? Fatima: That’s a good idea. I could test the waters without risking everything. Dr. Emily: Exactly. Let’s also explore mentorship opportunities. Having a guide can make a big difference.</t>
+  </si>
+  <si>
+    <t>Mr. Samuel: Aisha, last session we discussed your goal to become a certified public accountant (CPA). How’s your preparation going? Aisha: I’ve started studying, but the material is challenging. Mr. Samuel: It’s a tough exam, but you’re capable. Have you joined any study groups? Aisha: No, I’ve been studying alone. Mr. Samuel: Consider joining a group. Collaborative learning can help. Also, let’s look into tutoring options. Aisha: That sounds helpful. I’ll look into it. Mr. Samuel: Great. Let’s set a study schedule for the next month.</t>
+  </si>
+  <si>
+    <t>Dr. Sharma: Michael, it’s good to see you again. Last time, we discussed your interest in transitioning into the tech industry. How have you been exploring that? Michael: Hi, Dr. Sharma. I’ve been taking online courses in data analysis and coding. I’m enjoying it, but I’m worried about my lack of formal experience. Dr. Sharma: That’s a great start. Upskilling is essential, but let’s also focus on how to leverage your business background. Have you considered roles like business analyst or product manager? Michael: I’ve thought about it, but I’m not sure how to position myself for those roles. Dr. Sharma: Your business degree is a strong foundation. Highlight your analytical skills and any projects you’ve worked on. Networking is also key—have you reached out to professionals in those roles? Michael: Not yet. I’m not sure how to approach them. Dr. Sharma: Let’s work on crafting a LinkedIn message template. Also, consider informational interviews to learn more about these roles. Michael: That sounds helpful. I’ll start working on that.</t>
+  </si>
+  <si>
+    <t>Mr. Rivera: Aisha, welcome back. Last session, we talked about your desire to move into a leadership role. How’s that going? Aisha: Hi, Mr. Rivera. I’ve been applying for managerial positions, but I’m not getting many responses. Mr. Rivera: Let’s review your resume. Are you tailoring it to highlight leadership skills like project management or team coordination? Aisha: I’ve tried, but I’m not sure if it’s strong enough. Mr. Rivera: Your experience in healthcare administration is valuable. Let’s emphasize specific achievements, like streamlining processes or leading teams. Also, have you considered certifications like PMP? Aisha: I’ve heard of it, but I’m not sure if it’s worth the investment. Mr. Rivera: It can boost your credibility. Let’s explore scholarships or employer-sponsored programs. Aisha: That’s a good idea. I’ll look into it.</t>
+  </si>
+  <si>
+    <t>Ms. Zhang: James, it’s good to see you. Last time, we discussed your dissatisfaction with your current role. What’s changed since then? James: Hi, Ms. Zhang. I’ve realized I want to move into renewable energy, but I’m not sure how to make the switch. Ms. Zhang: That’s a growing field. Have you researched companies or roles that align with your interests? James: I’ve looked, but most require experience I don’t have. Ms. Zhang: Let’s focus on transferable skills, like project management or technical expertise. Have you considered volunteering or internships? James: I hadn’t thought of that. Ms. Zhang: It’s a great way to gain experience and network. Let’s identify some opportunities.</t>
+  </si>
+  <si>
+    <t>Dr. Ali: Sarah, welcome back. Last session, we discussed your interest in counselling. How’s that going? Sarah: Hi, Dr. Ali. I’ve been researching programs, but I’m worried about the cost. Dr. Ali: That’s a valid concern. Have you looked into scholarships or part-time programs? Sarah: I’ve started, but it’s overwhelming. Dr. Ali: Let’s break it down. We’ll create a list of programs and funding options. Also, consider gaining experience through volunteering. Sarah: That sounds manageable.</t>
+  </si>
+  <si>
+    <t>Ms. Gonzalez: David, it’s good to see you. Last time, we discussed your desire for a more creative role. What’s new? David: Hi, Ms. Gonzalez. I’ve been exploring UX design, but I’m not sure how to transition. Ms. Gonzalez: UX design is a great fit. Have you taken any courses or built a portfolio? David: I’ve started, but I’m not confident in my work. Ms. Gonzalez: Let’s review your portfolio and identify areas for improvement. Networking with UX professionals can also help. David: That sounds like a plan.</t>
+  </si>
+  <si>
+    <t>Dr. Sharma: Raj, we’ve discussed your dissatisfaction with retail management. What have you reflected on since our last session? Raj: I’ve realized I want a career that aligns with my passion for sustainability. Retail feels stagnant, and I’m not making the impact I hoped for. Dr. Sharma: That’s a great insight. Have you explored roles in sustainable business or corporate social responsibility? Raj: I’ve looked into it, but I’m unsure if my skills translate. My experience is mostly in operations and customer service. Dr. Sharma: Your operational expertise is valuable. Many companies need leaders who can implement sustainable practices. Have you considered upskilling? Raj: I’ve thought about a certification in sustainability management. Would that help? Dr. Sharma: Absolutely. It would bridge the gap and make you a strong candidate. Let’s map out a plan to transition into this field.</t>
+  </si>
+  <si>
+    <t>Mr. Carter: Maria, last time we discussed your goal of becoming a registered nurse (RN). How’s your progress? Maria: I’ve started an RN program, but balancing work and school is overwhelming. I’m worried I won’t finish. Mr. Carter: That’s a common challenge. Have you explored flexible scheduling or employer-sponsored programs? Maria: My employer offers tuition reimbursement, but the shifts are rigid. I’m considering part-time work. Mr. Carter: That could help. Have you thought about online courses to supplement your program? Maria: I haven’t. Do you think that would ease the workload? Mr. Carter: Yes, and it would give you more control over your time. Let’s explore options to make this transition smoother.</t>
+  </si>
+  <si>
+    <t>Ms. Zhang: Ahmed, you mentioned feeling stuck in your current role. What’s changed since we last spoke? Ahmed: I’ve realized I want to move into a leadership position, but I lack management experience. Ms. Zhang: Leadership roles often require soft skills like communication and team management. Have you taken steps to develop these? Ahmed: I’ve started mentoring junior developers, but I’m not sure it’s enough. Ms. Zhang: Mentoring is a great start. Have you considered leadership training or certifications? Ahmed: Not yet. Would that make a difference? Ms. Zhang: Definitely. It would demonstrate your commitment to growth. Let’s identify programs that align with your goals.</t>
+  </si>
+  <si>
+    <t>Dr. Thompson: Fatima, you’ve expressed interest in transitioning to policy work. What steps have you taken? Fatima: I’ve networked with professionals in the field, but I’m unsure how to position myself for policy roles. Dr. Thompson: Networking is key. Have you identified transferable skills from your community health experience? Fatima: I’ve worked on health campaigns, but policy seems more technical. Dr. Thompson: Campaign work involves advocacy and stakeholder engagement—both crucial in policy. Have you considered short courses in health policy? Fatima: That’s a good idea. Would that help me stand out? Dr. Thompson: Absolutely. Let’s create a strategy to highlight your strengths and fill any gaps.</t>
+  </si>
+  <si>
+    <t>Mr. Okafor: Chiamaka, last time we discussed your interest in entrepreneurship. Have you made progress? Chiamaka: I’ve started a small business selling handmade crafts, but I’m struggling to balance it with my full-time job. Mr. Okafor: Balancing both is challenging. Have you considered scaling back your hours at work? Chiamaka: I’m hesitant to lose the stability. Is there another way? Mr. Okafor: You could explore automating parts of your business or hiring part-time help. Have you thought about that? Chiamaka: Not yet. Do you think it’s feasible? Mr. Okafor: Yes, with proper planning. Let’s outline steps to grow your business without sacrificing your career.</t>
+  </si>
+  <si>
+    <t>Dr. Patel: James, we’ve discussed your skills and interests over the past sessions. How do you feel about exploring roles in project management, given your background? James: I’m open to it, but I’m worried about my lack of formal certifications. Do you think that’s a dealbreaker? Dr. Patel: Not necessarily. Many employers value experience over certifications. However, obtaining a PMP or PRINCE2 certification could boost your credibility. Have you considered part-time study? James: I have, but finances are tight right now. I’m also unsure if I’m ready to commit to another course. Dr. Patel: That’s understandable. Let’s look for roles that offer training opportunities. Many companies invest in upskilling their employees. I’ll share some job postings that align with this. James: That sounds good. I’d prefer a role where I can grow rather than just fill a position. Dr. Patel: Exactly. Growth is key. Let’s also work on tailoring your CV to highlight transferable skills like leadership and problem-solving.</t>
+  </si>
+  <si>
+    <t>Mr. Kim: Maria, last time we talked about your passion for UX design. Have you had a chance to explore online courses like Coursera or Udemy? Maria: Yes, I started a UX design course last week. It’s challenging but exciting. I’m just not sure if I’m good enough to transition into this field. Mr. Kim: Self-doubt is normal when stepping into something new. Your design background gives you a solid foundation. Let’s focus on building a portfolio. Have you thought about freelance projects? Maria: I have, but I don’t know where to start. Mr. Kim: Platforms like Upwork or Fiverr are great for beginners. I can guide you on creating a profile and pricing your work. Maria: That would be helpful. I’m also worried about balancing this with my current job. Mr. Kim: Time management is crucial. Let’s create a schedule that allows you to dedicate a few hours weekly to freelancing.</t>
+  </si>
+  <si>
+    <t>Ms. Hassan: Ahmed, we’ve identified your interest in sustainable construction. How do you feel about pursuing a master’s in environmental engineering? Ahmed: It’s appealing, but I’m concerned about the cost and time commitment. Ms. Hassan: Those are valid concerns. Some universities offer scholarships for underrepresented groups. Would you like me to help you research options? Ahmed: Yes, please. I’d also like to know if there are entry-level roles in this field that don’t require further education. Ms. Hassan: Absolutely. Many firms value hands-on experience. Let’s explore internships or assistant roles in green construction companies. Ahmed: That sounds like a good starting point. I’d also like to improve my networking skills. Ms. Hassan: Networking is essential. I’ll share tips on leveraging LinkedIn and attending industry events.</t>
+  </si>
+  <si>
+    <t>Dr. Zhang: Sarah, we’ve discussed your interest in counselling. Have you thought about pursuing a master’s in clinical psychology? Sarah: I have, but I’m unsure if I can handle the emotional toll. Dr. Zhang: That’s a valid concern. Have you considered starting with volunteer work in mental health to test the waters? Sarah: That’s a good idea. I’d like to gain some experience before committing to further study. Dr. Zhang: Great. I’ll connect you with local organizations. In the meantime, let’s work on your application for graduate programs. Sarah: I’d appreciate that. I’m also worried about balancing study with work. Dr. Zhang: Many programs offer part-time options. Let’s explore those to ease the transition.</t>
+  </si>
+  <si>
+    <t>Mr. Mendez: Lucia, we’ve talked about your interest in hospitality management. Have you considered enrolling in a vocational training program? Lucia: I have, but I’m worried about the cost. Mr. Mendez: Many programs offer scholarships or payment plans. I can help you find one that fits your budget. Lucia: That would be great. I’d also like to know if there are entry-level roles in hotels that offer training. Mr. Mendez: Definitely. Many hotels hire trainees and provide on-the-job training. Let’s identify some opportunities and prepare your application. Lucia: Thank you. I’m excited about the possibilities. Mr. Mendez: That’s the spirit! Let’s take it step by step.</t>
+  </si>
+  <si>
+    <t>Dr. Thompson: "James, we’ve been working together for a few weeks now. How do you feel about the progress we’ve made in identifying your career goals?" James: "It’s been helpful, but I’m still unsure about how to transition from retail management to corporate strategy. I feel like my experience isn’t directly transferable." Dr. Thompson: "That’s a common concern. Let’s break it down. Your leadership and operational skills are highly valuable. Have you considered certifications like PMP or Six Sigma to bridge the gap?" James: "I’ve heard of them, but I’m not sure if they’re worth the investment." Dr. Thompson: "They can be, especially if they align with your target roles. Let’s explore job postings for corporate strategy positions and identify the skills they require. We can then map your experience and see where certifications or additional training might help." James: "That makes sense. I’ve also been networking, but I’m not sure how to leverage those connections effectively." Dr. Thompson: "Networking is key. Let’s strategize on how to approach your contacts. For example, you could ask for informational interviews to learn more about their roles and express your interest in transitioning." James: "I’ll give that a try. Thanks, Dr. Thompson."</t>
+  </si>
+  <si>
+    <t>Mr. Kumar: "Priya, we’ve discussed your interest in data science. Have you taken any steps toward upskilling?" Priya: "Yes, I’ve started an online course in machine learning, but I’m worried it’s not enough to make the switch." Mr. Kumar: "Upskilling is a great start. Let’s look at your current projects. Are there opportunities to incorporate data science techniques, even on a small scale?" Priya: "I’ve been trying, but my team is focused on traditional software development." Mr. Kumar: "That’s a challenge, but not insurmountable. Could you propose a pilot project to demonstrate the value of data science? This would also showcase your initiative to your managers." Priya: "That’s a good idea. I’ll draft a proposal. What about certifications? Are they necessary?" Mr. Kumar: "Certifications can help, especially in a competitive field like data science. Let’s identify a few that are recognized in the industry and align with your goals." Priya: "Thank you, Mr. Kumar. I feel more confident about this transition now."</t>
+  </si>
+  <si>
+    <t>Ms. Zhang: "Carlos, we’ve been working on adapting your experience to the Canadian job market. How do you feel about the progress?" Carlos: "It’s been challenging. My qualifications aren’t always recognized here, and I’m not sure how to compete with local candidates." Ms. Zhang: "That’s a common hurdle for immigrant professionals. Let’s focus on networking and building relationships within the industry. Have you joined any professional associations?" Carlos: "I’ve joined a few, but I’m not sure how to engage effectively." Ms. Zhang: "Start by attending events and connecting with members on LinkedIn. You could also volunteer for committees to gain visibility." Carlos: "I’ll try that. What about certifications? Would they help?" Ms. Zhang: "Absolutely. Canadian certifications like PMP or Gold Seal can enhance your credibility. Let’s explore which ones align with your goals." Carlos: "Thank you, Ms. Zhang. I’ll start working on these steps."</t>
+  </si>
+  <si>
+    <t>Dr. O’Connor: "Lisa, we’ve been discussing your goal of moving into a leadership role. How do you feel about your readiness?" Lisa: "I feel confident in my technical skills, but I’m not sure if I have the leadership experience employers are looking for." Dr. O’Connor: "Leadership isn’t just about titles. Let’s identify instances where you’ve led projects or mentored colleagues. These experiences are valuable." Lisa: "I’ve led a few campaigns, but they were small-scale." Dr. O’Connor: "Scale isn’t the only measure of success. Focus on the outcomes and how you influenced the team. Let’s also explore leadership training programs to build your skills further." Lisa: "That sounds helpful. What about networking? Should I focus on that too?" Dr. O’Connor: "Absolutely. Networking can open doors to leadership opportunities. Let’s identify key events and strategize on how to connect with industry leaders." Lisa: "Thank you, Dr. O’Connor. I’ll start working on these areas."</t>
+  </si>
+  <si>
+    <t>Ms. Hassan: "Fatima, we’ve been exploring your interest in human resources. How do you feel about the transition so far?" Fatima: "I’m excited but nervous. I’m not sure if my social work experience is relevant." Ms. Hassan: "Your experience is highly relevant. Skills like communication, empathy, and conflict resolution are crucial in HR. Let’s identify specific HR roles that align with your strengths." Fatima: "I’ve been looking at HR coordinator roles, but I’m not sure if I meet the requirements." Ms. Hassan: "Let’s review the job descriptions together and identify any gaps. We can then create a plan to address them, such as short courses or certifications." Fatima: "That would be helpful. What about networking? Should I focus on that too?" Ms. Hassan: "Yes, networking is key. Attend HR events and connect with professionals on LinkedIn. You could also seek informational interviews to learn more about the field." Fatima: "Thank you, Ms. Hassan. I feel more confident about this transition now."</t>
+  </si>
+  <si>
+    <t>Dr. Carter: Raj, it’s great to see you again. Last time, we discussed your interest in transitioning from software development to data science. How have you been progressing with the online courses you mentioned? Raj: Hi, Dr. Carter. I’ve completed two courses on machine learning and Python for data analysis. I’m enjoying it, but I’m still unsure if this is the right path for me. I worry about competing with people who have more experience. Dr. Carter: That’s a valid concern, but remember, your background in software development gives you a strong foundation. Have you thought about applying for internships or freelance projects to build your portfolio? Raj: I haven’t, but that’s a good idea. I’ve been so focused on learning that I didn’t consider practical experience. Do you think I should reach out to my network for opportunities? Dr. Carter: Absolutely. Networking is crucial. Let’s also explore job boards and LinkedIn for entry-level data science roles. You’re making great progress, Raj. Confidence comes with action.</t>
+  </si>
+  <si>
+    <t>Mr. Okafor: Fatima, welcome back. Last session, you expressed a desire to move into a managerial role. Have you had a chance to discuss this with your supervisor? Fatima: Yes, I did. They suggested I take on more responsibilities in my current role to prove my readiness. But I feel stuck—I’ve been doing the same tasks for years. Mr. Okafor: It’s common to feel that way. Let’s focus on upskilling. Have you considered pursuing a certification in project management or leadership? Fatima: I’ve looked into it, but I’m not sure which program would be most respected in my industry. Mr. Okafor: I recommend the PMP certification. It’s globally recognized and aligns with your goals. Let’s also identify specific projects at work where you can take the lead. Fatima: That sounds like a plan. I’ll start researching PMP courses today.</t>
+  </si>
+  <si>
+    <t>Ms. Martinez: Liam, it’s good to see you. Last time, we talked about your interest in moving into a more strategic role. How have you been exploring that? Liam: Hi, Ms. Martinez. I’ve been trying to take on more strategic tasks at work, but my boss seems hesitant to delegate. I’m considering looking for a new job. Ms. Martinez: That’s a big decision. Before jumping ship, let’s explore ways to demonstrate your strategic skills. Have you thought about proposing a new campaign or initiative? Liam: Not really. I guess I’ve been waiting for opportunities to come to me. Ms. Martinez: Proactivity is key. Draft a proposal for a campaign and present it to your boss. This could showcase your readiness for a more strategic role. Liam: That’s a great idea. I’ll start working on it right away.</t>
+  </si>
+  <si>
+    <t>Dr. Desai: Maria, welcome back. Last session, we discussed your interest in transitioning to a nurse practitioner role. How have you been progressing with your application for advanced programs? Maria: Hi, Dr. Desai. I’ve applied to three programs, but I’m nervous about balancing work and studies. Dr. Desai: It’s a valid concern, but many programs offer part-time options. Have you explored those? Maria: I have, but I’m still worried about the financial burden. Dr. Desai: Let’s look into scholarships and employer-sponsored programs. Many hospitals offer tuition reimbursement for nurses pursuing advanced degrees. Maria: That’s a great idea. I’ll check with my HR department.</t>
+  </si>
+  <si>
+    <t>Mr. Kim: Amina, it’s good to see you again. Last time, we discussed your desire to secure a full-time role in journalism. How has your job search been going? Amina: Hi, Mr. Kim. I’ve applied to several positions, but I haven’t heard back from most. I’m starting to feel discouraged. Mr. Kim: Job searches can be challenging, but persistence pays off. Have you considered tailoring your portfolio to specific roles or industries? Amina: I haven’t, but that makes sense. I’ve been using the same portfolio for every application. Mr. Kim: Let’s work on creating targeted portfolios and cover letters. Also, consider reaching out to editors or journalists for informational interviews. Amina: That’s a great idea. I’ll start researching contacts today.</t>
+  </si>
+  <si>
+    <t>Dr. Sharma: Michael, it’s great to see you again. Last time, we discussed your interest in transitioning from retail management to digital marketing. How have you been exploring that? Michael: Thanks, Dr. Sharma. I’ve been taking online courses in SEO and content marketing. I’ve also started networking on LinkedIn, but I’m still unsure about how to make the leap. Dr. Sharma: That’s excellent progress! Networking is key. Have you identified any specific roles or companies that align with your skills and interests? Michael: Yes, I’ve been looking at digital marketing roles in e-commerce companies. But I’m worried my retail background might not be enough. Dr. Sharma: Your retail experience is valuable—it gives you customer insights and operational knowledge. Let’s work on tailoring your resume to highlight transferable skills. Have you considered informational interviews? Michael: Not yet, but that sounds like a good idea. How do I approach someone for that? Dr. Sharma: Start by reaching out to professionals in your target field via LinkedIn. Be polite and express genuine interest in their career path. Would you like to practice drafting a message? Michael: Yes, that would help a lot.</t>
+  </si>
+  <si>
+    <t>Mr. Lee: Maria, welcome back. Last session, we talked about your goal of becoming a registered nurse (RN). How’s your preparation going? Maria: Hi, Mr. Lee. I’ve enrolled in an RN program, but balancing work and school is tough. I’m feeling overwhelmed. Mr. Lee: That’s understandable. Have you explored flexible scheduling options at work or discussed your goals with your employer? Maria: I haven’t yet. I’m worried they might not support me. Mr. Lee: Many employers value upskilling. Let’s strategize how to approach them. Also, have you looked into financial aid or part-time study options? Maria: I’ve applied for a scholarship, but I’m still waiting to hear back. Part-time study might be a better fit. Mr. Lee: That’s a good backup plan. Let’s also explore time management techniques to help you balance everything.</t>
+  </si>
+  <si>
+    <t>Ms. Ali: James, it’s good to see you again. Last time, we discussed your interest in moving into renewable energy. How’s your job search going? James: Hi, Ms. Ali. I’ve applied to a few roles, but I’m not getting many responses. I think my lack of direct experience in renewables is holding me back. Ms. Ali: That’s a common challenge. Have you considered highlighting your transferable skills, like project management and technical expertise? James: I’ve tried, but I’m not sure if I’m doing it effectively. Ms. Ali: Let’s review your resume together. Additionally, have you thought about certifications or short courses in renewable energy to bolster your profile? James: That’s a good idea. Are there any specific certifications you’d recommend? Ms. Ali: Yes, I’ll share a list with you. Also, networking with professionals in the field could open doors.</t>
+  </si>
+  <si>
+    <t>Dr. Carter: Fatima, welcome back. Last session, we discussed your desire to move into educational leadership. How have you been progressing? Fatima: Hi, Dr. Carter. I’ve been researching leadership roles, but I’m unsure if I have the right experience. Dr. Carter: Leadership roles often require a mix of teaching experience and additional training. Have you considered pursuing a leadership qualification? Fatima: Yes, but I’m not sure which one to choose. Dr. Carter: Let’s explore options like the National Professional Qualification for Leadership (NPQL). Also, have you taken on any leadership responsibilities at your current school? Fatima: I’ve led a few projects, but nothing major. Dr. Carter: That’s a great start. Let’s work on building your leadership portfolio and identifying opportunities to take on more responsibilities.</t>
+  </si>
+  <si>
+    <t>Mr. Mendez: Sarah, it’s great to see you again. Last time, we discussed your interest in transitioning to corporate communications. How’s your progress? Sarah: Hi, Mr. Mendez. I’ve been networking and applying for roles, but I’m not getting many interviews. Mr. Mendez: Let’s review your application materials. Are you tailoring your resume and cover letter for each role? Sarah: I try to, but I’m not sure if I’m doing it right. Mr. Mendez: Let’s work on that today. Also, have you considered leveraging your PR experience to highlight your crisis management and media relations skills? Sarah: That’s a good point. I’ll focus on that. Mr. Mendez: Great. Let’s also explore informational interviews to learn more about the corporate communications field.</t>
+  </si>
+  <si>
+    <t>David: Hi Anya, thanks for seeing me again. I’m still feeling stuck. I’ve applied for dozens of sales jobs, but nothing. I’m starting to wonder if sales is even the right path anymore. Anya: David, we've talked about your transferable skills. Your experience in relationship building and negotiation is valuable. Have you considered roles outside of traditional sales, perhaps in client management or even training? David: I haven't, honestly. I've been so focused on sales roles, I haven't looked elsewhere. It feels like starting over. Anya: It doesn't have to be. We can explore those other avenues. We can also refine your resume and cover letter to highlight those transferable skills, making them more appealing to a broader range of employers. Let’s also discuss your networking strategy. Are you leveraging LinkedIn and other professional platforms? David: I have a LinkedIn profile, but I haven't been very active. Anya: Let's work on that. A strong online presence is crucial. We can also explore some industry events where you can connect with people in different fields. Don't get discouraged, David. We'll find the right fit for you.</t>
+  </si>
+  <si>
+    <t>Maria: Anya, I'm feeling burnt out. Freelancing is tough. The feast-or-famine cycle is exhausting, and I'm tired of constantly hustling for work. Anya: Maria, I understand. Freelancing can be challenging. We've discussed your creative skills and your passion for design. Have you considered exploring more stable roles, perhaps in-house at a company? Maria: I have, but I'm worried about losing the flexibility I have now. And I'm not sure my portfolio is strong enough for those kinds of jobs. Anya: We can work on strengthening your portfolio. We can also identify companies that value creativity and offer a good work-life balance. It doesn't have to be all or nothing. You could look for part-time or contract positions initially to transition gradually. Maria: That's a good idea. I hadn't thought of that. Anya: We can also explore developing a niche within graphic design. Specializing in a particular area could make you more marketable and allow you to command higher rates.</t>
+  </si>
+  <si>
+    <t>Kenji: Anya, I feel like I've hit a ceiling in my research career. I enjoy the work, but I'm ready for more leadership opportunities. Anya: Kenji, your PhD and research experience are highly valuable. We've talked about your interest in moving into management. Have you explored any specific management training programs or certifications? Kenji: I haven't yet. I wasn't sure where to start. Anya: We can research some reputable programs that align with your goals. We can also work on highlighting your leadership qualities in your resume and during interviews. Your experience leading research teams and projects is relevant. Kenji: I see. I need to frame my experience differently. Anya: Exactly. We can also work on your networking strategy within the engineering field. Connecting with people in management roles can provide valuable insights and opportunities.</t>
+  </si>
+  <si>
+    <t>Fatima: Anya, I'm not sure social services are for me long-term. It's emotionally draining, and I feel like I'm not making the impact I hoped for. Anya: Fatima, your passion for helping others is clear. We've discussed your interest in psychology. Have you considered other career paths within that field, perhaps in education or human resources? Fatima: I've thought about HR. I like the idea of helping people within a company setting. Anya: That’s a great option to explore. We can look at HR certifications or entry-level positions that might be a good fit. Your psychology background would be a valuable asset. Fatima: I'm also a bit worried about the salary. Social services don’t pay well, and I'd like to find something more financially stable. Anya: We can research salary expectations for different HR roles in your area. We can also discuss strategies for negotiating your salary when you start applying for jobs.</t>
+  </si>
+  <si>
+    <t>Ricardo: Anya, I've been an electronics technician for 20 years, and I'm good at what I do. But I feel stuck. I want to move up, but I’m not sure how. Anya: Ricardo, your experience is invaluable. Have you considered specializing in a particular area of electronics, perhaps renewable energy systems or robotics? Ricardo: I've thought about it, but I'm not sure I want to go back to school for a full degree. Anya: There are other options. You could look into certificate programs or online courses to gain specialized knowledge. We can also explore leadership opportunities within your current company. Perhaps you could mentor junior technicians or take on more project management responsibilities. Ricardo: That's interesting. I hadn't thought about mentoring. Anya: It's a great way to develop your leadership skills and share your expertise. We can also work on updating your resume to highlight your accomplishments and the value you bring to your current role. Sometimes, internal promotions are overlooked because employees haven't effectively communicated their contributions.</t>
+  </si>
+  <si>
+    <t>Maria: "I'm still feeling stuck, David. I've applied for dozens of marketing positions, but I haven't even gotten many interviews. I'm starting to doubt myself." David: "Maria, we've discussed your resume and cover letter extensively. They're strong. Let's revisit your interview skills. We can do a mock interview today and pinpoint areas for improvement." Maria: "That sounds helpful. I get so nervous in interviews. I think that's my biggest problem." David: "Nerves are normal. We can work on strategies to manage them. We'll also discuss how to showcase your transferable skills, even for roles slightly outside your direct marketing experience. Have you considered networking more actively?" Maria: "I've been hesitant. I feel awkward approaching people." David: "Networking is about building genuine connections. We can practice some conversation starters and strategies to make it feel less daunting. Small steps can make a big difference."</t>
+  </si>
+  <si>
+    <t>Aisha: "Sarah, I'm still torn. I'm good at engineering, but I'm not passionate about it. I keep thinking about going into sustainable development." Sarah: "Aisha, that's a significant shift. We've explored your interests and values, and sustainable development aligns well. Let's discuss the practical steps. Have you researched specific programs or certifications?" Aisha: "I've looked at a few master's programs, but I'm worried about the financial commitment." Sarah: "That's a valid concern. We can explore funding options, scholarships, and part-time study. We can also identify transferable skills from your engineering background that would be valuable in sustainable development roles." Aisha: "I hadn't thought about that. I guess my analytical and problem-solving skills would be relevant." Sarah: "Exactly. We can highlight those in your application materials. Let's also discuss networking opportunities within the sustainable development field."</t>
+  </si>
+  <si>
+    <t>Jean-Pierre: "Isabelle, I'm frustrated. I've been in sales for ten years, and I feel like I've hit a plateau. I want to move into management, but my company isn't offering any opportunities." Isabelle: "Jean-Pierre, we've discussed your leadership potential. Let's focus on how to demonstrate that more effectively. Have you considered taking any leadership training courses?" Jean-Pierre: "I haven't. I wasn't sure if they would be worth it." Isabelle: "They can be. We can research reputable programs that align with your career goals. We can also discuss how to showcase your leadership skills in your current role, even without a formal management title. Project leadership, mentoring, and cross-functional team participation are all valuable experiences." Jean-Pierre: "That makes sense. I could volunteer to lead the next team project." Isabelle: "Excellent idea. We can also refine your resume and cover letter to emphasize your leadership qualities and achievements."</t>
+  </si>
+  <si>
+    <t>Kenji: "Emily, I'm bored with my current job. The work is too repetitive. I want to work on more innovative projects." Emily: "Kenji, we've talked about your passion for artificial intelligence. Let's discuss how to transition into that field. Have you explored AI-related certifications or online courses?" Kenji: "I've started looking at some online courses, but I'm not sure which ones are the most valuable." Emily: "We can research reputable programs and discuss how to incorporate them into your professional development plan. We can also identify companies that are actively working on AI projects and tailor your resume and cover letter to highlight your relevant skills and interests." Kenji: "That would be great. I'm also a bit nervous about competing with more experienced AI specialists." Emily: "That's understandable. We can focus on building your portfolio with personal projects and contributing to open-source AI initiatives. This will demonstrate your skills and passion to potential employers."</t>
+  </si>
+  <si>
+    <t>Fatima: "Robert, I'm feeling overwhelmed. I've been in customer service for so long, and I'm ready for something more fulfilling. I'm interested in social work, but I'm not sure where to start." Robert: "Fatima, we've discussed your passion for helping others. Social work aligns well with your values. Let's explore the educational requirements and licensing process in your province." Fatima: "I know I'll need a bachelor's degree in social work. I'm worried about going back to school at my age." Robert: "It's never too late to pursue your dreams, Fatima. We can explore part-time study options, online programs, and financial aid opportunities. We can also discuss how your customer service experience can be an asset in a social work role." Fatima: "Really? I hadn't thought of that." Robert: "Absolutely. Your experience in dealing with people from diverse backgrounds, resolving conflicts, and providing support are all valuable skills. We can highlight those in your applications."</t>
+  </si>
+  <si>
+    <t>David: Yes, Anya. I’ve applied for a few positions. I even had one interview, but I didn't get it. They said I lacked direct project management experience. Anya: That's understandable. It's a common hurdle. Let's look at some strategies to address this. We could consider a project management certification course, or perhaps volunteering for projects to build your portfolio. What are your thoughts? David: A certification sounds expensive, and honestly, I need to find something soon. Volunteering… I hadn't thought of that. It might be a good way to gain experience. Anya: Exactly. We can explore some local organizations that might need your skills. It's a win-win. You gain experience, and they get valuable help. Let's research some options together.</t>
+  </si>
+  <si>
+    <t>Maria: Hi Anya. Things are okay, but I'm still feeling unfulfilled. I've been looking at UX/UI design courses, as we discussed. Anya: That's great! Have you narrowed down any specific programs? Maria: I'm considering a few online options. They seem more flexible with my current job. But I'm also a little nervous about making the switch. It feels like a big step. Anya: It is a big step, but it's also an exciting one. We can break it down into smaller, more manageable steps. Let's discuss your financial situation, explore scholarship opportunities, and also connect you with some UX/UI professionals for informational interviews.</t>
+  </si>
+  <si>
+    <t>Kenji: Yes, Anya. I've been thinking about it a lot. I'm comfortable with coding, but I feel I have more to offer. Anya: Absolutely. Have you considered specific leadership paths, like team lead or project manager? Kenji: Project manager, I think. I enjoy organizing and coordinating projects. But I don’t have any formal project management experience. Anya: We can address that. We could explore some internal opportunities within your current company, perhaps shadowing a project manager. We can also look at relevant certifications like PMP. What do you think? Kenji: Shadowing sounds great. I'll talk to my manager about it. And I'll research the PMP certification.</t>
+  </si>
+  <si>
+    <t>Fatima: Hi Anya. Yes, I've been researching careers in human resources. It seems like a good fit for my skills and interests. Anya: That's interesting. Human resources is a growing field. What aspects of HR are you most drawn to? Fatima: Recruitment and employee relations, I think. I enjoy working with people and helping them find the right opportunities. Anya: Excellent. Let's discuss the different paths within HR and the qualifications needed. We can also explore internship opportunities to gain some practical experience. Fatima: That would be great. I'm a bit worried about starting over in a new field. Anya: It's natural to feel that way. But your social work background has equipped you with valuable transferable skills. We'll highlight those in your resume and cover letter.</t>
+  </si>
+  <si>
+    <t>Omar: Hi Anya. I’ve been thinking a lot about what we discussed. My back is getting worse, and I don't think I can continue as a mechanic much longer. Anya: I understand. We talked about your interest in teaching. Have you explored that further? Omar: Yes, I’ve looked at some vocational training programs. But I'm not sure if I'm qualified to teach. Anya: Your years of experience as a mechanic are incredibly valuable. We can explore programs that will allow you to leverage that experience in a teaching role. We can also discuss bridging courses or certifications that might be beneficial. Don't worry, we'll find a path that works for you. Omar: Thank you, Anya. That gives me some hope.</t>
+  </si>
+  <si>
+    <t>David: Hi Sarah, thanks for seeing me again. I've been doing some networking, like we discussed. I had a couple of informational interviews, but nothing concrete yet. I'm starting to feel a bit discouraged. Sarah: That's completely understandable, David. Job searching can be tough. Tell me about the interviews. What did you learn? David: Well, one was at a tech company, which was interesting, but their sales cycle is much longer than what I'm used to. The other was at a smaller firm, but the pay was significantly lower. Sarah: Okay, so we're getting some clarity. It sounds like you're learning what you don't want, which is just as valuable. Let's revisit your salary expectations and also consider the company culture fit. Sometimes a slightly lower salary can be worth it for a better work environment. David: That's a good point. I hadn't really focused on the culture aspect. Sarah: Let's explore that next time. We can also work on refining your interview skills to better address the culture fit question.</t>
+  </si>
+  <si>
+    <t>Aisha: Maria, I'm still struggling with the idea of changing careers completely. Engineering is all I've ever known. Maria: Aisha, remember we talked about your passion for sustainable development? Your engineering background is a huge asset in that field. It's not about abandoning your skills, but applying them in a new context. Aisha: I see what you're saying. I've found a few organizations working on sustainable infrastructure projects. They seem interesting, but I lack experience in that specific area. Maria: We can address that. Let's look at some online courses or workshops that can bridge that gap. We can also highlight your transferable skills in your resume and cover letter. Project management experience is highly valued in any field. Aisha: That gives me some hope. I was feeling a bit lost. Maria: It's a process, Aisha. We'll take it one step at a time.</t>
+  </si>
+  <si>
+    <t>Jean-Pierre: Kenji, I'm starting to think a stable income is more important than pursuing my art full-time. The inconsistency is just too stressful. Kenji: Jean-Pierre, that's a valid concern. Many artists struggle with financial instability. Let's explore ways to leverage your artistic skills in a more stable environment. Jean-Pierre: Like what? I've considered teaching, but the pay isn't great. Kenji: We could look at graphic design roles, or even marketing positions where your creativity would be valued. We can also explore corporate art programs. There are more options than you might think. Jean-Pierre: I hadn't considered corporate art programs. That's interesting. Kenji: Let's research some companies in your area that have those programs. We can also work on tailoring your portfolio to highlight the skills relevant to these roles.</t>
+  </si>
+  <si>
+    <t>Samuel: Anika, I'm feeling burnt out in my current role. The work is monotonous, and I don't see any room for growth. Anika: Samuel, burnout is a serious issue. It's important to address it before it impacts your well-being. Have you considered talking to your manager about your concerns? Samuel: I have, but they weren't very receptive. They said everyone feels that way sometimes. Anika: That's disappointing. It sounds like it might be time to explore other opportunities. Let's look at companies that prioritize employee well-being and offer professional development programs. Samuel: That would be great. I'm also interested in exploring different areas within software development, maybe something more creative. Anika: We can definitely do that. Let's assess your interests and skills to identify potential roles that align with your goals.</t>
+  </si>
+  <si>
+    <t>Isabelle: Ricardo, I'm not sure if I want to go back to teaching. I've been feeling very disillusioned with the education system. Ricardo: Isabelle, that's understandable. Teaching can be incredibly demanding. What aspects of teaching are you feeling disillusioned with? Isabelle: The lack of resources, the large class sizes, and the constant pressure to meet standardized testing requirements. I feel like I'm not making a real difference anymore. Ricardo: Have you considered other roles within education, perhaps curriculum development or educational consulting? Your experience as a teacher would be invaluable in those areas. Isabelle: I hadn't thought about that. That could be interesting. Ricardo: Let's explore those options. We can also look at related fields, such as corporate training or instructional design. Your skills are transferable to many different areas.</t>
+  </si>
+  <si>
+    <t>"Welcome back, David. In our last session, we discussed your interest in transitioning from sales to project management. Have you had a chance to explore the online resources I suggested regarding project management certifications?" "Yes, Sarah. I've looked into the PRINCE2 Foundation course. It seems like a good starting point, but I'm a bit worried about the cost and time commitment, especially being unemployed. I've also been applying for sales roles, just to have something coming in." "That's understandable. Let's look at some funding options for the certification. We can also refine your resume to highlight transferable skills applicable to project management, even from your sales experience. Have you considered networking with project managers in your area?" "Not really. I don't know any, to be honest." "We can work on that. LinkedIn can be a valuable tool. Let's dedicate some time today to building your professional network online and identifying relevant project management groups."</t>
+  </si>
+  <si>
+    <t>"Maria, it's good to see you again. How have things been since our last session where we discussed diversifying your income streams?" "Hi, Dr. Patel. I've started offering online tutorials in graphic design, which has been bringing in a little extra income. However, I'm still struggling to find consistent, well-paying design work." "That's a positive step, Maria. Have you considered specializing in a particular niche within graphic design? For example, UX/UI design or branding for tech companies?" "I've thought about UX/UI, but it seems like I need more technical skills. I'm not sure where to start." "There are several online boot camps and courses that can equip you with the necessary skills. We can research some that fit your budget and learning style. We should also focus on building your portfolio to showcase your skills in this area."</t>
+  </si>
+  <si>
+    <t>"John, welcome back. In our last meeting, you expressed a strong interest in moving away from construction and towards a career in environmental conservation. How has your job search been progressing?" "Hi, Susan. It's been tough. I've applied for a few park ranger positions, but haven't heard back. I think my resume isn't strong enough." "Let's review your resume again. We can highlight your experience working outdoors and your knowledge of the local environment. Have you considered volunteering with any local conservation organizations? That could provide valuable experience and networking opportunities." "That's a good idea. I hadn't thought of that." "It would also demonstrate your commitment to the field. We can also research relevant certifications or training programs in environmental conservation that might enhance your qualifications."</t>
+  </si>
+  <si>
+    <t>"Hello, Alice. It's good to see you again. How have you been reflecting on our previous discussions about your desire for a less demanding, more flexible career as you approach retirement?" "Hi, David. I've been doing some research into online tutoring and educational consulting. It seems like a good fit, but I'm not sure how to get started." "That sounds promising. Your extensive teaching experience is a valuable asset. We can explore platforms for online tutoring and develop a marketing strategy to reach potential clients. Have you considered networking with other educators who have transitioned to similar roles?" "Not yet. I'm a bit hesitant to put myself out there." "We can work on building your confidence and developing a professional online presence. We can also discuss strategies for setting your rates and managing your workload as a consultant."</t>
+  </si>
+  <si>
+    <t>"Welcome back, James. In our last session, we talked about your interest in moving from tech support to a more specialized role in cybersecurity. Have you made any progress in exploring relevant certifications?" "Hi, Michelle. I've started studying for the CompTIA Security+ exam. It's challenging, but I'm determined to get certified." "That's excellent, James. Have you considered internships or entry-level cybersecurity positions to gain practical experience while you study? Many companies offer opportunities for career growth within the field." "I haven't looked into internships. I thought I needed more experience first." "Gaining practical experience alongside your studies can be very beneficial. We can explore internship programs and entry-level positions that align with your current skills and career goals. We can also refine your resume to highlight your IT background and your commitment to cybersecurity."</t>
+  </si>
+  <si>
+    <t>David: Hi Maria, thanks for seeing me again. I'm still feeling a bit stuck. The networking events you suggested have been helpful, I've made some good contacts, but no concrete job offers yet. I'm starting to wonder if my business degree is pigeonholing me. Maria: I understand your frustration, David. Let's revisit your skills assessment. Remember, your transferable skills are valuable. We identified strong communication, negotiation, and leadership skills. These aren't limited to sales. Have you considered project management or even training and development roles? David: I've thought about project management, but I lack the formal certification. Training…hmm, I’ve mentored junior colleagues, but never formally trained. Maria: That mentoring experience is relevant! We can highlight that. Let's explore project management certifications you could pursue part-time. We can also refine your resume to emphasize those transferable skills and frame your sales experience in a way that appeals to a broader range of employers.</t>
+  </si>
+  <si>
+    <t>Sarah: Aisha, I'm feeling much more confident since our last session. I've revamped my portfolio and started actively pitching to larger publications. I even got a small contract with a magazine! Aisha: That's fantastic, Sarah! I'm so pleased to hear that. Remember our discussion about diversifying your income streams? Have you explored content marketing for businesses? Sarah: I have. I've created a few sample blog posts and reached out to some local businesses. It's a bit outside my comfort zone, but I'm willing to learn. Aisha: Excellent! We can work on your pricing strategy and how to present your services to businesses. We can also explore online platforms for freelance writers to expand your reach.</t>
+  </si>
+  <si>
+    <t>Michael: Kenji, I'm at a crossroads. My current role is stable, but I'm not passionate about it anymore. I'm interested in moving into tech leadership, but I'm not sure I have the right experience. Kenji: I understand, Michael. Let's analyze your current skillset and identify any gaps. You mentioned an interest in leadership. Have you taken any leadership training or workshops? Michael: Not formally. I've led small teams on projects, but nothing substantial. Kenji: That's a good starting point. We can highlight those experiences. We can also look at leadership development programs and certifications that would enhance your profile. We should also discuss how to position yourself for leadership roles in your resume and cover letter.</t>
+  </si>
+  <si>
+    <t>Fatima: Isabelle, I'm feeling a bit discouraged. I've applied for several marketing manager positions, but I haven't even gotten any interviews. I'm starting to doubt myself. Isabelle: Fatima, let's not lose heart. The job market can be competitive. Let's review your resume and cover letter. Are you tailoring them to each specific job you apply for? Fatima: I try to, but sometimes I feel like I'm just tweaking a few words here and there. Isabelle: We need to go deeper than that. We need to showcase how your skills and experience directly align with the requirements of each role. We should also work on your interview skills, particularly how to answer behavioral questions and highlight your accomplishments.</t>
+  </si>
+  <si>
+    <t>Elena: Javier, I'm seriously considering a career change. Teaching is fulfilling, but I'm looking for something more challenging and with better growth potential. I'm interested in project management, but I don't have any direct experience. Javier: Elena, it's never too late for a career change. Your teaching experience has equipped you with valuable transferable skills, such as communication, organization, and leadership. We can highlight these skills and frame them in a way that appeals to project management roles. Elena: Really? I never thought about it that way. Javier: Absolutely. We can also explore project management methodologies and certifications you could pursue to strengthen your profile. We can also discuss how to network with people in the project management field.</t>
+  </si>
+  <si>
+    <t>David: Anika, thanks for seeing me again. I'm still feeling stuck. I've applied for a few marketing roles, but haven't had much luck. I'm starting to wonder if I'm on the right track. Sales is draining me, but I'm not sure if marketing is the answer. Anika: David, it's common to feel this way. Let's revisit your skills assessment. Remember, we identified your strong analytical and communication skills. Marketing uses those, but perhaps we should explore what kind of marketing. Digital marketing is booming. Have you considered that? David: I've dabbled a bit. I took an online course, but it feels overwhelming. Anika: That's understandable. Let's look at some specific digital marketing certifications and training programs. We can also connect you with professionals in the field for informational interviews. This will give you a clearer picture.</t>
+  </si>
+  <si>
+    <t>Maria: Anika, I’m frustrated. My freelance work is inconsistent. Some months are great, others are a struggle. I'm thinking about going back to school for a more stable career. Anika: Maria, let's explore that. You have a strong creative portfolio. Before considering more schooling, have you looked into specializing? UX/UI design is in high demand and utilizes your design skills. Maria: I've heard of it. It sounds technical. Anika: It has a technical component, but your artistic eye is a huge asset. We can research bootcamps and short courses that focus on UX/UI. It's a faster route than a full degree. Let's also discuss your pricing and marketing strategies for your freelance work. Perhaps we can improve your current situation while you explore other options.</t>
+  </si>
+  <si>
+    <t>Kenji: Anika, I appreciate your time. I'm at a crossroads. My career has plateaued. I'm good at what I do, but I'm not passionate anymore. I feel I need a new challenge. Anika: Kenji, many people experience this mid-career. Your experience is valuable. Have you considered transitioning into consulting? Your expertise is highly sought after. Kenji: Consulting? I haven't. I've always been in-house. Anika: It offers more autonomy and variety. We can explore your transferable skills and create a plan to network with consulting firms. We can also look at executive coaching, which leverages your leadership experience.</t>
+  </si>
+  <si>
+    <t>Aisha: Anika, I’m feeling discouraged. I’ve been searching for a job for months. I want to stay in the non-profit sector, but it's so competitive. Anika: Aisha, the non-profit world can be challenging. Let's refine your job search strategy. Your resume highlights your passion, but we need to showcase your quantifiable achievements. Did you increase volunteer participation? Did you manage a specific budget? Aisha: I did manage a small budget for a community outreach program. Anika: Excellent. Let's quantify that. We can also explore related fields, like public health or community development, where your skills might be transferable. We can also work on your interviewing skills.</t>
+  </si>
+  <si>
+    <t>Ben: Anika, I want to advance in IT. I'm comfortable with support, but I want to move into cybersecurity. It seems like the future. Anika: Ben, it's a smart move. Cybersecurity is a growing field. Let's map out a learning path. There are certifications like CompTIA Security+ and CISSP that are highly valued. We can find online courses and resources to prepare you. We can also look at entry-level cybersecurity roles to gain experience while you study. Have you considered specializing in a particular area of cybersecurity? Ben: Not really. It all seems so complex. Anika: It is, but we can break it down. Do any areas interest you more than others, like network security or data protection? Exploring those interests will help you focus your efforts.</t>
+  </si>
+  <si>
+    <t>David: Anya, thanks for seeing me again. I'm still struggling with the idea of leaving sales. I've been doing it for so long, it feels like my only skill. Anya: David, we've discussed this. Your transferable skills are significant. Your communication, negotiation, and client relationship management are valuable in many fields. We've identified project management and client success roles as potential fits. David: I know, but starting over feels daunting. I'm 42. Will anyone hire me? Anya: Absolutely. We'll focus on building a resume and LinkedIn profile that highlights your transferable skills. We'll also explore networking opportunities in your target industries. Remember, many people change careers later in life. Your experience is an asset. David: I appreciate that. I'm just worried about the financial aspect. Sales paid well. Anya: We can research salary expectations in your target roles. We can also discuss bridging strategies, like part-time work or freelance projects, while you transition. David: Okay. Let's work on that resume.</t>
+  </si>
+  <si>
+    <t>Maria: Anya, I’m feeling burnt out. Freelancing is unpredictable. I love the creative aspect, but the business side is overwhelming. Anya: Maria, that’s common. Many creatives struggle with the business management aspects. We’ve discussed your interest in moving into a more stable, team-based environment. Maria: Yes, but I’m worried about losing creative control. Anya: We can explore roles in design agencies or in-house creative teams where you can still utilize your skills while having more structure and support. We can also look at companies that value and nurture creativity. Remember, a stable environment can actually enhance your creativity by reducing stress. Maria: That makes sense. I’m also worried about my portfolio. It’s very freelance-focused. Anya: We can tailor your portfolio to highlight projects that align with the types of roles you’re targeting. We can also work on your interview skills to showcase your collaborative abilities. Maria: Okay. Let’s start with the portfolio.</t>
+  </si>
+  <si>
+    <t>Kenji: Anya, I’m at a crossroads. I’ve been in development for 20 years. I’m good at it, but I’m not passionate anymore. Anya: Kenji, we’ve discussed your interest in moving into management or mentorship roles. Your technical expertise is invaluable. Kenji: I know, but I’m not sure I have the leadership skills. Anya: We can work on developing those skills. We can explore leadership training programs and identify opportunities for you to take on leadership responsibilities in your current role. We can also work on your communication and interpersonal skills. Kenji: That sounds good. I'm also concerned about the work-life balance in management. Anya: That’s a valid concern. We can research companies that prioritize work-life balance and discuss strategies for setting boundaries in a management role. Kenji: Okay. Let’s look at those training programs.</t>
+  </si>
+  <si>
+    <t>Isabelle: Anya, I’m feeling stuck. I love my work, but I’m not seeing a clear career path. Anya: Isabelle, we’ve discussed your passion for sustainability and your interest in moving into a more strategic role. Isabelle: Yes, but I don’t know how to get there. Anya: We can explore further education opportunities, like a Master’s in Environmental Management or Sustainable Business. We can also look at networking opportunities in the sustainability field. Isabelle: I’m hesitant about more school. It’s expensive. Anya: We can research funding options, like scholarships and grants. We can also look at part-time programs that allow you to continue working. We can also identify mentors in the field who can offer guidance. Isabelle: That sounds helpful. Let’s talk about networking.</t>
+  </si>
+  <si>
+    <t>Omar: Anya, I’m thinking about a career change completely. I’ve always been interested in teaching. Anya: Omar, that’s a big decision. We’ve discussed your passion for education and your desire to make a difference. Omar: Yes, but I’m not sure I have the qualifications. Anya: We can research teaching certification requirements in your province. We can also explore alternative pathways into teaching, like teaching in vocational schools or community colleges. We can also discuss the financial implications of a career change. Omar: I’m also worried about my lack of experience in education. Anya: We can explore volunteer teaching opportunities or shadowing experienced teachers to gain some practical experience. We can also highlight your communication and training skills from your engineering background. Omar: Okay. Let’s look at those certification requirements.</t>
+  </si>
+  <si>
+    <t>David: Hi Sarah, thanks for seeing me again. I'm still struggling with the job search. I've sent out dozens of applications, but haven't had any real bites. I'm starting to feel really discouraged. Sarah: I understand, David. Job searching can be tough, especially after a layoff. Let's review your application materials again. Have you tailored your resume and cover letter to each specific job you're applying for? David: I've tried to, but it's hard to keep track. And honestly, sometimes I just feel like I'm throwing applications into a black hole. Sarah: We can work on that. Let's also explore some networking strategies. Have you considered reaching out to people in your field on LinkedIn or attending industry events? David: I haven't really done much of that. I'm not sure where to start. Sarah: We can brainstorm some contacts and create a networking plan. Remember, David, your experience is valuable. We just need to find the right way to showcase it.</t>
+  </si>
+  <si>
+    <t>Maria: Hi Sarah. I'm feeling more and more certain that teaching isn't for me long-term. The stress is burning me out, and I don't see a lot of room for growth. Sarah: I understand. Burnout is a serious issue. What aspects of teaching are you finding most draining, and what parts do you actually enjoy? Maria: I love working with the kids and seeing them learn, but the administrative burden and lack of work-life balance are killing me. Sarah: Okay. Let's explore some related fields that might utilize your skills in education but offer a different environment. Have you thought about corporate training or curriculum development? Maria: Those sound interesting. I haven't really considered them. Sarah: We can research those areas and see what kind of training or certifications you might need. We can also discuss how to highlight your transferable skills on your resume.</t>
+  </si>
+  <si>
+    <t>Kenji: Sarah, I'm ready to make the leap into management. I've been in research for a long time, and I'm ready for a new challenge. Sarah: That's great, Kenji. What kind of management roles are you interested in? Kenji: Ideally, something in R&amp;D or technology. I want to use my technical expertise, but also have more influence on the direction of projects. Sarah: Let's work on framing your resume and cover letter to emphasize your leadership skills, even if they haven't been in a formal management role. We can also discuss strategies for networking with people in management positions. Kenji: I'm a bit hesitant about networking. I'm not very good at self-promotion. Sarah: We can practice some talking points and focus on building genuine connections. It's not about bragging, it's about showcasing your value.</t>
+  </si>
+  <si>
+    <t>Aisha: Sarah, I love being a freelance artist, but the inconsistency is getting to me. I need more stability in my income. Sarah: I understand. The freelance life can be unpredictable. Have you considered any related fields where you could use your artistic skills but have a more regular paycheck? Aisha: Maybe graphic design or illustration? But I don't have formal training in those areas. Sarah: We can explore some online courses or workshops to build your skills in those areas. We can also discuss how to create a portfolio that showcases your artistic abilities. Aisha: That sounds helpful. I'm also worried about the competition. Sarah: It's a competitive field, but your unique artistic style will help you stand out. We can work on developing a strong personal brand and marketing strategy.</t>
+  </si>
+  <si>
+    <t>Ricardo: Sarah, I feel stuck in my current role. I want to move up in IT, but I'm not sure what steps to take. Sarah: Let's discuss your long-term career goals. What kind of IT roles are you interested in? Ricardo: Maybe network administration or cybersecurity. Those areas seem challenging and rewarding. Sarah: Excellent choices. Let's look at the specific skills and certifications required for those roles. We can create a plan to help you acquire those qualifications. Ricardo: I'm also thinking about going back to school to get my bachelor's degree. Sarah: That's a great idea. We can research different programs and discuss how to balance work and studies. We can also explore potential tuition assistance programs.</t>
+  </si>
+  <si>
+    <t>Counselor: "Welcome back, David. In our last session, we discussed your frustration with your current sales role. Have you had any further thoughts about the marketing positions we explored?" David: "Yes, I've been looking at the job descriptions more closely. The Marketing Director role at GreenTech really intrigues me. It aligns with my passion for sustainability, and the leadership aspect is appealing. However, I'm a bit hesitant. I haven't worked directly in marketing, although my sales experience has given me a good understanding of customer needs and market trends." Counselor: "That's a valid point. Your sales background is definitely transferable, but we might need to highlight those transferable skills more effectively on your CV and during interviews. Perhaps we can brainstorm some examples of how your sales achievements demonstrate marketing competencies. Also, have you considered any online marketing courses to bridge the skills gap?" David: "I've looked at a few. I'm thinking of starting one next month. I also networked with someone in marketing at my company, and they suggested I focus on demonstrating my analytical skills, as marketing is becoming increasingly data-driven." Counselor: "Excellent initiative, David. Networking and continuous learning are key. Let’s dedicate our next session to refining your CV and cover letter to emphasize those transferable skills and the steps you're taking to upskill."</t>
+  </si>
+  <si>
+    <t>Counselor: "Maria, it's good to see you again. How have things been since our last meeting when we discussed your desire to move beyond preschool teaching?" Maria: "Hi, John. It's been a bit overwhelming, to be honest. I've been researching different career paths in education, like becoming a teacher's aide in a public school or maybe even working in educational administration. But I feel stuck. I love working with children, but the low pay and lack of growth opportunities in preschool are discouraging." Counselor: "I understand. It's important to find a career that offers both personal fulfillment and financial stability. Have you considered specializing in a particular area of early childhood education, like special needs education? This could open up more opportunities and potentially lead to higher pay." Maria: "That's an interesting idea. I've always been drawn to helping children with learning differences. But I'm not sure if I have the qualifications or the resources to pursue further education." Counselor: "We can explore that. There are grants and scholarships available for educators. We can also look at online programs that offer flexible schedules for working professionals. Let's research some specific programs and funding options for our next session."</t>
+  </si>
+  <si>
+    <t>Counselor: "Welcome back, Michael. I know the layoff has been difficult. How have you been feeling, and have you made any progress in your job search?" Michael: "Thanks, Sarah. It's been tough, but I'm trying to stay positive. I've applied for several software developer positions, but haven't had much luck. The market seems really competitive right now." Counselor: "It is competitive, but your skills are in demand. Let's review your resume and cover letter again. We might need to tailor them more specifically to each job you apply for, highlighting the skills that are most relevant to the position." Michael: "I've been trying to do that, but sometimes I feel like I'm just sending my resume into a black hole." Counselor: "I understand the frustration. Networking can be really helpful in this situation. Have you reached out to any former colleagues or attended any industry events recently?" Michael: "Not really. I haven't felt much like socializing lately." Counselor: "I understand. But networking isn't just about socializing; it's about building connections and learning about potential job opportunities that might not be advertised. Let's work on a networking strategy for you. We can start by identifying some key people in your field and crafting a short, compelling introduction about yourself."</t>
+  </si>
+  <si>
+    <t>Counselor: "Good to see you, Aisha. At our last meeting, we discussed your desire to transition into a more creative field. Have you had any time to reflect on that?" Aisha: "Hi, David. Yes, I've been thinking a lot about it. I'm still drawn to graphic design, but I'm worried about starting over at my age. I also don't have any formal training in design." Counselor: "It's never too late to pursue your passion, Aisha. Many successful designers have transitioned into the field later in life. And while formal training is helpful, there are also many resources available for self-learning, like online courses and tutorials. Have you explored any of those?" Aisha: "I've looked at a few online courses, but I'm not sure if they'll be enough to get me a job." Counselor: "They can be a great starting point. Building a portfolio of your work is also essential. Even if it's just personal projects or volunteer work, showcasing your skills is crucial. We can discuss strategies for building your portfolio and finding opportunities to gain practical experience."</t>
+  </si>
+  <si>
+    <t>Counselor: "Hi, Ben. Welcome back. In our previous sessions, we talked about your interest in moving into a management role within the hospitality industry. How are things progressing?" Ben: "G'day, Sarah. Things are okay. I'm still bartending, but I've been talking to my manager about taking on some more responsibilities, like training new staff. I'm hoping that will help me move up the ladder." Counselor: "That's a great initiative, Ben. Taking on extra responsibilities demonstrates your willingness to learn and grow. Have you considered any further education or training in hospitality management?" Ben: "I've thought about it, but I'm not sure if I can afford it. And I'm also a bit worried about balancing work and study." Counselor: "Those are valid concerns. We can explore different options for funding your education, like scholarships or government assistance programs specifically for Indigenous Australians. There are also flexible study options available, like online courses or part-time programs. Let's research some of those and create a plan that works for you."</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2714,7 +3316,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -2952,26 +3554,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="double">
         <color indexed="64"/>
@@ -2980,17 +3562,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3032,11 +3603,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3105,19 +3702,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3129,10 +3723,34 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3144,31 +3762,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3189,7 +3789,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="test_1" connectionId="1" xr16:uid="{00000000-0016-0000-0300-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="test_1" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3454,33 +4054,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="B1:R107"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:S107"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="28.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="48.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.81640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="48.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.26953125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="7"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -3497,42 +4098,46 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="9"/>
-    </row>
-    <row r="2" spans="2:18" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="35" t="s">
+      <c r="R1" s="8"/>
+      <c r="S1" s="9"/>
+    </row>
+    <row r="2" spans="2:19" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="42" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="37" t="s">
         <v>266</v>
       </c>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="40" t="s">
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
       <c r="P2" s="21"/>
-      <c r="Q2" s="37" t="s">
+      <c r="Q2" s="45" t="s">
+        <v>872</v>
+      </c>
+      <c r="R2" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="R2" s="41" t="s">
+      <c r="S2" s="35" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="36"/>
-      <c r="C3" s="38"/>
+    <row r="3" spans="2:19" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="43"/>
+      <c r="C3" s="34"/>
       <c r="D3" s="11" t="s">
         <v>268</v>
       </c>
@@ -3572,11 +4177,12 @@
       <c r="P3" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="42"/>
-    </row>
-    <row r="4" spans="2:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="33">
+      <c r="Q3" s="46"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="36"/>
+    </row>
+    <row r="4" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="39">
         <v>1</v>
       </c>
       <c r="C4" s="4">
@@ -3621,15 +4227,18 @@
       <c r="P4" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="Q4" s="17" t="s">
+      <c r="Q4" t="s">
+        <v>873</v>
+      </c>
+      <c r="R4" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="33"/>
+      <c r="S4" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B5" s="39"/>
       <c r="C5" s="4">
         <v>2</v>
       </c>
@@ -3672,15 +4281,18 @@
       <c r="P5" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="Q5" s="17" t="s">
+      <c r="Q5" t="s">
+        <v>874</v>
+      </c>
+      <c r="R5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="R5" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B6" s="33"/>
+      <c r="S5" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B6" s="39"/>
       <c r="C6" s="4">
         <v>3</v>
       </c>
@@ -3723,15 +4335,18 @@
       <c r="P6" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="Q6" s="17" t="s">
+      <c r="Q6" t="s">
+        <v>875</v>
+      </c>
+      <c r="R6" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="R6" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B7" s="33"/>
+      <c r="S6" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B7" s="39"/>
       <c r="C7" s="4">
         <v>4</v>
       </c>
@@ -3774,15 +4389,18 @@
       <c r="P7" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="Q7" s="17" t="s">
+      <c r="Q7" t="s">
+        <v>876</v>
+      </c>
+      <c r="R7" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="39"/>
+      <c r="S7" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B8" s="40"/>
       <c r="C8" s="5">
         <v>5</v>
       </c>
@@ -3825,15 +4443,18 @@
       <c r="P8" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="Q8" s="18" t="s">
+      <c r="Q8" t="s">
+        <v>877</v>
+      </c>
+      <c r="R8" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="R8" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="32">
+      <c r="S8" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B9" s="38">
         <v>2</v>
       </c>
       <c r="C9" s="6">
@@ -3878,15 +4499,18 @@
       <c r="P9" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="Q9" s="19" t="s">
+      <c r="Q9" t="s">
+        <v>878</v>
+      </c>
+      <c r="R9" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="R9" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="33"/>
+      <c r="S9" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B10" s="39"/>
       <c r="C10" s="4">
         <v>2</v>
       </c>
@@ -3929,15 +4553,18 @@
       <c r="P10" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="Q10" s="17" t="s">
+      <c r="Q10" t="s">
+        <v>879</v>
+      </c>
+      <c r="R10" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="R10" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="33"/>
+      <c r="S10" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B11" s="39"/>
       <c r="C11" s="4">
         <v>3</v>
       </c>
@@ -3980,15 +4607,18 @@
       <c r="P11" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="Q11" s="29" t="s">
+      <c r="Q11" t="s">
+        <v>880</v>
+      </c>
+      <c r="R11" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="R11" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="33"/>
+      <c r="S11" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B12" s="39"/>
       <c r="C12" s="4">
         <v>4</v>
       </c>
@@ -4031,15 +4661,18 @@
       <c r="P12" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="Q12" s="17" t="s">
+      <c r="Q12" t="s">
+        <v>881</v>
+      </c>
+      <c r="R12" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="R12" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="39"/>
+      <c r="S12" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B13" s="40"/>
       <c r="C13" s="5">
         <v>5</v>
       </c>
@@ -4082,15 +4715,18 @@
       <c r="P13" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="Q13" s="18" t="s">
+      <c r="Q13" t="s">
+        <v>882</v>
+      </c>
+      <c r="R13" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="R13" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="32">
+      <c r="S13" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B14" s="38">
         <v>3</v>
       </c>
       <c r="C14" s="6">
@@ -4135,15 +4771,18 @@
       <c r="P14" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="Q14" s="19" t="s">
+      <c r="Q14" t="s">
+        <v>883</v>
+      </c>
+      <c r="R14" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="R14" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="33"/>
+      <c r="S14" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B15" s="39"/>
       <c r="C15" s="4">
         <v>2</v>
       </c>
@@ -4186,15 +4825,18 @@
       <c r="P15" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="Q15" s="17" t="s">
+      <c r="Q15" t="s">
+        <v>884</v>
+      </c>
+      <c r="R15" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="R15" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="33"/>
+      <c r="S15" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B16" s="39"/>
       <c r="C16" s="4">
         <v>3</v>
       </c>
@@ -4237,15 +4879,18 @@
       <c r="P16" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="Q16" s="17" t="s">
+      <c r="Q16" t="s">
+        <v>885</v>
+      </c>
+      <c r="R16" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="R16" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="33"/>
+      <c r="S16" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B17" s="39"/>
       <c r="C17" s="4">
         <v>4</v>
       </c>
@@ -4288,15 +4933,18 @@
       <c r="P17" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="Q17" s="29" t="s">
+      <c r="Q17" t="s">
+        <v>886</v>
+      </c>
+      <c r="R17" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="R17" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="39"/>
+      <c r="S17" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B18" s="40"/>
       <c r="C18" s="5">
         <v>5</v>
       </c>
@@ -4339,15 +4987,18 @@
       <c r="P18" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="Q18" s="18" t="s">
+      <c r="Q18" t="s">
+        <v>887</v>
+      </c>
+      <c r="R18" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="R18" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="32">
+      <c r="S18" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B19" s="38">
         <v>4</v>
       </c>
       <c r="C19" s="6">
@@ -4392,15 +5043,18 @@
       <c r="P19" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="Q19" s="19" t="s">
+      <c r="Q19" t="s">
+        <v>888</v>
+      </c>
+      <c r="R19" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="R19" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="33"/>
+      <c r="S19" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B20" s="39"/>
       <c r="C20" s="4">
         <v>2</v>
       </c>
@@ -4443,15 +5097,18 @@
       <c r="P20" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="Q20" s="17" t="s">
+      <c r="Q20" t="s">
+        <v>889</v>
+      </c>
+      <c r="R20" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="R20" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="33"/>
+      <c r="S20" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B21" s="39"/>
       <c r="C21" s="4">
         <v>3</v>
       </c>
@@ -4494,15 +5151,18 @@
       <c r="P21" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="Q21" s="17" t="s">
+      <c r="Q21" t="s">
+        <v>890</v>
+      </c>
+      <c r="R21" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="R21" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="33"/>
+      <c r="S21" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B22" s="39"/>
       <c r="C22" s="4">
         <v>4</v>
       </c>
@@ -4545,15 +5205,18 @@
       <c r="P22" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="Q22" s="29" t="s">
+      <c r="Q22" t="s">
+        <v>891</v>
+      </c>
+      <c r="R22" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="R22" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="39"/>
+      <c r="S22" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B23" s="40"/>
       <c r="C23" s="5">
         <v>5</v>
       </c>
@@ -4596,15 +5259,18 @@
       <c r="P23" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="Q23" s="18" t="s">
+      <c r="Q23" t="s">
+        <v>892</v>
+      </c>
+      <c r="R23" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="R23" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="32">
+      <c r="S23" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B24" s="38">
         <v>5</v>
       </c>
       <c r="C24" s="6">
@@ -4649,15 +5315,18 @@
       <c r="P24" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="Q24" s="19" t="s">
+      <c r="Q24" t="s">
+        <v>893</v>
+      </c>
+      <c r="R24" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="R24" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="33"/>
+      <c r="S24" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B25" s="39"/>
       <c r="C25" s="4">
         <v>2</v>
       </c>
@@ -4700,15 +5369,18 @@
       <c r="P25" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="Q25" s="17" t="s">
+      <c r="Q25" t="s">
+        <v>894</v>
+      </c>
+      <c r="R25" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="R25" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="33"/>
+      <c r="S25" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B26" s="39"/>
       <c r="C26" s="4">
         <v>3</v>
       </c>
@@ -4751,15 +5423,18 @@
       <c r="P26" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="Q26" s="29" t="s">
+      <c r="Q26" t="s">
+        <v>895</v>
+      </c>
+      <c r="R26" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="R26" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="33"/>
+      <c r="S26" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B27" s="39"/>
       <c r="C27" s="4">
         <v>4</v>
       </c>
@@ -4802,15 +5477,18 @@
       <c r="P27" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="Q27" s="17" t="s">
+      <c r="Q27" t="s">
+        <v>896</v>
+      </c>
+      <c r="R27" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="R27" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="39"/>
+      <c r="S27" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B28" s="40"/>
       <c r="C28" s="5">
         <v>5</v>
       </c>
@@ -4853,15 +5531,18 @@
       <c r="P28" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="Q28" s="18" t="s">
+      <c r="Q28" t="s">
+        <v>897</v>
+      </c>
+      <c r="R28" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="R28" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="32">
+      <c r="S28" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B29" s="38">
         <v>6</v>
       </c>
       <c r="C29" s="6">
@@ -4906,15 +5587,18 @@
       <c r="P29" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="Q29" s="19" t="s">
+      <c r="Q29" t="s">
+        <v>898</v>
+      </c>
+      <c r="R29" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="R29" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="33"/>
+      <c r="S29" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B30" s="39"/>
       <c r="C30" s="4">
         <v>2</v>
       </c>
@@ -4957,15 +5641,18 @@
       <c r="P30" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="Q30" s="17" t="s">
+      <c r="Q30" t="s">
+        <v>899</v>
+      </c>
+      <c r="R30" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="R30" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B31" s="33"/>
+      <c r="S30" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B31" s="39"/>
       <c r="C31" s="4">
         <v>3</v>
       </c>
@@ -5008,15 +5695,18 @@
       <c r="P31" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="Q31" s="17" t="s">
+      <c r="Q31" t="s">
+        <v>900</v>
+      </c>
+      <c r="R31" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="R31" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B32" s="33"/>
+      <c r="S31" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B32" s="39"/>
       <c r="C32" s="4">
         <v>4</v>
       </c>
@@ -5059,15 +5749,18 @@
       <c r="P32" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="Q32" s="17" t="s">
+      <c r="Q32" t="s">
+        <v>901</v>
+      </c>
+      <c r="R32" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="R32" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B33" s="39"/>
+      <c r="S32" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B33" s="40"/>
       <c r="C33" s="5">
         <v>5</v>
       </c>
@@ -5110,15 +5803,18 @@
       <c r="P33" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="Q33" s="18" t="s">
+      <c r="Q33" t="s">
+        <v>902</v>
+      </c>
+      <c r="R33" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="R33" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B34" s="32">
+      <c r="S33" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B34" s="38">
         <v>7</v>
       </c>
       <c r="C34" s="6">
@@ -5163,15 +5859,18 @@
       <c r="P34" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="Q34" s="19" t="s">
+      <c r="Q34" t="s">
+        <v>903</v>
+      </c>
+      <c r="R34" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="R34" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B35" s="33"/>
+      <c r="S34" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B35" s="39"/>
       <c r="C35" s="4">
         <v>2</v>
       </c>
@@ -5214,15 +5913,18 @@
       <c r="P35" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="Q35" s="29" t="s">
+      <c r="Q35" t="s">
+        <v>904</v>
+      </c>
+      <c r="R35" s="28" t="s">
         <v>314</v>
       </c>
-      <c r="R35" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B36" s="33"/>
+      <c r="S35" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B36" s="39"/>
       <c r="C36" s="4">
         <v>3</v>
       </c>
@@ -5265,15 +5967,18 @@
       <c r="P36" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="Q36" s="17" t="s">
+      <c r="Q36" t="s">
+        <v>905</v>
+      </c>
+      <c r="R36" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="R36" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="33"/>
+      <c r="S36" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B37" s="39"/>
       <c r="C37" s="4">
         <v>4</v>
       </c>
@@ -5316,15 +6021,18 @@
       <c r="P37" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="Q37" s="17" t="s">
+      <c r="Q37" t="s">
+        <v>906</v>
+      </c>
+      <c r="R37" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="R37" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B38" s="39"/>
+      <c r="S37" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B38" s="40"/>
       <c r="C38" s="5">
         <v>5</v>
       </c>
@@ -5367,15 +6075,18 @@
       <c r="P38" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="Q38" s="18" t="s">
+      <c r="Q38" t="s">
+        <v>907</v>
+      </c>
+      <c r="R38" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="R38" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B39" s="32">
+      <c r="S38" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B39" s="38">
         <v>8</v>
       </c>
       <c r="C39" s="6">
@@ -5420,15 +6131,18 @@
       <c r="P39" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="Q39" s="19" t="s">
+      <c r="Q39" t="s">
+        <v>908</v>
+      </c>
+      <c r="R39" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="R39" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="33"/>
+      <c r="S39" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B40" s="39"/>
       <c r="C40" s="4">
         <v>2</v>
       </c>
@@ -5471,15 +6185,18 @@
       <c r="P40" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="Q40" s="17" t="s">
+      <c r="Q40" t="s">
+        <v>909</v>
+      </c>
+      <c r="R40" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="R40" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B41" s="33"/>
+      <c r="S40" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B41" s="39"/>
       <c r="C41" s="4">
         <v>3</v>
       </c>
@@ -5522,15 +6239,18 @@
       <c r="P41" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="Q41" s="17" t="s">
+      <c r="Q41" t="s">
+        <v>910</v>
+      </c>
+      <c r="R41" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="R41" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="33"/>
+      <c r="S41" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B42" s="39"/>
       <c r="C42" s="4">
         <v>4</v>
       </c>
@@ -5573,15 +6293,18 @@
       <c r="P42" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="Q42" s="17" t="s">
+      <c r="Q42" t="s">
+        <v>911</v>
+      </c>
+      <c r="R42" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="R42" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" s="39"/>
+      <c r="S42" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B43" s="40"/>
       <c r="C43" s="5">
         <v>5</v>
       </c>
@@ -5624,15 +6347,18 @@
       <c r="P43" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="Q43" s="30" t="s">
+      <c r="Q43" t="s">
+        <v>912</v>
+      </c>
+      <c r="R43" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="R43" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="32">
+      <c r="S43" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B44" s="38">
         <v>9</v>
       </c>
       <c r="C44" s="6">
@@ -5677,15 +6403,18 @@
       <c r="P44" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="Q44" s="19" t="s">
+      <c r="Q44" t="s">
+        <v>913</v>
+      </c>
+      <c r="R44" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="R44" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B45" s="33"/>
+      <c r="S44" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B45" s="39"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
@@ -5728,15 +6457,18 @@
       <c r="P45" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="Q45" s="17" t="s">
+      <c r="Q45" t="s">
+        <v>914</v>
+      </c>
+      <c r="R45" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="R45" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B46" s="33"/>
+      <c r="S45" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B46" s="39"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
@@ -5779,15 +6511,18 @@
       <c r="P46" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="Q46" s="17" t="s">
+      <c r="Q46" t="s">
+        <v>915</v>
+      </c>
+      <c r="R46" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="R46" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="33"/>
+      <c r="S46" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B47" s="39"/>
       <c r="C47" s="4">
         <v>4</v>
       </c>
@@ -5830,15 +6565,18 @@
       <c r="P47" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="Q47" s="17" t="s">
+      <c r="Q47" t="s">
+        <v>916</v>
+      </c>
+      <c r="R47" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="R47" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B48" s="39"/>
+      <c r="S47" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B48" s="40"/>
       <c r="C48" s="5">
         <v>5</v>
       </c>
@@ -5881,15 +6619,18 @@
       <c r="P48" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="Q48" s="18" t="s">
+      <c r="Q48" t="s">
+        <v>917</v>
+      </c>
+      <c r="R48" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="R48" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B49" s="32">
+      <c r="S48" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="49" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B49" s="38">
         <v>10</v>
       </c>
       <c r="C49" s="6">
@@ -5934,15 +6675,18 @@
       <c r="P49" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="Q49" s="19" t="s">
+      <c r="Q49" t="s">
+        <v>918</v>
+      </c>
+      <c r="R49" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="R49" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B50" s="33"/>
+      <c r="S49" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="50" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B50" s="39"/>
       <c r="C50" s="4">
         <v>2</v>
       </c>
@@ -5985,15 +6729,18 @@
       <c r="P50" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="Q50" s="17" t="s">
+      <c r="Q50" t="s">
+        <v>919</v>
+      </c>
+      <c r="R50" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="R50" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B51" s="33"/>
+      <c r="S50" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="51" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B51" s="39"/>
       <c r="C51" s="4">
         <v>3</v>
       </c>
@@ -6036,15 +6783,18 @@
       <c r="P51" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="Q51" s="17" t="s">
+      <c r="Q51" t="s">
+        <v>920</v>
+      </c>
+      <c r="R51" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="R51" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B52" s="33"/>
+      <c r="S51" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="52" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B52" s="39"/>
       <c r="C52" s="4">
         <v>4</v>
       </c>
@@ -6087,15 +6837,18 @@
       <c r="P52" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="Q52" s="17" t="s">
+      <c r="Q52" t="s">
+        <v>921</v>
+      </c>
+      <c r="R52" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="R52" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="53" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="34"/>
+      <c r="S52" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="53" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="41"/>
       <c r="C53" s="10">
         <v>5</v>
       </c>
@@ -6138,379 +6891,382 @@
       <c r="P53" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="Q53" s="20" t="s">
+      <c r="Q53" t="s">
+        <v>922</v>
+      </c>
+      <c r="R53" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="R53" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="54" spans="2:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="R54" s="23"/>
-    </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S53" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="S54" s="23"/>
+    </row>
+    <row r="55" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
       <c r="F56"/>
     </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
@@ -6518,12 +7274,7 @@
       <c r="F107" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="B44:B48"/>
+  <mergeCells count="17">
     <mergeCell ref="B49:B53"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -6535,6 +7286,12 @@
     <mergeCell ref="B14:B18"/>
     <mergeCell ref="B29:B33"/>
     <mergeCell ref="B24:B28"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="B44:B48"/>
+    <mergeCell ref="Q2:Q3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6542,33 +7299,34 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="B1:R107"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:S107"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="50.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="50.54296875" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.1796875" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="40" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="55.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="40" style="3" customWidth="1"/>
+    <col min="18" max="18" width="55.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.26953125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="7"/>
       <c r="C1" s="8"/>
       <c r="J1" s="8"/>
@@ -6579,43 +7337,47 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="9"/>
-    </row>
-    <row r="2" spans="2:18" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="35" t="s">
+      <c r="R1" s="8"/>
+      <c r="S1" s="9"/>
+    </row>
+    <row r="2" spans="2:19" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="42" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="37" t="s">
         <v>266</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="40" t="s">
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="37" t="s">
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="45" t="s">
+        <v>872</v>
+      </c>
+      <c r="R2" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="R2" s="41" t="s">
+      <c r="S2" s="35" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="36"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="24" t="s">
+    <row r="3" spans="2:19" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="43"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="11" t="s">
         <v>268</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -6630,7 +7392,7 @@
       <c r="H3" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="12" t="s">
         <v>273</v>
       </c>
       <c r="J3" s="11" t="s">
@@ -6654,11 +7416,12 @@
       <c r="P3" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="42"/>
-    </row>
-    <row r="4" spans="2:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="33">
+      <c r="Q3" s="46"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="36"/>
+    </row>
+    <row r="4" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="39">
         <v>1</v>
       </c>
       <c r="C4" s="4">
@@ -6679,7 +7442,7 @@
       <c r="H4" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="I4" s="25" t="s">
+      <c r="I4" s="24" t="s">
         <v>319</v>
       </c>
       <c r="J4" s="17" t="s">
@@ -6703,15 +7466,18 @@
       <c r="P4" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="Q4" s="17" t="s">
+      <c r="Q4" s="44" t="s">
+        <v>923</v>
+      </c>
+      <c r="R4" s="17" t="s">
         <v>478</v>
       </c>
-      <c r="R4" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="33"/>
+      <c r="S4" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B5" s="39"/>
       <c r="C5" s="4">
         <v>2</v>
       </c>
@@ -6754,15 +7520,18 @@
       <c r="P5" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="Q5" s="17" t="s">
+      <c r="Q5" s="44" t="s">
+        <v>924</v>
+      </c>
+      <c r="R5" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="R5" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B6" s="33"/>
+      <c r="S5" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B6" s="39"/>
       <c r="C6" s="4">
         <v>3</v>
       </c>
@@ -6805,15 +7574,18 @@
       <c r="P6" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="Q6" s="17" t="s">
+      <c r="Q6" s="44" t="s">
+        <v>925</v>
+      </c>
+      <c r="R6" s="17" t="s">
         <v>480</v>
       </c>
-      <c r="R6" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B7" s="33"/>
+      <c r="S6" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B7" s="39"/>
       <c r="C7" s="4">
         <v>4</v>
       </c>
@@ -6856,15 +7628,18 @@
       <c r="P7" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="Q7" s="29" t="s">
+      <c r="Q7" s="44" t="s">
+        <v>926</v>
+      </c>
+      <c r="R7" s="28" t="s">
         <v>481</v>
       </c>
-      <c r="R7" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="39"/>
+      <c r="S7" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B8" s="40"/>
       <c r="C8" s="5">
         <v>5</v>
       </c>
@@ -6908,14 +7683,17 @@
         <v>505</v>
       </c>
       <c r="Q8" s="18" t="s">
+        <v>927</v>
+      </c>
+      <c r="R8" s="18" t="s">
         <v>482</v>
       </c>
-      <c r="R8" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="32">
+      <c r="S8" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B9" s="38">
         <v>2</v>
       </c>
       <c r="C9" s="6">
@@ -6961,14 +7739,17 @@
         <v>506</v>
       </c>
       <c r="Q9" s="19" t="s">
+        <v>928</v>
+      </c>
+      <c r="R9" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="R9" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="33"/>
+      <c r="S9" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B10" s="39"/>
       <c r="C10" s="4">
         <v>2</v>
       </c>
@@ -7011,15 +7792,18 @@
       <c r="P10" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="Q10" s="17" t="s">
+      <c r="Q10" s="44" t="s">
+        <v>929</v>
+      </c>
+      <c r="R10" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="R10" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="33"/>
+      <c r="S10" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B11" s="39"/>
       <c r="C11" s="4">
         <v>3</v>
       </c>
@@ -7062,15 +7846,18 @@
       <c r="P11" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="Q11" s="17" t="s">
+      <c r="Q11" s="44" t="s">
+        <v>930</v>
+      </c>
+      <c r="R11" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="R11" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="33"/>
+      <c r="S11" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B12" s="39"/>
       <c r="C12" s="4">
         <v>4</v>
       </c>
@@ -7113,15 +7900,18 @@
       <c r="P12" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="Q12" s="17" t="s">
+      <c r="Q12" s="44" t="s">
+        <v>931</v>
+      </c>
+      <c r="R12" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="R12" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="39"/>
+      <c r="S12" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B13" s="40"/>
       <c r="C13" s="5">
         <v>5</v>
       </c>
@@ -7165,14 +7955,17 @@
         <v>510</v>
       </c>
       <c r="Q13" s="18" t="s">
+        <v>932</v>
+      </c>
+      <c r="R13" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="R13" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="32">
+      <c r="S13" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B14" s="38">
         <v>3</v>
       </c>
       <c r="C14" s="6">
@@ -7218,14 +8011,17 @@
         <v>511</v>
       </c>
       <c r="Q14" s="19" t="s">
+        <v>933</v>
+      </c>
+      <c r="R14" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="R14" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="33"/>
+      <c r="S14" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B15" s="39"/>
       <c r="C15" s="4">
         <v>2</v>
       </c>
@@ -7268,15 +8064,18 @@
       <c r="P15" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="Q15" s="17" t="s">
+      <c r="Q15" s="44" t="s">
+        <v>934</v>
+      </c>
+      <c r="R15" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="R15" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="33"/>
+      <c r="S15" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B16" s="39"/>
       <c r="C16" s="4">
         <v>3</v>
       </c>
@@ -7319,15 +8118,18 @@
       <c r="P16" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="Q16" s="17" t="s">
+      <c r="Q16" s="44" t="s">
+        <v>935</v>
+      </c>
+      <c r="R16" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="R16" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="33"/>
+      <c r="S16" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B17" s="39"/>
       <c r="C17" s="4">
         <v>4</v>
       </c>
@@ -7370,15 +8172,18 @@
       <c r="P17" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="Q17" s="29" t="s">
+      <c r="Q17" s="44" t="s">
+        <v>936</v>
+      </c>
+      <c r="R17" s="28" t="s">
         <v>388</v>
       </c>
-      <c r="R17" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="39"/>
+      <c r="S17" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B18" s="40"/>
       <c r="C18" s="5">
         <v>5</v>
       </c>
@@ -7422,14 +8227,17 @@
         <v>514</v>
       </c>
       <c r="Q18" s="18" t="s">
+        <v>937</v>
+      </c>
+      <c r="R18" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="R18" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="32">
+      <c r="S18" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B19" s="38">
         <v>4</v>
       </c>
       <c r="C19" s="6">
@@ -7475,14 +8283,17 @@
         <v>506</v>
       </c>
       <c r="Q19" s="19" t="s">
+        <v>938</v>
+      </c>
+      <c r="R19" s="19" t="s">
         <v>484</v>
       </c>
-      <c r="R19" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="33"/>
+      <c r="S19" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B20" s="39"/>
       <c r="C20" s="4">
         <v>2</v>
       </c>
@@ -7525,15 +8336,18 @@
       <c r="P20" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="Q20" s="17" t="s">
+      <c r="Q20" s="44" t="s">
+        <v>939</v>
+      </c>
+      <c r="R20" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="R20" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="33"/>
+      <c r="S20" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B21" s="39"/>
       <c r="C21" s="4">
         <v>3</v>
       </c>
@@ -7576,15 +8390,18 @@
       <c r="P21" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="Q21" s="17" t="s">
+      <c r="Q21" s="44" t="s">
+        <v>940</v>
+      </c>
+      <c r="R21" s="17" t="s">
         <v>536</v>
       </c>
-      <c r="R21" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="33"/>
+      <c r="S21" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B22" s="39"/>
       <c r="C22" s="4">
         <v>4</v>
       </c>
@@ -7627,15 +8444,18 @@
       <c r="P22" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="Q22" s="17" t="s">
+      <c r="Q22" s="44" t="s">
+        <v>941</v>
+      </c>
+      <c r="R22" s="17" t="s">
         <v>537</v>
       </c>
-      <c r="R22" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="39"/>
+      <c r="S22" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B23" s="40"/>
       <c r="C23" s="5">
         <v>5</v>
       </c>
@@ -7679,14 +8499,17 @@
         <v>518</v>
       </c>
       <c r="Q23" s="18" t="s">
+        <v>942</v>
+      </c>
+      <c r="R23" s="18" t="s">
         <v>538</v>
       </c>
-      <c r="R23" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="32">
+      <c r="S23" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B24" s="38">
         <v>5</v>
       </c>
       <c r="C24" s="6">
@@ -7732,14 +8555,17 @@
         <v>519</v>
       </c>
       <c r="Q24" s="19" t="s">
+        <v>943</v>
+      </c>
+      <c r="R24" s="19" t="s">
         <v>490</v>
       </c>
-      <c r="R24" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="33"/>
+      <c r="S24" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B25" s="39"/>
       <c r="C25" s="4">
         <v>2</v>
       </c>
@@ -7782,15 +8608,18 @@
       <c r="P25" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="Q25" s="17" t="s">
+      <c r="Q25" s="44" t="s">
+        <v>944</v>
+      </c>
+      <c r="R25" s="17" t="s">
         <v>539</v>
       </c>
-      <c r="R25" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="33"/>
+      <c r="S25" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B26" s="39"/>
       <c r="C26" s="4">
         <v>3</v>
       </c>
@@ -7833,15 +8662,18 @@
       <c r="P26" s="13" t="s">
         <v>520</v>
       </c>
-      <c r="Q26" s="17" t="s">
+      <c r="Q26" s="44" t="s">
+        <v>945</v>
+      </c>
+      <c r="R26" s="17" t="s">
         <v>540</v>
       </c>
-      <c r="R26" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="33"/>
+      <c r="S26" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B27" s="39"/>
       <c r="C27" s="4">
         <v>4</v>
       </c>
@@ -7884,15 +8716,18 @@
       <c r="P27" s="13" t="s">
         <v>521</v>
       </c>
-      <c r="Q27" s="17" t="s">
+      <c r="Q27" s="44" t="s">
+        <v>946</v>
+      </c>
+      <c r="R27" s="17" t="s">
         <v>541</v>
       </c>
-      <c r="R27" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="39"/>
+      <c r="S27" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B28" s="40"/>
       <c r="C28" s="5">
         <v>5</v>
       </c>
@@ -7936,14 +8771,17 @@
         <v>522</v>
       </c>
       <c r="Q28" s="18" t="s">
+        <v>947</v>
+      </c>
+      <c r="R28" s="18" t="s">
         <v>542</v>
       </c>
-      <c r="R28" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="32">
+      <c r="S28" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B29" s="38">
         <v>6</v>
       </c>
       <c r="C29" s="6">
@@ -7989,14 +8827,17 @@
         <v>515</v>
       </c>
       <c r="Q29" s="19" t="s">
+        <v>948</v>
+      </c>
+      <c r="R29" s="19" t="s">
         <v>491</v>
       </c>
-      <c r="R29" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="33"/>
+      <c r="S29" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B30" s="39"/>
       <c r="C30" s="4">
         <v>2</v>
       </c>
@@ -8039,15 +8880,18 @@
       <c r="P30" s="13" t="s">
         <v>523</v>
       </c>
-      <c r="Q30" s="17" t="s">
+      <c r="Q30" s="44" t="s">
+        <v>949</v>
+      </c>
+      <c r="R30" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="R30" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B31" s="33"/>
+      <c r="S30" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B31" s="39"/>
       <c r="C31" s="4">
         <v>3</v>
       </c>
@@ -8090,15 +8934,18 @@
       <c r="P31" s="13" t="s">
         <v>524</v>
       </c>
-      <c r="Q31" s="17" t="s">
+      <c r="Q31" s="44" t="s">
+        <v>950</v>
+      </c>
+      <c r="R31" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="R31" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B32" s="33"/>
+      <c r="S31" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B32" s="39"/>
       <c r="C32" s="4">
         <v>4</v>
       </c>
@@ -8141,15 +8988,18 @@
       <c r="P32" s="13" t="s">
         <v>525</v>
       </c>
-      <c r="Q32" s="17" t="s">
+      <c r="Q32" s="44" t="s">
+        <v>951</v>
+      </c>
+      <c r="R32" s="17" t="s">
         <v>543</v>
       </c>
-      <c r="R32" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B33" s="39"/>
+      <c r="S32" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B33" s="40"/>
       <c r="C33" s="5">
         <v>5</v>
       </c>
@@ -8193,14 +9043,17 @@
         <v>526</v>
       </c>
       <c r="Q33" s="18" t="s">
+        <v>952</v>
+      </c>
+      <c r="R33" s="18" t="s">
         <v>544</v>
       </c>
-      <c r="R33" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B34" s="32">
+      <c r="S33" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B34" s="38">
         <v>7</v>
       </c>
       <c r="C34" s="6">
@@ -8246,14 +9099,17 @@
         <v>527</v>
       </c>
       <c r="Q34" s="19" t="s">
+        <v>953</v>
+      </c>
+      <c r="R34" s="19" t="s">
         <v>490</v>
       </c>
-      <c r="R34" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B35" s="33"/>
+      <c r="S34" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B35" s="39"/>
       <c r="C35" s="4">
         <v>2</v>
       </c>
@@ -8296,15 +9152,18 @@
       <c r="P35" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="Q35" s="17" t="s">
+      <c r="Q35" s="44" t="s">
+        <v>954</v>
+      </c>
+      <c r="R35" s="17" t="s">
         <v>545</v>
       </c>
-      <c r="R35" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B36" s="33"/>
+      <c r="S35" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B36" s="39"/>
       <c r="C36" s="4">
         <v>3</v>
       </c>
@@ -8347,15 +9206,18 @@
       <c r="P36" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="Q36" s="17" t="s">
+      <c r="Q36" s="44" t="s">
+        <v>955</v>
+      </c>
+      <c r="R36" s="17" t="s">
         <v>546</v>
       </c>
-      <c r="R36" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="33"/>
+      <c r="S36" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B37" s="39"/>
       <c r="C37" s="4">
         <v>4</v>
       </c>
@@ -8398,15 +9260,18 @@
       <c r="P37" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="Q37" s="17" t="s">
+      <c r="Q37" s="44" t="s">
+        <v>956</v>
+      </c>
+      <c r="R37" s="17" t="s">
         <v>547</v>
       </c>
-      <c r="R37" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B38" s="39"/>
+      <c r="S37" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B38" s="40"/>
       <c r="C38" s="5">
         <v>5</v>
       </c>
@@ -8450,14 +9315,17 @@
         <v>507</v>
       </c>
       <c r="Q38" s="18" t="s">
+        <v>957</v>
+      </c>
+      <c r="R38" s="18" t="s">
         <v>548</v>
       </c>
-      <c r="R38" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B39" s="32">
+      <c r="S38" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B39" s="38">
         <v>8</v>
       </c>
       <c r="C39" s="6">
@@ -8503,14 +9371,17 @@
         <v>519</v>
       </c>
       <c r="Q39" s="19" t="s">
+        <v>958</v>
+      </c>
+      <c r="R39" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="R39" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="33"/>
+      <c r="S39" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B40" s="39"/>
       <c r="C40" s="4">
         <v>2</v>
       </c>
@@ -8553,15 +9424,18 @@
       <c r="P40" s="13" t="s">
         <v>530</v>
       </c>
-      <c r="Q40" s="17" t="s">
+      <c r="Q40" s="44" t="s">
+        <v>959</v>
+      </c>
+      <c r="R40" s="17" t="s">
         <v>443</v>
       </c>
-      <c r="R40" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B41" s="33"/>
+      <c r="S40" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B41" s="39"/>
       <c r="C41" s="4">
         <v>3</v>
       </c>
@@ -8604,15 +9478,18 @@
       <c r="P41" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="Q41" s="17" t="s">
+      <c r="Q41" s="44" t="s">
+        <v>960</v>
+      </c>
+      <c r="R41" s="17" t="s">
         <v>447</v>
       </c>
-      <c r="R41" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="33"/>
+      <c r="S41" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B42" s="39"/>
       <c r="C42" s="4">
         <v>4</v>
       </c>
@@ -8655,15 +9532,18 @@
       <c r="P42" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="Q42" s="17" t="s">
+      <c r="Q42" s="44" t="s">
+        <v>961</v>
+      </c>
+      <c r="R42" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="R42" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" s="39"/>
+      <c r="S42" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B43" s="40"/>
       <c r="C43" s="5">
         <v>5</v>
       </c>
@@ -8706,15 +9586,18 @@
       <c r="P43" s="14" t="s">
         <v>520</v>
       </c>
-      <c r="Q43" s="30" t="s">
+      <c r="Q43" s="18" t="s">
+        <v>962</v>
+      </c>
+      <c r="R43" s="29" t="s">
         <v>454</v>
       </c>
-      <c r="R43" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="32">
+      <c r="S43" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B44" s="38">
         <v>9</v>
       </c>
       <c r="C44" s="6">
@@ -8758,14 +9641,17 @@
         <v>532</v>
       </c>
       <c r="Q44" s="19" t="s">
+        <v>963</v>
+      </c>
+      <c r="R44" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="R44" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B45" s="33"/>
+      <c r="S44" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B45" s="39"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
@@ -8806,15 +9692,18 @@
       <c r="P45" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="Q45" s="17" t="s">
+      <c r="Q45" s="44" t="s">
+        <v>964</v>
+      </c>
+      <c r="R45" s="17" t="s">
         <v>494</v>
       </c>
-      <c r="R45" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B46" s="33"/>
+      <c r="S45" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B46" s="39"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
@@ -8855,15 +9744,18 @@
       <c r="P46" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="Q46" s="17" t="s">
+      <c r="Q46" s="44" t="s">
+        <v>965</v>
+      </c>
+      <c r="R46" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="R46" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="33"/>
+      <c r="S46" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B47" s="39"/>
       <c r="C47" s="4">
         <v>4</v>
       </c>
@@ -8904,15 +9796,18 @@
       <c r="P47" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="Q47" s="17" t="s">
+      <c r="Q47" s="44" t="s">
+        <v>966</v>
+      </c>
+      <c r="R47" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="R47" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B48" s="39"/>
+      <c r="S47" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B48" s="40"/>
       <c r="C48" s="5">
         <v>5</v>
       </c>
@@ -8954,14 +9849,17 @@
         <v>526</v>
       </c>
       <c r="Q48" s="18" t="s">
+        <v>967</v>
+      </c>
+      <c r="R48" s="18" t="s">
         <v>500</v>
       </c>
-      <c r="R48" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B49" s="32">
+      <c r="S48" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="49" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B49" s="38">
         <v>10</v>
       </c>
       <c r="C49" s="6">
@@ -9006,15 +9904,18 @@
       <c r="P49" s="15" t="s">
         <v>506</v>
       </c>
-      <c r="Q49" s="31" t="s">
+      <c r="Q49" s="19" t="s">
+        <v>968</v>
+      </c>
+      <c r="R49" s="30" t="s">
         <v>549</v>
       </c>
-      <c r="R49" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B50" s="33"/>
+      <c r="S49" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="50" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B50" s="39"/>
       <c r="C50" s="4">
         <v>2</v>
       </c>
@@ -9057,15 +9958,18 @@
       <c r="P50" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="Q50" s="17" t="s">
+      <c r="Q50" s="44" t="s">
+        <v>969</v>
+      </c>
+      <c r="R50" s="17" t="s">
         <v>501</v>
       </c>
-      <c r="R50" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B51" s="33"/>
+      <c r="S50" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="51" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B51" s="39"/>
       <c r="C51" s="4">
         <v>3</v>
       </c>
@@ -9108,15 +10012,18 @@
       <c r="P51" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="Q51" s="17" t="s">
+      <c r="Q51" s="44" t="s">
+        <v>970</v>
+      </c>
+      <c r="R51" s="17" t="s">
         <v>550</v>
       </c>
-      <c r="R51" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B52" s="33"/>
+      <c r="S51" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="52" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B52" s="39"/>
       <c r="C52" s="4">
         <v>4</v>
       </c>
@@ -9159,15 +10066,18 @@
       <c r="P52" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="Q52" s="17" t="s">
+      <c r="Q52" s="44" t="s">
+        <v>971</v>
+      </c>
+      <c r="R52" s="17" t="s">
         <v>551</v>
       </c>
-      <c r="R52" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="53" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="34"/>
+      <c r="S52" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="53" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="41"/>
       <c r="C53" s="10">
         <v>5</v>
       </c>
@@ -9211,378 +10121,381 @@
         <v>534</v>
       </c>
       <c r="Q53" s="20" t="s">
+        <v>972</v>
+      </c>
+      <c r="R53" s="20" t="s">
         <v>552</v>
       </c>
-      <c r="R53" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="54" spans="2:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="R54" s="23"/>
-    </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S53" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="S54" s="23"/>
+    </row>
+    <row r="55" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
       <c r="F56"/>
     </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
@@ -9590,7 +10503,14 @@
       <c r="F107" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="R2:R3"/>
     <mergeCell ref="B34:B38"/>
     <mergeCell ref="B39:B43"/>
     <mergeCell ref="B44:B48"/>
@@ -9601,12 +10521,6 @@
     <mergeCell ref="B19:B23"/>
     <mergeCell ref="B24:B28"/>
     <mergeCell ref="B29:B33"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="Q2:Q3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9614,33 +10528,34 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="B1:R107"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:S107"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="63.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="55.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="63.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="63.26953125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="55.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.26953125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="7"/>
       <c r="C1" s="8"/>
       <c r="J1" s="8"/>
@@ -9651,43 +10566,47 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="9"/>
-    </row>
-    <row r="2" spans="2:18" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="35" t="s">
+      <c r="R1" s="8"/>
+      <c r="S1" s="9"/>
+    </row>
+    <row r="2" spans="2:19" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="42" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="37" t="s">
         <v>266</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="40" t="s">
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="37" t="s">
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="45" t="s">
+        <v>872</v>
+      </c>
+      <c r="R2" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="R2" s="41" t="s">
+      <c r="S2" s="35" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="36"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="24" t="s">
+    <row r="3" spans="2:19" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="43"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="11" t="s">
         <v>268</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -9702,7 +10621,7 @@
       <c r="H3" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="12" t="s">
         <v>273</v>
       </c>
       <c r="J3" s="11" t="s">
@@ -9726,11 +10645,12 @@
       <c r="P3" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="42"/>
-    </row>
-    <row r="4" spans="2:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="33">
+      <c r="Q3" s="46"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="36"/>
+    </row>
+    <row r="4" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="39">
         <v>1</v>
       </c>
       <c r="C4" s="4">
@@ -9751,7 +10671,7 @@
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="25" t="s">
+      <c r="I4" s="24" t="s">
         <v>153</v>
       </c>
       <c r="J4" s="17" t="s">
@@ -9775,15 +10695,18 @@
       <c r="P4" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="Q4" s="17" t="s">
+      <c r="Q4" t="s">
+        <v>973</v>
+      </c>
+      <c r="R4" s="17" t="s">
         <v>555</v>
       </c>
-      <c r="R4" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="33"/>
+      <c r="S4" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B5" s="39"/>
       <c r="C5" s="4">
         <v>2</v>
       </c>
@@ -9826,15 +10749,18 @@
       <c r="P5" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="Q5" s="17" t="s">
+      <c r="Q5" t="s">
+        <v>974</v>
+      </c>
+      <c r="R5" s="17" t="s">
         <v>559</v>
       </c>
-      <c r="R5" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B6" s="33"/>
+      <c r="S5" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B6" s="39"/>
       <c r="C6" s="4">
         <v>3</v>
       </c>
@@ -9877,15 +10803,18 @@
       <c r="P6" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="Q6" s="17" t="s">
+      <c r="Q6" t="s">
+        <v>975</v>
+      </c>
+      <c r="R6" s="17" t="s">
         <v>564</v>
       </c>
-      <c r="R6" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B7" s="33"/>
+      <c r="S6" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B7" s="39"/>
       <c r="C7" s="4">
         <v>4</v>
       </c>
@@ -9928,15 +10857,18 @@
       <c r="P7" s="13" t="s">
         <v>568</v>
       </c>
-      <c r="Q7" s="17" t="s">
+      <c r="Q7" t="s">
+        <v>976</v>
+      </c>
+      <c r="R7" s="17" t="s">
         <v>569</v>
       </c>
-      <c r="R7" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="39"/>
+      <c r="S7" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B8" s="40"/>
       <c r="C8" s="5">
         <v>5</v>
       </c>
@@ -9979,15 +10911,18 @@
       <c r="P8" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="Q8" s="18" t="s">
+      <c r="Q8" t="s">
+        <v>977</v>
+      </c>
+      <c r="R8" s="18" t="s">
         <v>573</v>
       </c>
-      <c r="R8" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="32">
+      <c r="S8" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B9" s="38">
         <v>2</v>
       </c>
       <c r="C9" s="6">
@@ -10032,15 +10967,18 @@
       <c r="P9" s="15" t="s">
         <v>679</v>
       </c>
-      <c r="Q9" s="19" t="s">
+      <c r="Q9" t="s">
+        <v>978</v>
+      </c>
+      <c r="R9" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="R9" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="33"/>
+      <c r="S9" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B10" s="39"/>
       <c r="C10" s="4">
         <v>2</v>
       </c>
@@ -10083,15 +11021,18 @@
       <c r="P10" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="Q10" s="17" t="s">
+      <c r="Q10" t="s">
+        <v>979</v>
+      </c>
+      <c r="R10" s="17" t="s">
         <v>579</v>
       </c>
-      <c r="R10" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="33"/>
+      <c r="S10" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B11" s="39"/>
       <c r="C11" s="4">
         <v>3</v>
       </c>
@@ -10134,15 +11075,18 @@
       <c r="P11" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="Q11" s="17" t="s">
+      <c r="Q11" t="s">
+        <v>980</v>
+      </c>
+      <c r="R11" s="17" t="s">
         <v>581</v>
       </c>
-      <c r="R11" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="33"/>
+      <c r="S11" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B12" s="39"/>
       <c r="C12" s="4">
         <v>4</v>
       </c>
@@ -10185,15 +11129,18 @@
       <c r="P12" s="13" t="s">
         <v>680</v>
       </c>
-      <c r="Q12" s="17" t="s">
+      <c r="Q12" t="s">
+        <v>981</v>
+      </c>
+      <c r="R12" s="17" t="s">
         <v>585</v>
       </c>
-      <c r="R12" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="39"/>
+      <c r="S12" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B13" s="40"/>
       <c r="C13" s="5">
         <v>5</v>
       </c>
@@ -10236,15 +11183,18 @@
       <c r="P13" s="14" t="s">
         <v>681</v>
       </c>
-      <c r="Q13" s="18" t="s">
+      <c r="Q13" t="s">
+        <v>982</v>
+      </c>
+      <c r="R13" s="18" t="s">
         <v>589</v>
       </c>
-      <c r="R13" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="32">
+      <c r="S13" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B14" s="38">
         <v>3</v>
       </c>
       <c r="C14" s="6">
@@ -10289,15 +11239,18 @@
       <c r="P14" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="Q14" s="19" t="s">
+      <c r="Q14" t="s">
+        <v>983</v>
+      </c>
+      <c r="R14" s="19" t="s">
         <v>678</v>
       </c>
-      <c r="R14" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="33"/>
+      <c r="S14" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B15" s="39"/>
       <c r="C15" s="4">
         <v>2</v>
       </c>
@@ -10340,15 +11293,18 @@
       <c r="P15" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="Q15" s="17" t="s">
+      <c r="Q15" t="s">
+        <v>984</v>
+      </c>
+      <c r="R15" s="17" t="s">
         <v>594</v>
       </c>
-      <c r="R15" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="33"/>
+      <c r="S15" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B16" s="39"/>
       <c r="C16" s="4">
         <v>3</v>
       </c>
@@ -10391,15 +11347,18 @@
       <c r="P16" s="13" t="s">
         <v>682</v>
       </c>
-      <c r="Q16" s="17" t="s">
+      <c r="Q16" t="s">
+        <v>985</v>
+      </c>
+      <c r="R16" s="17" t="s">
         <v>564</v>
       </c>
-      <c r="R16" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="33"/>
+      <c r="S16" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B17" s="39"/>
       <c r="C17" s="4">
         <v>4</v>
       </c>
@@ -10442,15 +11401,18 @@
       <c r="P17" s="13" t="s">
         <v>683</v>
       </c>
-      <c r="Q17" s="17" t="s">
+      <c r="Q17" t="s">
+        <v>986</v>
+      </c>
+      <c r="R17" s="17" t="s">
         <v>599</v>
       </c>
-      <c r="R17" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="39"/>
+      <c r="S17" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B18" s="40"/>
       <c r="C18" s="5">
         <v>5</v>
       </c>
@@ -10493,15 +11455,18 @@
       <c r="P18" s="14" t="s">
         <v>515</v>
       </c>
-      <c r="Q18" s="18" t="s">
+      <c r="Q18" t="s">
+        <v>987</v>
+      </c>
+      <c r="R18" s="18" t="s">
         <v>603</v>
       </c>
-      <c r="R18" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="32">
+      <c r="S18" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B19" s="38">
         <v>4</v>
       </c>
       <c r="C19" s="6">
@@ -10546,15 +11511,18 @@
       <c r="P19" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="Q19" s="19" t="s">
+      <c r="Q19" t="s">
+        <v>988</v>
+      </c>
+      <c r="R19" s="19" t="s">
         <v>604</v>
       </c>
-      <c r="R19" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="33"/>
+      <c r="S19" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B20" s="39"/>
       <c r="C20" s="4">
         <v>2</v>
       </c>
@@ -10597,15 +11565,18 @@
       <c r="P20" s="13" t="s">
         <v>686</v>
       </c>
-      <c r="Q20" s="17" t="s">
+      <c r="Q20" t="s">
+        <v>989</v>
+      </c>
+      <c r="R20" s="17" t="s">
         <v>607</v>
       </c>
-      <c r="R20" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="33"/>
+      <c r="S20" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B21" s="39"/>
       <c r="C21" s="4">
         <v>3</v>
       </c>
@@ -10648,15 +11619,18 @@
       <c r="P21" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="Q21" s="17" t="s">
+      <c r="Q21" t="s">
+        <v>990</v>
+      </c>
+      <c r="R21" s="17" t="s">
         <v>564</v>
       </c>
-      <c r="R21" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="33"/>
+      <c r="S21" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B22" s="39"/>
       <c r="C22" s="4">
         <v>4</v>
       </c>
@@ -10699,15 +11673,18 @@
       <c r="P22" s="13" t="s">
         <v>687</v>
       </c>
-      <c r="Q22" s="17" t="s">
+      <c r="Q22" t="s">
+        <v>991</v>
+      </c>
+      <c r="R22" s="17" t="s">
         <v>612</v>
       </c>
-      <c r="R22" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="39"/>
+      <c r="S22" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B23" s="40"/>
       <c r="C23" s="5">
         <v>5</v>
       </c>
@@ -10750,15 +11727,18 @@
       <c r="P23" s="14" t="s">
         <v>688</v>
       </c>
-      <c r="Q23" s="18" t="s">
+      <c r="Q23" t="s">
+        <v>992</v>
+      </c>
+      <c r="R23" s="18" t="s">
         <v>618</v>
       </c>
-      <c r="R23" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="32">
+      <c r="S23" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B24" s="38">
         <v>5</v>
       </c>
       <c r="C24" s="6">
@@ -10803,15 +11783,18 @@
       <c r="P24" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="Q24" s="19" t="s">
+      <c r="Q24" t="s">
+        <v>993</v>
+      </c>
+      <c r="R24" s="19" t="s">
         <v>619</v>
       </c>
-      <c r="R24" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="33"/>
+      <c r="S24" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B25" s="39"/>
       <c r="C25" s="4">
         <v>2</v>
       </c>
@@ -10854,15 +11837,18 @@
       <c r="P25" s="13" t="s">
         <v>689</v>
       </c>
-      <c r="Q25" s="17" t="s">
+      <c r="Q25" t="s">
+        <v>994</v>
+      </c>
+      <c r="R25" s="17" t="s">
         <v>564</v>
       </c>
-      <c r="R25" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="33"/>
+      <c r="S25" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B26" s="39"/>
       <c r="C26" s="4">
         <v>3</v>
       </c>
@@ -10905,15 +11891,18 @@
       <c r="P26" s="13" t="s">
         <v>690</v>
       </c>
-      <c r="Q26" s="17" t="s">
+      <c r="Q26" t="s">
+        <v>995</v>
+      </c>
+      <c r="R26" s="17" t="s">
         <v>622</v>
       </c>
-      <c r="R26" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="33"/>
+      <c r="S26" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B27" s="39"/>
       <c r="C27" s="4">
         <v>4</v>
       </c>
@@ -10956,15 +11945,18 @@
       <c r="P27" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="Q27" s="17" t="s">
+      <c r="Q27" t="s">
+        <v>996</v>
+      </c>
+      <c r="R27" s="17" t="s">
         <v>626</v>
       </c>
-      <c r="R27" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="39"/>
+      <c r="S27" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B28" s="40"/>
       <c r="C28" s="5">
         <v>5</v>
       </c>
@@ -11007,15 +11999,18 @@
       <c r="P28" s="14" t="s">
         <v>515</v>
       </c>
-      <c r="Q28" s="18" t="s">
+      <c r="Q28" t="s">
+        <v>997</v>
+      </c>
+      <c r="R28" s="18" t="s">
         <v>628</v>
       </c>
-      <c r="R28" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="32">
+      <c r="S28" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B29" s="38">
         <v>6</v>
       </c>
       <c r="C29" s="6">
@@ -11060,15 +12055,18 @@
       <c r="P29" s="15" t="s">
         <v>506</v>
       </c>
-      <c r="Q29" s="19" t="s">
+      <c r="Q29" t="s">
+        <v>998</v>
+      </c>
+      <c r="R29" s="19" t="s">
         <v>629</v>
       </c>
-      <c r="R29" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="33"/>
+      <c r="S29" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B30" s="39"/>
       <c r="C30" s="4">
         <v>2</v>
       </c>
@@ -11111,15 +12109,18 @@
       <c r="P30" s="13" t="s">
         <v>686</v>
       </c>
-      <c r="Q30" s="17" t="s">
+      <c r="Q30" t="s">
+        <v>999</v>
+      </c>
+      <c r="R30" s="17" t="s">
         <v>607</v>
       </c>
-      <c r="R30" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B31" s="33"/>
+      <c r="S30" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B31" s="39"/>
       <c r="C31" s="4">
         <v>3</v>
       </c>
@@ -11162,15 +12163,18 @@
       <c r="P31" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="Q31" s="17" t="s">
+      <c r="Q31" t="s">
+        <v>1000</v>
+      </c>
+      <c r="R31" s="17" t="s">
         <v>630</v>
       </c>
-      <c r="R31" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B32" s="33"/>
+      <c r="S31" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B32" s="39"/>
       <c r="C32" s="4">
         <v>4</v>
       </c>
@@ -11213,15 +12217,18 @@
       <c r="P32" s="13" t="s">
         <v>692</v>
       </c>
-      <c r="Q32" s="17" t="s">
+      <c r="Q32" t="s">
+        <v>1001</v>
+      </c>
+      <c r="R32" s="17" t="s">
         <v>632</v>
       </c>
-      <c r="R32" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B33" s="39"/>
+      <c r="S32" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B33" s="40"/>
       <c r="C33" s="5">
         <v>5</v>
       </c>
@@ -11264,15 +12271,18 @@
       <c r="P33" s="14" t="s">
         <v>693</v>
       </c>
-      <c r="Q33" s="18" t="s">
+      <c r="Q33" t="s">
+        <v>1002</v>
+      </c>
+      <c r="R33" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="R33" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B34" s="32">
+      <c r="S33" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B34" s="38">
         <v>7</v>
       </c>
       <c r="C34" s="6">
@@ -11317,15 +12327,18 @@
       <c r="P34" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="Q34" s="19" t="s">
+      <c r="Q34" t="s">
+        <v>1003</v>
+      </c>
+      <c r="R34" s="19" t="s">
         <v>639</v>
       </c>
-      <c r="R34" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B35" s="33"/>
+      <c r="S34" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B35" s="39"/>
       <c r="C35" s="4">
         <v>2</v>
       </c>
@@ -11368,15 +12381,18 @@
       <c r="P35" s="13" t="s">
         <v>694</v>
       </c>
-      <c r="Q35" s="17" t="s">
+      <c r="Q35" t="s">
+        <v>1004</v>
+      </c>
+      <c r="R35" s="17" t="s">
         <v>640</v>
       </c>
-      <c r="R35" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B36" s="33"/>
+      <c r="S35" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B36" s="39"/>
       <c r="C36" s="4">
         <v>3</v>
       </c>
@@ -11419,15 +12435,18 @@
       <c r="P36" s="13" t="s">
         <v>695</v>
       </c>
-      <c r="Q36" s="17" t="s">
+      <c r="Q36" t="s">
+        <v>1005</v>
+      </c>
+      <c r="R36" s="17" t="s">
         <v>644</v>
       </c>
-      <c r="R36" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="33"/>
+      <c r="S36" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B37" s="39"/>
       <c r="C37" s="4">
         <v>4</v>
       </c>
@@ -11470,15 +12489,18 @@
       <c r="P37" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="Q37" s="17" t="s">
+      <c r="Q37" t="s">
+        <v>1006</v>
+      </c>
+      <c r="R37" s="17" t="s">
         <v>626</v>
       </c>
-      <c r="R37" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B38" s="39"/>
+      <c r="S37" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B38" s="40"/>
       <c r="C38" s="5">
         <v>5</v>
       </c>
@@ -11521,15 +12543,18 @@
       <c r="P38" s="14" t="s">
         <v>696</v>
       </c>
-      <c r="Q38" s="18" t="s">
+      <c r="Q38" t="s">
+        <v>1007</v>
+      </c>
+      <c r="R38" s="18" t="s">
         <v>647</v>
       </c>
-      <c r="R38" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B39" s="32">
+      <c r="S38" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B39" s="38">
         <v>8</v>
       </c>
       <c r="C39" s="6">
@@ -11574,15 +12599,18 @@
       <c r="P39" s="15" t="s">
         <v>697</v>
       </c>
-      <c r="Q39" s="19" t="s">
+      <c r="Q39" t="s">
+        <v>1008</v>
+      </c>
+      <c r="R39" s="19" t="s">
         <v>649</v>
       </c>
-      <c r="R39" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="33"/>
+      <c r="S39" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B40" s="39"/>
       <c r="C40" s="4">
         <v>2</v>
       </c>
@@ -11625,15 +12653,18 @@
       <c r="P40" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="Q40" s="17" t="s">
+      <c r="Q40" t="s">
+        <v>1009</v>
+      </c>
+      <c r="R40" s="17" t="s">
         <v>684</v>
       </c>
-      <c r="R40" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B41" s="33"/>
+      <c r="S40" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B41" s="39"/>
       <c r="C41" s="4">
         <v>3</v>
       </c>
@@ -11676,15 +12707,18 @@
       <c r="P41" s="13" t="s">
         <v>698</v>
       </c>
-      <c r="Q41" s="17" t="s">
+      <c r="Q41" t="s">
+        <v>1010</v>
+      </c>
+      <c r="R41" s="17" t="s">
         <v>652</v>
       </c>
-      <c r="R41" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="33"/>
+      <c r="S41" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B42" s="39"/>
       <c r="C42" s="4">
         <v>4</v>
       </c>
@@ -11727,15 +12761,18 @@
       <c r="P42" s="13" t="s">
         <v>699</v>
       </c>
-      <c r="Q42" s="17" t="s">
+      <c r="Q42" t="s">
+        <v>1011</v>
+      </c>
+      <c r="R42" s="17" t="s">
         <v>656</v>
       </c>
-      <c r="R42" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" s="39"/>
+      <c r="S42" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B43" s="40"/>
       <c r="C43" s="5">
         <v>5</v>
       </c>
@@ -11778,15 +12815,18 @@
       <c r="P43" s="14" t="s">
         <v>700</v>
       </c>
-      <c r="Q43" s="18" t="s">
+      <c r="Q43" t="s">
+        <v>1012</v>
+      </c>
+      <c r="R43" s="18" t="s">
         <v>685</v>
       </c>
-      <c r="R43" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="32">
+      <c r="S43" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B44" s="38">
         <v>9</v>
       </c>
       <c r="C44" s="6">
@@ -11831,15 +12871,18 @@
       <c r="P44" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="Q44" s="19" t="s">
+      <c r="Q44" t="s">
+        <v>1013</v>
+      </c>
+      <c r="R44" s="19" t="s">
         <v>659</v>
       </c>
-      <c r="R44" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B45" s="33"/>
+      <c r="S44" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B45" s="39"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
@@ -11882,15 +12925,18 @@
       <c r="P45" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="Q45" s="17" t="s">
+      <c r="Q45" t="s">
+        <v>1014</v>
+      </c>
+      <c r="R45" s="17" t="s">
         <v>661</v>
       </c>
-      <c r="R45" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B46" s="33"/>
+      <c r="S45" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B46" s="39"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
@@ -11933,15 +12979,18 @@
       <c r="P46" s="13" t="s">
         <v>701</v>
       </c>
-      <c r="Q46" s="17" t="s">
+      <c r="Q46" t="s">
+        <v>1015</v>
+      </c>
+      <c r="R46" s="17" t="s">
         <v>664</v>
       </c>
-      <c r="R46" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="33"/>
+      <c r="S46" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B47" s="39"/>
       <c r="C47" s="4">
         <v>4</v>
       </c>
@@ -11984,15 +13033,18 @@
       <c r="P47" s="13" t="s">
         <v>702</v>
       </c>
-      <c r="Q47" s="17" t="s">
+      <c r="Q47" t="s">
+        <v>1016</v>
+      </c>
+      <c r="R47" s="17" t="s">
         <v>667</v>
       </c>
-      <c r="R47" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B48" s="39"/>
+      <c r="S47" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B48" s="40"/>
       <c r="C48" s="5">
         <v>5</v>
       </c>
@@ -12035,15 +13087,18 @@
       <c r="P48" s="14" t="s">
         <v>681</v>
       </c>
-      <c r="Q48" s="18" t="s">
+      <c r="Q48" t="s">
+        <v>1017</v>
+      </c>
+      <c r="R48" s="18" t="s">
         <v>671</v>
       </c>
-      <c r="R48" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B49" s="32">
+      <c r="S48" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="49" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B49" s="38">
         <v>10</v>
       </c>
       <c r="C49" s="6">
@@ -12088,15 +13143,18 @@
       <c r="P49" s="15" t="s">
         <v>506</v>
       </c>
-      <c r="Q49" s="19" t="s">
+      <c r="Q49" t="s">
+        <v>1018</v>
+      </c>
+      <c r="R49" s="19" t="s">
         <v>579</v>
       </c>
-      <c r="R49" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B50" s="33"/>
+      <c r="S49" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="50" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B50" s="39"/>
       <c r="C50" s="4">
         <v>2</v>
       </c>
@@ -12139,15 +13197,18 @@
       <c r="P50" s="13" t="s">
         <v>686</v>
       </c>
-      <c r="Q50" s="17" t="s">
+      <c r="Q50" t="s">
+        <v>1019</v>
+      </c>
+      <c r="R50" s="17" t="s">
         <v>607</v>
       </c>
-      <c r="R50" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B51" s="33"/>
+      <c r="S50" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="51" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B51" s="39"/>
       <c r="C51" s="4">
         <v>3</v>
       </c>
@@ -12190,15 +13251,18 @@
       <c r="P51" s="13" t="s">
         <v>703</v>
       </c>
-      <c r="Q51" s="17" t="s">
+      <c r="Q51" t="s">
+        <v>1020</v>
+      </c>
+      <c r="R51" s="17" t="s">
         <v>622</v>
       </c>
-      <c r="R51" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B52" s="33"/>
+      <c r="S51" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="52" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B52" s="39"/>
       <c r="C52" s="4">
         <v>4</v>
       </c>
@@ -12241,15 +13305,18 @@
       <c r="P52" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="Q52" s="17" t="s">
+      <c r="Q52" t="s">
+        <v>1021</v>
+      </c>
+      <c r="R52" s="17" t="s">
         <v>676</v>
       </c>
-      <c r="R52" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="53" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="34"/>
+      <c r="S52" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="53" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="41"/>
       <c r="C53" s="10">
         <v>5</v>
       </c>
@@ -12292,379 +13359,382 @@
       <c r="P53" s="16" t="s">
         <v>510</v>
       </c>
-      <c r="Q53" s="20" t="s">
+      <c r="Q53" t="s">
+        <v>1022</v>
+      </c>
+      <c r="R53" s="20" t="s">
         <v>677</v>
       </c>
-      <c r="R53" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="54" spans="2:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="R54" s="23"/>
-    </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S53" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="S54" s="23"/>
+    </row>
+    <row r="55" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
       <c r="F56"/>
     </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
@@ -12672,7 +13742,14 @@
       <c r="F107" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="B34:B38"/>
     <mergeCell ref="B39:B43"/>
     <mergeCell ref="B44:B48"/>
@@ -12683,12 +13760,6 @@
     <mergeCell ref="B19:B23"/>
     <mergeCell ref="B24:B28"/>
     <mergeCell ref="B29:B33"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="Q2:Q3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12696,33 +13767,34 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="B1:R107"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:S107"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.5703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="4.453125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.54296875" style="3" customWidth="1"/>
     <col min="10" max="10" width="15" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.42578125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.453125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="4.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.54296875" style="3" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="38" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="76.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="32.26953125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="76.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.26953125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="7"/>
       <c r="C1" s="8"/>
       <c r="J1" s="8"/>
@@ -12733,43 +13805,47 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="9"/>
-    </row>
-    <row r="2" spans="2:18" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="35" t="s">
+      <c r="R1" s="8"/>
+      <c r="S1" s="9"/>
+    </row>
+    <row r="2" spans="2:19" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="42" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="37" t="s">
         <v>266</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="40" t="s">
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="37" t="s">
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="45" t="s">
+        <v>872</v>
+      </c>
+      <c r="R2" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="R2" s="41" t="s">
+      <c r="S2" s="35" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="36"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="24" t="s">
+    <row r="3" spans="2:19" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="43"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="11" t="s">
         <v>268</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -12784,7 +13860,7 @@
       <c r="H3" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="12" t="s">
         <v>273</v>
       </c>
       <c r="J3" s="11" t="s">
@@ -12808,11 +13884,12 @@
       <c r="P3" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="42"/>
-    </row>
-    <row r="4" spans="2:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="33">
+      <c r="Q3" s="46"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="36"/>
+    </row>
+    <row r="4" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="39">
         <v>1</v>
       </c>
       <c r="C4" s="4">
@@ -12833,7 +13910,7 @@
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="25" t="s">
+      <c r="I4" s="24" t="s">
         <v>705</v>
       </c>
       <c r="J4" s="17" t="s">
@@ -12857,15 +13934,18 @@
       <c r="P4" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="Q4" s="22" t="s">
+      <c r="Q4" s="17" t="s">
+        <v>1023</v>
+      </c>
+      <c r="R4" s="22" t="s">
         <v>707</v>
       </c>
-      <c r="R4" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="33"/>
+      <c r="S4" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B5" s="39"/>
       <c r="C5" s="4">
         <v>2</v>
       </c>
@@ -12908,15 +13988,18 @@
       <c r="P5" s="17" t="s">
         <v>708</v>
       </c>
-      <c r="Q5" s="22" t="s">
+      <c r="Q5" s="17" t="s">
+        <v>1024</v>
+      </c>
+      <c r="R5" s="22" t="s">
         <v>709</v>
       </c>
-      <c r="R5" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B6" s="33"/>
+      <c r="S5" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B6" s="39"/>
       <c r="C6" s="4">
         <v>3</v>
       </c>
@@ -12959,15 +14042,18 @@
       <c r="P6" s="17" t="s">
         <v>522</v>
       </c>
-      <c r="Q6" s="22" t="s">
+      <c r="Q6" s="17" t="s">
+        <v>1025</v>
+      </c>
+      <c r="R6" s="22" t="s">
         <v>712</v>
       </c>
-      <c r="R6" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B7" s="33"/>
+      <c r="S6" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B7" s="39"/>
       <c r="C7" s="4">
         <v>4</v>
       </c>
@@ -13010,15 +14096,18 @@
       <c r="P7" s="17" t="s">
         <v>850</v>
       </c>
-      <c r="Q7" s="22" t="s">
+      <c r="Q7" s="17" t="s">
+        <v>1026</v>
+      </c>
+      <c r="R7" s="22" t="s">
         <v>715</v>
       </c>
-      <c r="R7" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="39"/>
+      <c r="S7" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B8" s="40"/>
       <c r="C8" s="5">
         <v>5</v>
       </c>
@@ -13061,15 +14150,18 @@
       <c r="P8" s="18" t="s">
         <v>851</v>
       </c>
-      <c r="Q8" s="27" t="s">
+      <c r="Q8" s="18" t="s">
+        <v>1027</v>
+      </c>
+      <c r="R8" s="26" t="s">
         <v>718</v>
       </c>
-      <c r="R8" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="32">
+      <c r="S8" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B9" s="38">
         <v>2</v>
       </c>
       <c r="C9" s="6">
@@ -13114,15 +14206,18 @@
       <c r="P9" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="Q9" s="22" t="s">
+      <c r="Q9" s="44" t="s">
+        <v>1028</v>
+      </c>
+      <c r="R9" s="22" t="s">
         <v>721</v>
       </c>
-      <c r="R9" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="33"/>
+      <c r="S9" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B10" s="39"/>
       <c r="C10" s="4">
         <v>2</v>
       </c>
@@ -13165,15 +14260,18 @@
       <c r="P10" s="17" t="s">
         <v>852</v>
       </c>
-      <c r="Q10" s="22" t="s">
+      <c r="Q10" s="17" t="s">
+        <v>1029</v>
+      </c>
+      <c r="R10" s="22" t="s">
         <v>726</v>
       </c>
-      <c r="R10" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="33"/>
+      <c r="S10" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B11" s="39"/>
       <c r="C11" s="4">
         <v>3</v>
       </c>
@@ -13216,15 +14314,18 @@
       <c r="P11" s="17" t="s">
         <v>853</v>
       </c>
-      <c r="Q11" s="22" t="s">
+      <c r="Q11" s="17" t="s">
+        <v>1030</v>
+      </c>
+      <c r="R11" s="22" t="s">
         <v>732</v>
       </c>
-      <c r="R11" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="33"/>
+      <c r="S11" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B12" s="39"/>
       <c r="C12" s="4">
         <v>4</v>
       </c>
@@ -13267,15 +14368,18 @@
       <c r="P12" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="Q12" s="22" t="s">
+      <c r="Q12" s="17" t="s">
+        <v>1031</v>
+      </c>
+      <c r="R12" s="22" t="s">
         <v>735</v>
       </c>
-      <c r="R12" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="39"/>
+      <c r="S12" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B13" s="40"/>
       <c r="C13" s="5">
         <v>5</v>
       </c>
@@ -13318,15 +14422,18 @@
       <c r="P13" s="18" t="s">
         <v>854</v>
       </c>
-      <c r="Q13" s="22" t="s">
+      <c r="Q13" s="44" t="s">
+        <v>1032</v>
+      </c>
+      <c r="R13" s="22" t="s">
         <v>742</v>
       </c>
-      <c r="R13" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="32">
+      <c r="S13" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B14" s="38">
         <v>3</v>
       </c>
       <c r="C14" s="6">
@@ -13371,15 +14478,18 @@
       <c r="P14" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="Q14" s="28" t="s">
+      <c r="Q14" s="19" t="s">
+        <v>1033</v>
+      </c>
+      <c r="R14" s="27" t="s">
         <v>745</v>
       </c>
-      <c r="R14" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="33"/>
+      <c r="S14" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B15" s="39"/>
       <c r="C15" s="4">
         <v>2</v>
       </c>
@@ -13422,15 +14532,18 @@
       <c r="P15" s="17" t="s">
         <v>747</v>
       </c>
-      <c r="Q15" s="22" t="s">
+      <c r="Q15" s="17" t="s">
+        <v>1034</v>
+      </c>
+      <c r="R15" s="22" t="s">
         <v>748</v>
       </c>
-      <c r="R15" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="33"/>
+      <c r="S15" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B16" s="39"/>
       <c r="C16" s="4">
         <v>3</v>
       </c>
@@ -13473,15 +14586,18 @@
       <c r="P16" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="Q16" s="22" t="s">
+      <c r="Q16" s="17" t="s">
+        <v>1035</v>
+      </c>
+      <c r="R16" s="22" t="s">
         <v>750</v>
       </c>
-      <c r="R16" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="33"/>
+      <c r="S16" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B17" s="39"/>
       <c r="C17" s="4">
         <v>4</v>
       </c>
@@ -13524,15 +14640,18 @@
       <c r="P17" s="17" t="s">
         <v>752</v>
       </c>
-      <c r="Q17" s="22" t="s">
+      <c r="Q17" s="17" t="s">
+        <v>1036</v>
+      </c>
+      <c r="R17" s="22" t="s">
         <v>753</v>
       </c>
-      <c r="R17" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="39"/>
+      <c r="S17" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B18" s="40"/>
       <c r="C18" s="5">
         <v>5</v>
       </c>
@@ -13575,15 +14694,18 @@
       <c r="P18" s="18" t="s">
         <v>756</v>
       </c>
-      <c r="Q18" s="22" t="s">
+      <c r="Q18" s="44" t="s">
+        <v>1037</v>
+      </c>
+      <c r="R18" s="22" t="s">
         <v>757</v>
       </c>
-      <c r="R18" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="32">
+      <c r="S18" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B19" s="38">
         <v>4</v>
       </c>
       <c r="C19" s="6">
@@ -13628,15 +14750,18 @@
       <c r="P19" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="Q19" s="28" t="s">
+      <c r="Q19" s="19" t="s">
+        <v>1038</v>
+      </c>
+      <c r="R19" s="27" t="s">
         <v>758</v>
       </c>
-      <c r="R19" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="33"/>
+      <c r="S19" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B20" s="39"/>
       <c r="C20" s="4">
         <v>2</v>
       </c>
@@ -13679,15 +14804,18 @@
       <c r="P20" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="Q20" s="22" t="s">
+      <c r="Q20" s="17" t="s">
+        <v>1039</v>
+      </c>
+      <c r="R20" s="22" t="s">
         <v>761</v>
       </c>
-      <c r="R20" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="33"/>
+      <c r="S20" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B21" s="39"/>
       <c r="C21" s="4">
         <v>3</v>
       </c>
@@ -13730,15 +14858,18 @@
       <c r="P21" s="17" t="s">
         <v>763</v>
       </c>
-      <c r="Q21" s="22" t="s">
+      <c r="Q21" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="R21" s="22" t="s">
         <v>764</v>
       </c>
-      <c r="R21" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="33"/>
+      <c r="S21" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B22" s="39"/>
       <c r="C22" s="4">
         <v>4</v>
       </c>
@@ -13781,15 +14912,18 @@
       <c r="P22" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="Q22" s="22" t="s">
+      <c r="Q22" s="17" t="s">
+        <v>1041</v>
+      </c>
+      <c r="R22" s="22" t="s">
         <v>768</v>
       </c>
-      <c r="R22" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="39"/>
+      <c r="S22" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B23" s="40"/>
       <c r="C23" s="5">
         <v>5</v>
       </c>
@@ -13832,15 +14966,18 @@
       <c r="P23" s="18" t="s">
         <v>773</v>
       </c>
-      <c r="Q23" s="27" t="s">
+      <c r="Q23" s="18" t="s">
+        <v>1042</v>
+      </c>
+      <c r="R23" s="26" t="s">
         <v>774</v>
       </c>
-      <c r="R23" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="32">
+      <c r="S23" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B24" s="38">
         <v>5</v>
       </c>
       <c r="C24" s="6">
@@ -13885,15 +15022,18 @@
       <c r="P24" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="Q24" s="22" t="s">
+      <c r="Q24" s="44" t="s">
+        <v>1043</v>
+      </c>
+      <c r="R24" s="22" t="s">
         <v>775</v>
       </c>
-      <c r="R24" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="33"/>
+      <c r="S24" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B25" s="39"/>
       <c r="C25" s="4">
         <v>2</v>
       </c>
@@ -13936,15 +15076,18 @@
       <c r="P25" s="17" t="s">
         <v>695</v>
       </c>
-      <c r="Q25" s="22" t="s">
+      <c r="Q25" s="17" t="s">
+        <v>1044</v>
+      </c>
+      <c r="R25" s="22" t="s">
         <v>779</v>
       </c>
-      <c r="R25" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="33"/>
+      <c r="S25" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B26" s="39"/>
       <c r="C26" s="4">
         <v>3</v>
       </c>
@@ -13987,15 +15130,18 @@
       <c r="P26" s="17" t="s">
         <v>863</v>
       </c>
-      <c r="Q26" s="22" t="s">
+      <c r="Q26" s="17" t="s">
+        <v>1045</v>
+      </c>
+      <c r="R26" s="22" t="s">
         <v>782</v>
       </c>
-      <c r="R26" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="33"/>
+      <c r="S26" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B27" s="39"/>
       <c r="C27" s="4">
         <v>4</v>
       </c>
@@ -14038,15 +15184,18 @@
       <c r="P27" s="17" t="s">
         <v>831</v>
       </c>
-      <c r="Q27" s="22" t="s">
+      <c r="Q27" s="17" t="s">
+        <v>1046</v>
+      </c>
+      <c r="R27" s="22" t="s">
         <v>784</v>
       </c>
-      <c r="R27" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="39"/>
+      <c r="S27" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B28" s="40"/>
       <c r="C28" s="5">
         <v>5</v>
       </c>
@@ -14089,15 +15238,18 @@
       <c r="P28" s="18" t="s">
         <v>680</v>
       </c>
-      <c r="Q28" s="22" t="s">
+      <c r="Q28" s="44" t="s">
+        <v>1047</v>
+      </c>
+      <c r="R28" s="22" t="s">
         <v>787</v>
       </c>
-      <c r="R28" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="32">
+      <c r="S28" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B29" s="38">
         <v>6</v>
       </c>
       <c r="C29" s="6">
@@ -14142,15 +15294,18 @@
       <c r="P29" s="19" t="s">
         <v>683</v>
       </c>
-      <c r="Q29" s="28" t="s">
+      <c r="Q29" s="19" t="s">
+        <v>1048</v>
+      </c>
+      <c r="R29" s="27" t="s">
         <v>790</v>
       </c>
-      <c r="R29" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="33"/>
+      <c r="S29" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B30" s="39"/>
       <c r="C30" s="4">
         <v>2</v>
       </c>
@@ -14193,15 +15348,18 @@
       <c r="P30" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="Q30" s="22" t="s">
+      <c r="Q30" s="17" t="s">
+        <v>1049</v>
+      </c>
+      <c r="R30" s="22" t="s">
         <v>795</v>
       </c>
-      <c r="R30" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B31" s="33"/>
+      <c r="S30" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B31" s="39"/>
       <c r="C31" s="4">
         <v>3</v>
       </c>
@@ -14244,15 +15402,18 @@
       <c r="P31" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="Q31" s="22" t="s">
+      <c r="Q31" s="17" t="s">
+        <v>1050</v>
+      </c>
+      <c r="R31" s="22" t="s">
         <v>800</v>
       </c>
-      <c r="R31" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B32" s="33"/>
+      <c r="S31" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B32" s="39"/>
       <c r="C32" s="4">
         <v>4</v>
       </c>
@@ -14295,15 +15456,18 @@
       <c r="P32" s="17" t="s">
         <v>864</v>
       </c>
-      <c r="Q32" s="22" t="s">
+      <c r="Q32" s="17" t="s">
+        <v>1051</v>
+      </c>
+      <c r="R32" s="22" t="s">
         <v>803</v>
       </c>
-      <c r="R32" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B33" s="39"/>
+      <c r="S32" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B33" s="40"/>
       <c r="C33" s="5">
         <v>5</v>
       </c>
@@ -14346,15 +15510,18 @@
       <c r="P33" s="18" t="s">
         <v>526</v>
       </c>
-      <c r="Q33" s="27" t="s">
+      <c r="Q33" s="18" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R33" s="26" t="s">
         <v>808</v>
       </c>
-      <c r="R33" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B34" s="32">
+      <c r="S33" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B34" s="38">
         <v>7</v>
       </c>
       <c r="C34" s="6">
@@ -14399,15 +15566,18 @@
       <c r="P34" s="19" t="s">
         <v>853</v>
       </c>
-      <c r="Q34" s="22" t="s">
+      <c r="Q34" s="44" t="s">
+        <v>1053</v>
+      </c>
+      <c r="R34" s="22" t="s">
         <v>810</v>
       </c>
-      <c r="R34" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B35" s="33"/>
+      <c r="S34" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B35" s="39"/>
       <c r="C35" s="4">
         <v>2</v>
       </c>
@@ -14450,15 +15620,18 @@
       <c r="P35" s="17" t="s">
         <v>708</v>
       </c>
-      <c r="Q35" s="22" t="s">
+      <c r="Q35" s="17" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R35" s="22" t="s">
         <v>811</v>
       </c>
-      <c r="R35" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B36" s="33"/>
+      <c r="S35" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B36" s="39"/>
       <c r="C36" s="4">
         <v>3</v>
       </c>
@@ -14501,15 +15674,18 @@
       <c r="P36" s="17" t="s">
         <v>813</v>
       </c>
-      <c r="Q36" s="22" t="s">
+      <c r="Q36" s="17" t="s">
+        <v>1055</v>
+      </c>
+      <c r="R36" s="22" t="s">
         <v>814</v>
       </c>
-      <c r="R36" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="33"/>
+      <c r="S36" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B37" s="39"/>
       <c r="C37" s="4">
         <v>4</v>
       </c>
@@ -14552,15 +15728,18 @@
       <c r="P37" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="Q37" s="22" t="s">
+      <c r="Q37" s="17" t="s">
+        <v>1056</v>
+      </c>
+      <c r="R37" s="22" t="s">
         <v>816</v>
       </c>
-      <c r="R37" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B38" s="39"/>
+      <c r="S37" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B38" s="40"/>
       <c r="C38" s="5">
         <v>5</v>
       </c>
@@ -14603,15 +15782,18 @@
       <c r="P38" s="18" t="s">
         <v>865</v>
       </c>
-      <c r="Q38" s="27" t="s">
+      <c r="Q38" s="18" t="s">
+        <v>1057</v>
+      </c>
+      <c r="R38" s="26" t="s">
         <v>866</v>
       </c>
-      <c r="R38" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B39" s="32">
+      <c r="S38" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B39" s="38">
         <v>8</v>
       </c>
       <c r="C39" s="6">
@@ -14656,15 +15838,18 @@
       <c r="P39" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="Q39" s="22" t="s">
+      <c r="Q39" s="44" t="s">
+        <v>1058</v>
+      </c>
+      <c r="R39" s="22" t="s">
         <v>818</v>
       </c>
-      <c r="R39" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="33"/>
+      <c r="S39" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B40" s="39"/>
       <c r="C40" s="4">
         <v>2</v>
       </c>
@@ -14707,15 +15892,18 @@
       <c r="P40" s="17" t="s">
         <v>819</v>
       </c>
-      <c r="Q40" s="22" t="s">
+      <c r="Q40" s="17" t="s">
+        <v>1059</v>
+      </c>
+      <c r="R40" s="22" t="s">
         <v>820</v>
       </c>
-      <c r="R40" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B41" s="33"/>
+      <c r="S40" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B41" s="39"/>
       <c r="C41" s="4">
         <v>3</v>
       </c>
@@ -14758,15 +15946,18 @@
       <c r="P41" s="17" t="s">
         <v>822</v>
       </c>
-      <c r="Q41" s="22" t="s">
+      <c r="Q41" s="17" t="s">
+        <v>1060</v>
+      </c>
+      <c r="R41" s="22" t="s">
         <v>823</v>
       </c>
-      <c r="R41" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="33"/>
+      <c r="S41" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B42" s="39"/>
       <c r="C42" s="4">
         <v>4</v>
       </c>
@@ -14809,15 +16000,18 @@
       <c r="P42" s="17" t="s">
         <v>824</v>
       </c>
-      <c r="Q42" s="22" t="s">
+      <c r="Q42" s="17" t="s">
+        <v>1061</v>
+      </c>
+      <c r="R42" s="22" t="s">
         <v>825</v>
       </c>
-      <c r="R42" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" s="39"/>
+      <c r="S42" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B43" s="40"/>
       <c r="C43" s="5">
         <v>5</v>
       </c>
@@ -14860,15 +16054,18 @@
       <c r="P43" s="18" t="s">
         <v>826</v>
       </c>
-      <c r="Q43" s="22" t="s">
+      <c r="Q43" s="44" t="s">
+        <v>1062</v>
+      </c>
+      <c r="R43" s="22" t="s">
         <v>827</v>
       </c>
-      <c r="R43" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="32">
+      <c r="S43" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B44" s="38">
         <v>9</v>
       </c>
       <c r="C44" s="6">
@@ -14913,15 +16110,18 @@
       <c r="P44" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="Q44" s="28" t="s">
+      <c r="Q44" s="19" t="s">
+        <v>1063</v>
+      </c>
+      <c r="R44" s="27" t="s">
         <v>830</v>
       </c>
-      <c r="R44" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B45" s="33"/>
+      <c r="S44" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B45" s="39"/>
       <c r="C45" s="4">
         <v>2</v>
       </c>
@@ -14964,15 +16164,18 @@
       <c r="P45" s="17" t="s">
         <v>831</v>
       </c>
-      <c r="Q45" s="22" t="s">
+      <c r="Q45" s="17" t="s">
+        <v>1064</v>
+      </c>
+      <c r="R45" s="22" t="s">
         <v>832</v>
       </c>
-      <c r="R45" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B46" s="33"/>
+      <c r="S45" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B46" s="39"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
@@ -15015,15 +16218,18 @@
       <c r="P46" s="17" t="s">
         <v>833</v>
       </c>
-      <c r="Q46" s="22" t="s">
+      <c r="Q46" s="17" t="s">
+        <v>1065</v>
+      </c>
+      <c r="R46" s="22" t="s">
         <v>834</v>
       </c>
-      <c r="R46" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="33"/>
+      <c r="S46" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B47" s="39"/>
       <c r="C47" s="4">
         <v>4</v>
       </c>
@@ -15066,15 +16272,18 @@
       <c r="P47" s="17" t="s">
         <v>836</v>
       </c>
-      <c r="Q47" s="22" t="s">
+      <c r="Q47" s="17" t="s">
+        <v>1066</v>
+      </c>
+      <c r="R47" s="22" t="s">
         <v>837</v>
       </c>
-      <c r="R47" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B48" s="39"/>
+      <c r="S47" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B48" s="40"/>
       <c r="C48" s="5">
         <v>5</v>
       </c>
@@ -15117,15 +16326,18 @@
       <c r="P48" s="18" t="s">
         <v>838</v>
       </c>
-      <c r="Q48" s="27" t="s">
+      <c r="Q48" s="18" t="s">
+        <v>1067</v>
+      </c>
+      <c r="R48" s="26" t="s">
         <v>839</v>
       </c>
-      <c r="R48" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B49" s="32">
+      <c r="S48" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="49" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B49" s="38">
         <v>10</v>
       </c>
       <c r="C49" s="6">
@@ -15168,15 +16380,18 @@
       <c r="P49" s="19" t="s">
         <v>683</v>
       </c>
-      <c r="Q49" s="22" t="s">
+      <c r="Q49" s="44" t="s">
+        <v>1068</v>
+      </c>
+      <c r="R49" s="22" t="s">
         <v>840</v>
       </c>
-      <c r="R49" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B50" s="33"/>
+      <c r="S49" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="50" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B50" s="39"/>
       <c r="C50" s="4">
         <v>2</v>
       </c>
@@ -15219,15 +16434,18 @@
       <c r="P50" s="17" t="s">
         <v>869</v>
       </c>
-      <c r="Q50" s="22" t="s">
+      <c r="Q50" s="17" t="s">
+        <v>1069</v>
+      </c>
+      <c r="R50" s="22" t="s">
         <v>842</v>
       </c>
-      <c r="R50" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B51" s="33"/>
+      <c r="S50" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="51" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B51" s="39"/>
       <c r="C51" s="4">
         <v>3</v>
       </c>
@@ -15270,15 +16488,18 @@
       <c r="P51" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="Q51" s="22" t="s">
+      <c r="Q51" s="17" t="s">
+        <v>1070</v>
+      </c>
+      <c r="R51" s="22" t="s">
         <v>843</v>
       </c>
-      <c r="R51" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B52" s="33"/>
+      <c r="S51" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="52" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B52" s="39"/>
       <c r="C52" s="4">
         <v>4</v>
       </c>
@@ -15321,15 +16542,18 @@
       <c r="P52" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="Q52" s="22" t="s">
+      <c r="Q52" s="17" t="s">
+        <v>1071</v>
+      </c>
+      <c r="R52" s="22" t="s">
         <v>846</v>
       </c>
-      <c r="R52" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="53" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="34"/>
+      <c r="S52" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="53" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="41"/>
       <c r="C53" s="10">
         <v>5</v>
       </c>
@@ -15372,430 +16596,440 @@
       <c r="P53" s="20" t="s">
         <v>870</v>
       </c>
-      <c r="Q53" s="26" t="s">
+      <c r="Q53" s="20" t="s">
+        <v>1072</v>
+      </c>
+      <c r="R53" s="25" t="s">
         <v>849</v>
       </c>
-      <c r="R53" s="22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="54" spans="2:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="R54" s="23"/>
-    </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S53" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="S54" s="23"/>
+    </row>
+    <row r="55" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
       <c r="F56"/>
     </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="R65" s="2"/>
-    </row>
-    <row r="66" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S65" s="2"/>
+    </row>
+    <row r="66" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="R66" s="2"/>
-    </row>
-    <row r="67" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S66" s="2"/>
+    </row>
+    <row r="67" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="R67" s="2"/>
-    </row>
-    <row r="68" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S67" s="2"/>
+    </row>
+    <row r="68" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="R68" s="2"/>
-    </row>
-    <row r="69" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S68" s="2"/>
+    </row>
+    <row r="69" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="R69" s="2"/>
-    </row>
-    <row r="70" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S69" s="2"/>
+    </row>
+    <row r="70" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="R70" s="2"/>
-    </row>
-    <row r="71" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S70" s="2"/>
+    </row>
+    <row r="71" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="R71" s="2"/>
-    </row>
-    <row r="72" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S71" s="2"/>
+    </row>
+    <row r="72" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="R72" s="2"/>
-    </row>
-    <row r="73" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S72" s="2"/>
+    </row>
+    <row r="73" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="R73" s="2"/>
-    </row>
-    <row r="74" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S73" s="2"/>
+    </row>
+    <row r="74" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="R74" s="2"/>
-    </row>
-    <row r="75" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S74" s="2"/>
+    </row>
+    <row r="75" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="R75" s="2"/>
-    </row>
-    <row r="76" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S75" s="2"/>
+    </row>
+    <row r="76" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="R76" s="2"/>
-    </row>
-    <row r="77" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S76" s="2"/>
+    </row>
+    <row r="77" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="R77" s="2"/>
-    </row>
-    <row r="78" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S77" s="2"/>
+    </row>
+    <row r="78" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="R78" s="2"/>
-    </row>
-    <row r="79" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S78" s="2"/>
+    </row>
+    <row r="79" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="R79" s="2"/>
-    </row>
-    <row r="80" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S79" s="2"/>
+    </row>
+    <row r="80" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="R81" s="2"/>
-    </row>
-    <row r="82" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S81" s="2"/>
+    </row>
+    <row r="82" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="R82" s="2"/>
-    </row>
-    <row r="83" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S82" s="2"/>
+    </row>
+    <row r="83" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-      <c r="R83" s="2"/>
-    </row>
-    <row r="84" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S83" s="2"/>
+    </row>
+    <row r="84" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
-      <c r="R84" s="2"/>
-    </row>
-    <row r="85" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S84" s="2"/>
+    </row>
+    <row r="85" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-      <c r="R85" s="2"/>
-    </row>
-    <row r="86" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S85" s="2"/>
+    </row>
+    <row r="86" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="R86" s="2"/>
-    </row>
-    <row r="87" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S86" s="2"/>
+    </row>
+    <row r="87" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="R87" s="2"/>
-    </row>
-    <row r="88" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S87" s="2"/>
+    </row>
+    <row r="88" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
-      <c r="R88" s="2"/>
-    </row>
-    <row r="89" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S88" s="2"/>
+    </row>
+    <row r="89" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
-      <c r="R89" s="2"/>
-    </row>
-    <row r="90" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S89" s="2"/>
+    </row>
+    <row r="90" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
-      <c r="R90" s="2"/>
-    </row>
-    <row r="91" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S90" s="2"/>
+    </row>
+    <row r="91" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
-      <c r="R91" s="2"/>
-    </row>
-    <row r="92" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S91" s="2"/>
+    </row>
+    <row r="92" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
-      <c r="R92" s="2"/>
-    </row>
-    <row r="93" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S92" s="2"/>
+    </row>
+    <row r="93" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
-      <c r="R93" s="2"/>
-    </row>
-    <row r="94" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S93" s="2"/>
+    </row>
+    <row r="94" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
-      <c r="R94" s="2"/>
-    </row>
-    <row r="95" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S94" s="2"/>
+    </row>
+    <row r="95" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
-      <c r="R95" s="2"/>
-    </row>
-    <row r="96" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S95" s="2"/>
+    </row>
+    <row r="96" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-      <c r="R96" s="2"/>
-    </row>
-    <row r="97" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S96" s="2"/>
+    </row>
+    <row r="97" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
-      <c r="R97" s="2"/>
-    </row>
-    <row r="98" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S97" s="2"/>
+    </row>
+    <row r="98" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="R98" s="2"/>
-    </row>
-    <row r="99" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S98" s="2"/>
+    </row>
+    <row r="99" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-      <c r="R99" s="2"/>
-    </row>
-    <row r="100" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S99" s="2"/>
+    </row>
+    <row r="100" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="R100" s="2"/>
-    </row>
-    <row r="101" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S100" s="2"/>
+    </row>
+    <row r="101" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="R101" s="2"/>
-    </row>
-    <row r="102" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S101" s="2"/>
+    </row>
+    <row r="102" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
-      <c r="R102" s="2"/>
-    </row>
-    <row r="103" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S102" s="2"/>
+    </row>
+    <row r="103" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
-      <c r="R103" s="2"/>
-    </row>
-    <row r="104" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S103" s="2"/>
+    </row>
+    <row r="104" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
-      <c r="R104" s="2"/>
-    </row>
-    <row r="105" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S104" s="2"/>
+    </row>
+    <row r="105" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
-      <c r="R105" s="2"/>
-    </row>
-    <row r="106" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S105" s="2"/>
+    </row>
+    <row r="106" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
-      <c r="R106" s="2"/>
-    </row>
-    <row r="107" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S106" s="2"/>
+    </row>
+    <row r="107" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
-      <c r="R107" s="2"/>
+      <c r="S107" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="B34:B38"/>
     <mergeCell ref="B39:B43"/>
     <mergeCell ref="B44:B48"/>
@@ -15806,12 +17040,6 @@
     <mergeCell ref="B19:B23"/>
     <mergeCell ref="B24:B28"/>
     <mergeCell ref="B29:B33"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="Q2:Q3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
